--- a/artfynd/A 9618-2025 artfynd.xlsx
+++ b/artfynd/A 9618-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AY52"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1024,6 +1024,5057 @@
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>124880332</v>
+      </c>
+      <c r="B5" t="n">
+        <v>91030</v>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>5432</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Granticka</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Porodaedalea chrysoloma</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Lill-tjärnvallen sö, Hjd</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>433197</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6935385</v>
+      </c>
+      <c r="S5" t="n">
+        <v>10</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Vemdalen</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2025-05-08</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2025-05-08</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>124880299</v>
+      </c>
+      <c r="B6" t="n">
+        <v>57513</v>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Lill-tjärnvallen sö, Hjd</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>434112</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6936130</v>
+      </c>
+      <c r="S6" t="n">
+        <v>10</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Vemdalen</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2025-05-08</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2025-05-08</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>124880315</v>
+      </c>
+      <c r="B7" t="n">
+        <v>57513</v>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Lill-tjärnvallen sö, Hjd</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>434466</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6936862</v>
+      </c>
+      <c r="S7" t="n">
+        <v>10</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Vemdalen</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2025-05-08</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2025-05-08</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>124880303</v>
+      </c>
+      <c r="B8" t="n">
+        <v>57513</v>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Lill-tjärnvallen sö, Hjd</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>434113</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6936181</v>
+      </c>
+      <c r="S8" t="n">
+        <v>10</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Vemdalen</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2025-05-08</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2025-05-08</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Ringhack färska och äldre</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>124880324</v>
+      </c>
+      <c r="B9" t="n">
+        <v>91008</v>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>1108</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Harticka</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Pelloporus leporinus</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(Fr.) Krieglst.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Lill-tjärnvallen sö, Hjd</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>433261</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6935504</v>
+      </c>
+      <c r="S9" t="n">
+        <v>10</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Vemdalen</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2025-05-08</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2025-05-08</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>124880337</v>
+      </c>
+      <c r="B10" t="n">
+        <v>91030</v>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>5432</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Granticka</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Porodaedalea chrysoloma</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Lill-tjärnvallen sö, Hjd</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>433534</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6935858</v>
+      </c>
+      <c r="S10" t="n">
+        <v>10</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Vemdalen</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2025-05-08</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2025-05-08</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>124880345</v>
+      </c>
+      <c r="B11" t="n">
+        <v>91030</v>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>5432</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Granticka</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Porodaedalea chrysoloma</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Lill-tjärnvallen sö, Hjd</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>434057</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6936091</v>
+      </c>
+      <c r="S11" t="n">
+        <v>10</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Vemdalen</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2025-05-08</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2025-05-08</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>124880237</v>
+      </c>
+      <c r="B12" t="n">
+        <v>91012</v>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Lill-tjärnvallen sö, Hjd</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>433636</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6935914</v>
+      </c>
+      <c r="S12" t="n">
+        <v>10</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Vemdalen</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2025-05-08</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2025-05-08</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>124880350</v>
+      </c>
+      <c r="B13" t="n">
+        <v>91030</v>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>5432</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Granticka</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Porodaedalea chrysoloma</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Lill-tjärnvallen sö, Hjd</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>434118</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6936187</v>
+      </c>
+      <c r="S13" t="n">
+        <v>10</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Vemdalen</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2025-05-08</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2025-05-08</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>124880369</v>
+      </c>
+      <c r="B14" t="n">
+        <v>78810</v>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Lill-tjärnvallen sö, Hjd</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>434091</v>
+      </c>
+      <c r="R14" t="n">
+        <v>6936122</v>
+      </c>
+      <c r="S14" t="n">
+        <v>10</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Vemdalen</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2025-05-08</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2025-05-08</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Mycket rikligt</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>124880358</v>
+      </c>
+      <c r="B15" t="n">
+        <v>78810</v>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Lill-tjärnvallen sö, Hjd</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>433076</v>
+      </c>
+      <c r="R15" t="n">
+        <v>6935108</v>
+      </c>
+      <c r="S15" t="n">
+        <v>10</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Vemdalen</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2025-05-08</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2025-05-08</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>124880340</v>
+      </c>
+      <c r="B16" t="n">
+        <v>91030</v>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>5432</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Granticka</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Porodaedalea chrysoloma</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Lill-tjärnvallen sö, Hjd</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>433661</v>
+      </c>
+      <c r="R16" t="n">
+        <v>6935941</v>
+      </c>
+      <c r="S16" t="n">
+        <v>10</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Vemdalen</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2025-05-08</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2025-05-08</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>124880305</v>
+      </c>
+      <c r="B17" t="n">
+        <v>57513</v>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Lill-tjärnvallen sö, Hjd</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>434128</v>
+      </c>
+      <c r="R17" t="n">
+        <v>6936677</v>
+      </c>
+      <c r="S17" t="n">
+        <v>10</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Vemdalen</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2025-05-08</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2025-05-08</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>124880367</v>
+      </c>
+      <c r="B18" t="n">
+        <v>78810</v>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Lill-tjärnvallen sö, Hjd</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>433984</v>
+      </c>
+      <c r="R18" t="n">
+        <v>6936073</v>
+      </c>
+      <c r="S18" t="n">
+        <v>10</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Vemdalen</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2025-05-08</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2025-05-08</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Mycket rikligt</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>124880275</v>
+      </c>
+      <c r="B19" t="n">
+        <v>57513</v>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Lill-tjärnvallen sö, Hjd</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>432954</v>
+      </c>
+      <c r="R19" t="n">
+        <v>6934982</v>
+      </c>
+      <c r="S19" t="n">
+        <v>10</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Vemdalen</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2025-05-08</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2025-05-08</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>124880326</v>
+      </c>
+      <c r="B20" t="n">
+        <v>91008</v>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>1108</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Harticka</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Pelloporus leporinus</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>(Fr.) Krieglst.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Lill-tjärnvallen sö, Hjd</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>434175</v>
+      </c>
+      <c r="R20" t="n">
+        <v>6936309</v>
+      </c>
+      <c r="S20" t="n">
+        <v>10</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Vemdalen</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2025-05-08</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2025-05-08</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>124880314</v>
+      </c>
+      <c r="B21" t="n">
+        <v>57513</v>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Lill-tjärnvallen sö, Hjd</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>434484</v>
+      </c>
+      <c r="R21" t="n">
+        <v>6936850</v>
+      </c>
+      <c r="S21" t="n">
+        <v>10</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Vemdalen</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2025-05-08</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2025-05-08</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>124880360</v>
+      </c>
+      <c r="B22" t="n">
+        <v>78810</v>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Lill-tjärnvallen sö, Hjd</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>433248</v>
+      </c>
+      <c r="R22" t="n">
+        <v>6935491</v>
+      </c>
+      <c r="S22" t="n">
+        <v>10</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Vemdalen</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2025-05-08</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2025-05-08</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>Mycket rikligt</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>124880373</v>
+      </c>
+      <c r="B23" t="n">
+        <v>78810</v>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Lill-tjärnvallen sö, Hjd</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>434482</v>
+      </c>
+      <c r="R23" t="n">
+        <v>6936858</v>
+      </c>
+      <c r="S23" t="n">
+        <v>10</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Vemdalen</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2025-05-08</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>2025-05-08</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
+        </is>
+      </c>
+      <c r="AD23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>124880290</v>
+      </c>
+      <c r="B24" t="n">
+        <v>57513</v>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>Lill-tjärnvallen sö, Hjd</t>
+        </is>
+      </c>
+      <c r="Q24" t="n">
+        <v>433820</v>
+      </c>
+      <c r="R24" t="n">
+        <v>6936000</v>
+      </c>
+      <c r="S24" t="n">
+        <v>10</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Vemdalen</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>2025-05-08</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>2025-05-08</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
+        </is>
+      </c>
+      <c r="AD24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT24" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>124880344</v>
+      </c>
+      <c r="B25" t="n">
+        <v>91030</v>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>5432</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Granticka</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Porodaedalea chrysoloma</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>Lill-tjärnvallen sö, Hjd</t>
+        </is>
+      </c>
+      <c r="Q25" t="n">
+        <v>434028</v>
+      </c>
+      <c r="R25" t="n">
+        <v>6936084</v>
+      </c>
+      <c r="S25" t="n">
+        <v>10</v>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>Vemdalen</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>2025-05-08</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>2025-05-08</t>
+        </is>
+      </c>
+      <c r="AD25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT25" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX25" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>124880310</v>
+      </c>
+      <c r="B26" t="n">
+        <v>57513</v>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>Lill-tjärnvallen sö, Hjd</t>
+        </is>
+      </c>
+      <c r="Q26" t="n">
+        <v>434385</v>
+      </c>
+      <c r="R26" t="n">
+        <v>6936814</v>
+      </c>
+      <c r="S26" t="n">
+        <v>10</v>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>Vemdalen</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>2025-05-08</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>2025-05-08</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
+        </is>
+      </c>
+      <c r="AD26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT26" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX26" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>124880364</v>
+      </c>
+      <c r="B27" t="n">
+        <v>78810</v>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>Lill-tjärnvallen sö, Hjd</t>
+        </is>
+      </c>
+      <c r="Q27" t="n">
+        <v>433682</v>
+      </c>
+      <c r="R27" t="n">
+        <v>6935955</v>
+      </c>
+      <c r="S27" t="n">
+        <v>10</v>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>Vemdalen</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>2025-05-08</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>2025-05-08</t>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>Mycket rikligt</t>
+        </is>
+      </c>
+      <c r="AD27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT27" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX27" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>124880288</v>
+      </c>
+      <c r="B28" t="n">
+        <v>57513</v>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>Lill-tjärnvallen sö, Hjd</t>
+        </is>
+      </c>
+      <c r="Q28" t="n">
+        <v>433505</v>
+      </c>
+      <c r="R28" t="n">
+        <v>6935809</v>
+      </c>
+      <c r="S28" t="n">
+        <v>10</v>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>Vemdalen</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>2025-05-08</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>2025-05-08</t>
+        </is>
+      </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
+        </is>
+      </c>
+      <c r="AD28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT28" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX28" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY28" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>124880316</v>
+      </c>
+      <c r="B29" t="n">
+        <v>57513</v>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>Lill-tjärnvallen sö, Hjd</t>
+        </is>
+      </c>
+      <c r="Q29" t="n">
+        <v>434532</v>
+      </c>
+      <c r="R29" t="n">
+        <v>6936893</v>
+      </c>
+      <c r="S29" t="n">
+        <v>10</v>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>Vemdalen</t>
+        </is>
+      </c>
+      <c r="Y29" t="inlineStr">
+        <is>
+          <t>2025-05-08</t>
+        </is>
+      </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>2025-05-08</t>
+        </is>
+      </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
+        </is>
+      </c>
+      <c r="AD29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT29" t="inlineStr"/>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX29" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY29" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>124880353</v>
+      </c>
+      <c r="B30" t="n">
+        <v>91030</v>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>5432</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Granticka</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Porodaedalea chrysoloma</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>Lill-tjärnvallen sö, Hjd</t>
+        </is>
+      </c>
+      <c r="Q30" t="n">
+        <v>434173</v>
+      </c>
+      <c r="R30" t="n">
+        <v>6936342</v>
+      </c>
+      <c r="S30" t="n">
+        <v>10</v>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t>Vemdalen</t>
+        </is>
+      </c>
+      <c r="Y30" t="inlineStr">
+        <is>
+          <t>2025-05-08</t>
+        </is>
+      </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>2025-05-08</t>
+        </is>
+      </c>
+      <c r="AD30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT30" t="inlineStr"/>
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX30" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY30" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>124880361</v>
+      </c>
+      <c r="B31" t="n">
+        <v>78810</v>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>Lill-tjärnvallen sö, Hjd</t>
+        </is>
+      </c>
+      <c r="Q31" t="n">
+        <v>433311</v>
+      </c>
+      <c r="R31" t="n">
+        <v>6935592</v>
+      </c>
+      <c r="S31" t="n">
+        <v>10</v>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W31" t="inlineStr">
+        <is>
+          <t>Vemdalen</t>
+        </is>
+      </c>
+      <c r="Y31" t="inlineStr">
+        <is>
+          <t>2025-05-08</t>
+        </is>
+      </c>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>2025-05-08</t>
+        </is>
+      </c>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
+        </is>
+      </c>
+      <c r="AD31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT31" t="inlineStr"/>
+      <c r="AW31" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX31" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY31" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>124880359</v>
+      </c>
+      <c r="B32" t="n">
+        <v>78810</v>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>Lill-tjärnvallen sö, Hjd</t>
+        </is>
+      </c>
+      <c r="Q32" t="n">
+        <v>433093</v>
+      </c>
+      <c r="R32" t="n">
+        <v>6935150</v>
+      </c>
+      <c r="S32" t="n">
+        <v>10</v>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W32" t="inlineStr">
+        <is>
+          <t>Vemdalen</t>
+        </is>
+      </c>
+      <c r="Y32" t="inlineStr">
+        <is>
+          <t>2025-05-08</t>
+        </is>
+      </c>
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t>2025-05-08</t>
+        </is>
+      </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
+        </is>
+      </c>
+      <c r="AD32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT32" t="inlineStr"/>
+      <c r="AW32" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX32" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY32" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>124880333</v>
+      </c>
+      <c r="B33" t="n">
+        <v>91030</v>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E33" t="n">
+        <v>5432</v>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Granticka</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Porodaedalea chrysoloma</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>Lill-tjärnvallen sö, Hjd</t>
+        </is>
+      </c>
+      <c r="Q33" t="n">
+        <v>433376</v>
+      </c>
+      <c r="R33" t="n">
+        <v>6935725</v>
+      </c>
+      <c r="S33" t="n">
+        <v>10</v>
+      </c>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V33" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W33" t="inlineStr">
+        <is>
+          <t>Vemdalen</t>
+        </is>
+      </c>
+      <c r="Y33" t="inlineStr">
+        <is>
+          <t>2025-05-08</t>
+        </is>
+      </c>
+      <c r="AA33" t="inlineStr">
+        <is>
+          <t>2025-05-08</t>
+        </is>
+      </c>
+      <c r="AD33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT33" t="inlineStr"/>
+      <c r="AW33" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX33" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY33" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>124880286</v>
+      </c>
+      <c r="B34" t="n">
+        <v>57513</v>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E34" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>Lill-tjärnvallen sö, Hjd</t>
+        </is>
+      </c>
+      <c r="Q34" t="n">
+        <v>433434</v>
+      </c>
+      <c r="R34" t="n">
+        <v>6935749</v>
+      </c>
+      <c r="S34" t="n">
+        <v>10</v>
+      </c>
+      <c r="T34" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V34" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W34" t="inlineStr">
+        <is>
+          <t>Vemdalen</t>
+        </is>
+      </c>
+      <c r="Y34" t="inlineStr">
+        <is>
+          <t>2025-05-08</t>
+        </is>
+      </c>
+      <c r="AA34" t="inlineStr">
+        <is>
+          <t>2025-05-08</t>
+        </is>
+      </c>
+      <c r="AC34" t="inlineStr">
+        <is>
+          <t>Ringhack färska och äldre</t>
+        </is>
+      </c>
+      <c r="AD34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT34" t="inlineStr"/>
+      <c r="AW34" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX34" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY34" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>124880313</v>
+      </c>
+      <c r="B35" t="n">
+        <v>57513</v>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E35" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>Lill-tjärnvallen sö, Hjd</t>
+        </is>
+      </c>
+      <c r="Q35" t="n">
+        <v>434447</v>
+      </c>
+      <c r="R35" t="n">
+        <v>6936828</v>
+      </c>
+      <c r="S35" t="n">
+        <v>10</v>
+      </c>
+      <c r="T35" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U35" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V35" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W35" t="inlineStr">
+        <is>
+          <t>Vemdalen</t>
+        </is>
+      </c>
+      <c r="Y35" t="inlineStr">
+        <is>
+          <t>2025-05-08</t>
+        </is>
+      </c>
+      <c r="AA35" t="inlineStr">
+        <is>
+          <t>2025-05-08</t>
+        </is>
+      </c>
+      <c r="AC35" t="inlineStr">
+        <is>
+          <t>Ringhack färska och äldre</t>
+        </is>
+      </c>
+      <c r="AD35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT35" t="inlineStr"/>
+      <c r="AW35" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX35" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY35" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>124880365</v>
+      </c>
+      <c r="B36" t="n">
+        <v>78810</v>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E36" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr"/>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>Lill-tjärnvallen sö, Hjd</t>
+        </is>
+      </c>
+      <c r="Q36" t="n">
+        <v>433755</v>
+      </c>
+      <c r="R36" t="n">
+        <v>6935995</v>
+      </c>
+      <c r="S36" t="n">
+        <v>10</v>
+      </c>
+      <c r="T36" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U36" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V36" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W36" t="inlineStr">
+        <is>
+          <t>Vemdalen</t>
+        </is>
+      </c>
+      <c r="Y36" t="inlineStr">
+        <is>
+          <t>2025-05-08</t>
+        </is>
+      </c>
+      <c r="AA36" t="inlineStr">
+        <is>
+          <t>2025-05-08</t>
+        </is>
+      </c>
+      <c r="AC36" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
+        </is>
+      </c>
+      <c r="AD36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT36" t="inlineStr"/>
+      <c r="AW36" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX36" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY36" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>124880343</v>
+      </c>
+      <c r="B37" t="n">
+        <v>91030</v>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E37" t="n">
+        <v>5432</v>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Granticka</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>Porodaedalea chrysoloma</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr"/>
+      <c r="P37" t="inlineStr">
+        <is>
+          <t>Lill-tjärnvallen sö, Hjd</t>
+        </is>
+      </c>
+      <c r="Q37" t="n">
+        <v>433952</v>
+      </c>
+      <c r="R37" t="n">
+        <v>6936054</v>
+      </c>
+      <c r="S37" t="n">
+        <v>10</v>
+      </c>
+      <c r="T37" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U37" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V37" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W37" t="inlineStr">
+        <is>
+          <t>Vemdalen</t>
+        </is>
+      </c>
+      <c r="Y37" t="inlineStr">
+        <is>
+          <t>2025-05-08</t>
+        </is>
+      </c>
+      <c r="AA37" t="inlineStr">
+        <is>
+          <t>2025-05-08</t>
+        </is>
+      </c>
+      <c r="AD37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT37" t="inlineStr"/>
+      <c r="AW37" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX37" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY37" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>124880283</v>
+      </c>
+      <c r="B38" t="n">
+        <v>57513</v>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E38" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr"/>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>Lill-tjärnvallen sö, Hjd</t>
+        </is>
+      </c>
+      <c r="Q38" t="n">
+        <v>433376</v>
+      </c>
+      <c r="R38" t="n">
+        <v>6935695</v>
+      </c>
+      <c r="S38" t="n">
+        <v>10</v>
+      </c>
+      <c r="T38" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U38" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V38" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W38" t="inlineStr">
+        <is>
+          <t>Vemdalen</t>
+        </is>
+      </c>
+      <c r="Y38" t="inlineStr">
+        <is>
+          <t>2025-05-08</t>
+        </is>
+      </c>
+      <c r="AA38" t="inlineStr">
+        <is>
+          <t>2025-05-08</t>
+        </is>
+      </c>
+      <c r="AC38" t="inlineStr">
+        <is>
+          <t>Ringhack färska</t>
+        </is>
+      </c>
+      <c r="AD38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT38" t="inlineStr"/>
+      <c r="AW38" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX38" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY38" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>124880318</v>
+      </c>
+      <c r="B39" t="n">
+        <v>57513</v>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E39" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr"/>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>Lill-tjärnvallen sö, Hjd</t>
+        </is>
+      </c>
+      <c r="Q39" t="n">
+        <v>434664</v>
+      </c>
+      <c r="R39" t="n">
+        <v>6936929</v>
+      </c>
+      <c r="S39" t="n">
+        <v>10</v>
+      </c>
+      <c r="T39" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U39" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V39" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W39" t="inlineStr">
+        <is>
+          <t>Vemdalen</t>
+        </is>
+      </c>
+      <c r="Y39" t="inlineStr">
+        <is>
+          <t>2025-05-08</t>
+        </is>
+      </c>
+      <c r="AA39" t="inlineStr">
+        <is>
+          <t>2025-05-08</t>
+        </is>
+      </c>
+      <c r="AC39" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
+        </is>
+      </c>
+      <c r="AD39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT39" t="inlineStr"/>
+      <c r="AW39" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX39" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY39" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>124880278</v>
+      </c>
+      <c r="B40" t="n">
+        <v>57513</v>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E40" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr"/>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>Lill-tjärnvallen sö, Hjd</t>
+        </is>
+      </c>
+      <c r="Q40" t="n">
+        <v>433331</v>
+      </c>
+      <c r="R40" t="n">
+        <v>6935597</v>
+      </c>
+      <c r="S40" t="n">
+        <v>10</v>
+      </c>
+      <c r="T40" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U40" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V40" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W40" t="inlineStr">
+        <is>
+          <t>Vemdalen</t>
+        </is>
+      </c>
+      <c r="Y40" t="inlineStr">
+        <is>
+          <t>2025-05-08</t>
+        </is>
+      </c>
+      <c r="AA40" t="inlineStr">
+        <is>
+          <t>2025-05-08</t>
+        </is>
+      </c>
+      <c r="AC40" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
+        </is>
+      </c>
+      <c r="AD40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT40" t="inlineStr"/>
+      <c r="AW40" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX40" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY40" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>124880355</v>
+      </c>
+      <c r="B41" t="n">
+        <v>91030</v>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E41" t="n">
+        <v>5432</v>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>Granticka</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>Porodaedalea chrysoloma</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr"/>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>Lill-tjärnvallen sö, Hjd</t>
+        </is>
+      </c>
+      <c r="Q41" t="n">
+        <v>434478</v>
+      </c>
+      <c r="R41" t="n">
+        <v>6936874</v>
+      </c>
+      <c r="S41" t="n">
+        <v>10</v>
+      </c>
+      <c r="T41" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U41" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V41" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W41" t="inlineStr">
+        <is>
+          <t>Vemdalen</t>
+        </is>
+      </c>
+      <c r="Y41" t="inlineStr">
+        <is>
+          <t>2025-05-08</t>
+        </is>
+      </c>
+      <c r="AA41" t="inlineStr">
+        <is>
+          <t>2025-05-08</t>
+        </is>
+      </c>
+      <c r="AD41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT41" t="inlineStr"/>
+      <c r="AW41" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX41" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY41" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>124880338</v>
+      </c>
+      <c r="B42" t="n">
+        <v>91030</v>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E42" t="n">
+        <v>5432</v>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>Granticka</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>Porodaedalea chrysoloma</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr"/>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>Lill-tjärnvallen sö, Hjd</t>
+        </is>
+      </c>
+      <c r="Q42" t="n">
+        <v>433585</v>
+      </c>
+      <c r="R42" t="n">
+        <v>6935882</v>
+      </c>
+      <c r="S42" t="n">
+        <v>10</v>
+      </c>
+      <c r="T42" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U42" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V42" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W42" t="inlineStr">
+        <is>
+          <t>Vemdalen</t>
+        </is>
+      </c>
+      <c r="Y42" t="inlineStr">
+        <is>
+          <t>2025-05-08</t>
+        </is>
+      </c>
+      <c r="AA42" t="inlineStr">
+        <is>
+          <t>2025-05-08</t>
+        </is>
+      </c>
+      <c r="AD42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT42" t="inlineStr"/>
+      <c r="AW42" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX42" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY42" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>124880371</v>
+      </c>
+      <c r="B43" t="n">
+        <v>78810</v>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E43" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr"/>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>Lill-tjärnvallen sö, Hjd</t>
+        </is>
+      </c>
+      <c r="Q43" t="n">
+        <v>434167</v>
+      </c>
+      <c r="R43" t="n">
+        <v>6936378</v>
+      </c>
+      <c r="S43" t="n">
+        <v>10</v>
+      </c>
+      <c r="T43" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U43" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V43" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W43" t="inlineStr">
+        <is>
+          <t>Vemdalen</t>
+        </is>
+      </c>
+      <c r="Y43" t="inlineStr">
+        <is>
+          <t>2025-05-08</t>
+        </is>
+      </c>
+      <c r="AA43" t="inlineStr">
+        <is>
+          <t>2025-05-08</t>
+        </is>
+      </c>
+      <c r="AC43" t="inlineStr">
+        <is>
+          <t>Mycket rikligt</t>
+        </is>
+      </c>
+      <c r="AD43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT43" t="inlineStr"/>
+      <c r="AW43" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX43" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY43" t="inlineStr"/>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>124880296</v>
+      </c>
+      <c r="B44" t="n">
+        <v>57513</v>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E44" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr"/>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>Lill-tjärnvallen sö, Hjd</t>
+        </is>
+      </c>
+      <c r="Q44" t="n">
+        <v>434019</v>
+      </c>
+      <c r="R44" t="n">
+        <v>6936070</v>
+      </c>
+      <c r="S44" t="n">
+        <v>10</v>
+      </c>
+      <c r="T44" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U44" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V44" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W44" t="inlineStr">
+        <is>
+          <t>Vemdalen</t>
+        </is>
+      </c>
+      <c r="Y44" t="inlineStr">
+        <is>
+          <t>2025-05-08</t>
+        </is>
+      </c>
+      <c r="AA44" t="inlineStr">
+        <is>
+          <t>2025-05-08</t>
+        </is>
+      </c>
+      <c r="AC44" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
+        </is>
+      </c>
+      <c r="AD44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT44" t="inlineStr"/>
+      <c r="AW44" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX44" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY44" t="inlineStr"/>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>124880329</v>
+      </c>
+      <c r="B45" t="n">
+        <v>91030</v>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E45" t="n">
+        <v>5432</v>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>Granticka</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>Porodaedalea chrysoloma</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr"/>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>Lill-tjärnvallen sö, Hjd</t>
+        </is>
+      </c>
+      <c r="Q45" t="n">
+        <v>433106</v>
+      </c>
+      <c r="R45" t="n">
+        <v>6935174</v>
+      </c>
+      <c r="S45" t="n">
+        <v>10</v>
+      </c>
+      <c r="T45" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U45" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V45" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W45" t="inlineStr">
+        <is>
+          <t>Vemdalen</t>
+        </is>
+      </c>
+      <c r="Y45" t="inlineStr">
+        <is>
+          <t>2025-05-08</t>
+        </is>
+      </c>
+      <c r="AA45" t="inlineStr">
+        <is>
+          <t>2025-05-08</t>
+        </is>
+      </c>
+      <c r="AD45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT45" t="inlineStr"/>
+      <c r="AW45" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX45" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY45" t="inlineStr"/>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>124880295</v>
+      </c>
+      <c r="B46" t="n">
+        <v>57513</v>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E46" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr"/>
+      <c r="P46" t="inlineStr">
+        <is>
+          <t>Lill-tjärnvallen sö, Hjd</t>
+        </is>
+      </c>
+      <c r="Q46" t="n">
+        <v>433952</v>
+      </c>
+      <c r="R46" t="n">
+        <v>6936043</v>
+      </c>
+      <c r="S46" t="n">
+        <v>10</v>
+      </c>
+      <c r="T46" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U46" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V46" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W46" t="inlineStr">
+        <is>
+          <t>Vemdalen</t>
+        </is>
+      </c>
+      <c r="Y46" t="inlineStr">
+        <is>
+          <t>2025-05-08</t>
+        </is>
+      </c>
+      <c r="AA46" t="inlineStr">
+        <is>
+          <t>2025-05-08</t>
+        </is>
+      </c>
+      <c r="AC46" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
+        </is>
+      </c>
+      <c r="AD46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT46" t="inlineStr"/>
+      <c r="AW46" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX46" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY46" t="inlineStr"/>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>124880317</v>
+      </c>
+      <c r="B47" t="n">
+        <v>57513</v>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E47" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr"/>
+      <c r="P47" t="inlineStr">
+        <is>
+          <t>Lill-tjärnvallen sö, Hjd</t>
+        </is>
+      </c>
+      <c r="Q47" t="n">
+        <v>434538</v>
+      </c>
+      <c r="R47" t="n">
+        <v>6936895</v>
+      </c>
+      <c r="S47" t="n">
+        <v>10</v>
+      </c>
+      <c r="T47" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U47" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V47" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W47" t="inlineStr">
+        <is>
+          <t>Vemdalen</t>
+        </is>
+      </c>
+      <c r="Y47" t="inlineStr">
+        <is>
+          <t>2025-05-08</t>
+        </is>
+      </c>
+      <c r="AA47" t="inlineStr">
+        <is>
+          <t>2025-05-08</t>
+        </is>
+      </c>
+      <c r="AC47" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
+        </is>
+      </c>
+      <c r="AD47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT47" t="inlineStr"/>
+      <c r="AW47" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX47" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY47" t="inlineStr"/>
+    </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>124880372</v>
+      </c>
+      <c r="B48" t="n">
+        <v>78810</v>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E48" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr"/>
+      <c r="P48" t="inlineStr">
+        <is>
+          <t>Lill-tjärnvallen sö, Hjd</t>
+        </is>
+      </c>
+      <c r="Q48" t="n">
+        <v>434443</v>
+      </c>
+      <c r="R48" t="n">
+        <v>6936839</v>
+      </c>
+      <c r="S48" t="n">
+        <v>10</v>
+      </c>
+      <c r="T48" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U48" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V48" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W48" t="inlineStr">
+        <is>
+          <t>Vemdalen</t>
+        </is>
+      </c>
+      <c r="Y48" t="inlineStr">
+        <is>
+          <t>2025-05-08</t>
+        </is>
+      </c>
+      <c r="AA48" t="inlineStr">
+        <is>
+          <t>2025-05-08</t>
+        </is>
+      </c>
+      <c r="AC48" t="inlineStr">
+        <is>
+          <t>Mycket rikligt</t>
+        </is>
+      </c>
+      <c r="AD48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT48" t="inlineStr"/>
+      <c r="AW48" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX48" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY48" t="inlineStr"/>
+    </row>
+    <row r="49">
+      <c r="A49" t="n">
+        <v>124880319</v>
+      </c>
+      <c r="B49" t="n">
+        <v>57513</v>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E49" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr"/>
+      <c r="P49" t="inlineStr">
+        <is>
+          <t>Lill-tjärnvallen sö, Hjd</t>
+        </is>
+      </c>
+      <c r="Q49" t="n">
+        <v>434789</v>
+      </c>
+      <c r="R49" t="n">
+        <v>6936947</v>
+      </c>
+      <c r="S49" t="n">
+        <v>10</v>
+      </c>
+      <c r="T49" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U49" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V49" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W49" t="inlineStr">
+        <is>
+          <t>Vemdalen</t>
+        </is>
+      </c>
+      <c r="Y49" t="inlineStr">
+        <is>
+          <t>2025-05-08</t>
+        </is>
+      </c>
+      <c r="AA49" t="inlineStr">
+        <is>
+          <t>2025-05-08</t>
+        </is>
+      </c>
+      <c r="AC49" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
+        </is>
+      </c>
+      <c r="AD49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT49" t="inlineStr"/>
+      <c r="AW49" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX49" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY49" t="inlineStr"/>
+    </row>
+    <row r="50">
+      <c r="A50" t="n">
+        <v>124880346</v>
+      </c>
+      <c r="B50" t="n">
+        <v>91030</v>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E50" t="n">
+        <v>5432</v>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>Granticka</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>Porodaedalea chrysoloma</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr"/>
+      <c r="P50" t="inlineStr">
+        <is>
+          <t>Lill-tjärnvallen sö, Hjd</t>
+        </is>
+      </c>
+      <c r="Q50" t="n">
+        <v>434113</v>
+      </c>
+      <c r="R50" t="n">
+        <v>6936148</v>
+      </c>
+      <c r="S50" t="n">
+        <v>10</v>
+      </c>
+      <c r="T50" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U50" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V50" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W50" t="inlineStr">
+        <is>
+          <t>Vemdalen</t>
+        </is>
+      </c>
+      <c r="Y50" t="inlineStr">
+        <is>
+          <t>2025-05-08</t>
+        </is>
+      </c>
+      <c r="AA50" t="inlineStr">
+        <is>
+          <t>2025-05-08</t>
+        </is>
+      </c>
+      <c r="AD50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT50" t="inlineStr"/>
+      <c r="AW50" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX50" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY50" t="inlineStr"/>
+    </row>
+    <row r="51">
+      <c r="A51" t="n">
+        <v>124880304</v>
+      </c>
+      <c r="B51" t="n">
+        <v>57513</v>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E51" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr"/>
+      <c r="P51" t="inlineStr">
+        <is>
+          <t>Lill-tjärnvallen sö, Hjd</t>
+        </is>
+      </c>
+      <c r="Q51" t="n">
+        <v>434155</v>
+      </c>
+      <c r="R51" t="n">
+        <v>6936279</v>
+      </c>
+      <c r="S51" t="n">
+        <v>10</v>
+      </c>
+      <c r="T51" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U51" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V51" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W51" t="inlineStr">
+        <is>
+          <t>Vemdalen</t>
+        </is>
+      </c>
+      <c r="Y51" t="inlineStr">
+        <is>
+          <t>2025-05-08</t>
+        </is>
+      </c>
+      <c r="AA51" t="inlineStr">
+        <is>
+          <t>2025-05-08</t>
+        </is>
+      </c>
+      <c r="AC51" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
+        </is>
+      </c>
+      <c r="AD51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT51" t="inlineStr"/>
+      <c r="AW51" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX51" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY51" t="inlineStr"/>
+    </row>
+    <row r="52">
+      <c r="A52" t="n">
+        <v>124880331</v>
+      </c>
+      <c r="B52" t="n">
+        <v>91030</v>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E52" t="n">
+        <v>5432</v>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>Granticka</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>Porodaedalea chrysoloma</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr"/>
+      <c r="P52" t="inlineStr">
+        <is>
+          <t>Lill-tjärnvallen sö, Hjd</t>
+        </is>
+      </c>
+      <c r="Q52" t="n">
+        <v>433193</v>
+      </c>
+      <c r="R52" t="n">
+        <v>6935352</v>
+      </c>
+      <c r="S52" t="n">
+        <v>10</v>
+      </c>
+      <c r="T52" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U52" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V52" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W52" t="inlineStr">
+        <is>
+          <t>Vemdalen</t>
+        </is>
+      </c>
+      <c r="Y52" t="inlineStr">
+        <is>
+          <t>2025-05-08</t>
+        </is>
+      </c>
+      <c r="AA52" t="inlineStr">
+        <is>
+          <t>2025-05-08</t>
+        </is>
+      </c>
+      <c r="AD52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT52" t="inlineStr"/>
+      <c r="AW52" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX52" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY52" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 9618-2025 artfynd.xlsx
+++ b/artfynd/A 9618-2025 artfynd.xlsx
@@ -1026,7 +1026,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124880332</v>
+        <v>124880346</v>
       </c>
       <c r="B5" t="n">
         <v>91030</v>
@@ -1066,10 +1066,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>433197</v>
+        <v>434113</v>
       </c>
       <c r="R5" t="n">
-        <v>6935385</v>
+        <v>6936148</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1128,10 +1128,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124880299</v>
+        <v>124880331</v>
       </c>
       <c r="B6" t="n">
-        <v>57513</v>
+        <v>91030</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1144,21 +1144,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1168,10 +1168,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>434112</v>
+        <v>433193</v>
       </c>
       <c r="R6" t="n">
-        <v>6936130</v>
+        <v>6935352</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1204,11 +1204,6 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-05-08</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1235,10 +1230,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124880315</v>
+        <v>124880338</v>
       </c>
       <c r="B7" t="n">
-        <v>57513</v>
+        <v>91030</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1251,21 +1246,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1275,10 +1270,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>434466</v>
+        <v>433585</v>
       </c>
       <c r="R7" t="n">
-        <v>6936862</v>
+        <v>6935882</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1311,11 +1306,6 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-05-08</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1449,10 +1439,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124880324</v>
+        <v>124880295</v>
       </c>
       <c r="B9" t="n">
-        <v>91008</v>
+        <v>57513</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1465,21 +1455,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1108</v>
+        <v>100109</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1489,10 +1479,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>433261</v>
+        <v>433952</v>
       </c>
       <c r="R9" t="n">
-        <v>6935504</v>
+        <v>6936043</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1525,6 +1515,11 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-05-08</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1551,10 +1546,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124880337</v>
+        <v>124880286</v>
       </c>
       <c r="B10" t="n">
-        <v>91030</v>
+        <v>57513</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1567,21 +1562,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1591,10 +1586,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>433534</v>
+        <v>433434</v>
       </c>
       <c r="R10" t="n">
-        <v>6935858</v>
+        <v>6935749</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1627,6 +1622,11 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-05-08</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1653,7 +1653,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124880345</v>
+        <v>124880344</v>
       </c>
       <c r="B11" t="n">
         <v>91030</v>
@@ -1693,10 +1693,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>434057</v>
+        <v>434028</v>
       </c>
       <c r="R11" t="n">
-        <v>6936091</v>
+        <v>6936084</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1755,10 +1755,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>124880237</v>
+        <v>124880275</v>
       </c>
       <c r="B12" t="n">
-        <v>91012</v>
+        <v>57513</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1771,21 +1771,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1795,10 +1795,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>433636</v>
+        <v>432954</v>
       </c>
       <c r="R12" t="n">
-        <v>6935914</v>
+        <v>6934982</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1831,6 +1831,11 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-05-08</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1857,10 +1862,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>124880350</v>
+        <v>124880310</v>
       </c>
       <c r="B13" t="n">
-        <v>91030</v>
+        <v>57513</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1873,21 +1878,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1897,10 +1902,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>434118</v>
+        <v>434385</v>
       </c>
       <c r="R13" t="n">
-        <v>6936187</v>
+        <v>6936814</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1933,6 +1938,11 @@
       <c r="AA13" t="inlineStr">
         <is>
           <t>2025-05-08</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1959,10 +1969,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>124880369</v>
+        <v>124880237</v>
       </c>
       <c r="B14" t="n">
-        <v>78810</v>
+        <v>91012</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1975,21 +1985,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1999,10 +2009,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>434091</v>
+        <v>433636</v>
       </c>
       <c r="R14" t="n">
-        <v>6936122</v>
+        <v>6935914</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2035,11 +2045,6 @@
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-05-08</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>Mycket rikligt</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2066,7 +2071,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>124880358</v>
+        <v>124880372</v>
       </c>
       <c r="B15" t="n">
         <v>78810</v>
@@ -2106,10 +2111,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>433076</v>
+        <v>434443</v>
       </c>
       <c r="R15" t="n">
-        <v>6935108</v>
+        <v>6936839</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2146,7 +2151,7 @@
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>Rikligt</t>
+          <t>Mycket rikligt</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2173,7 +2178,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>124880340</v>
+        <v>124880350</v>
       </c>
       <c r="B16" t="n">
         <v>91030</v>
@@ -2213,10 +2218,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>433661</v>
+        <v>434118</v>
       </c>
       <c r="R16" t="n">
-        <v>6935941</v>
+        <v>6936187</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2275,10 +2280,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>124880305</v>
+        <v>124880373</v>
       </c>
       <c r="B17" t="n">
-        <v>57513</v>
+        <v>78810</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2291,21 +2296,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2315,10 +2320,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>434128</v>
+        <v>434482</v>
       </c>
       <c r="R17" t="n">
-        <v>6936677</v>
+        <v>6936858</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2355,7 +2360,7 @@
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2382,10 +2387,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>124880367</v>
+        <v>124880340</v>
       </c>
       <c r="B18" t="n">
-        <v>78810</v>
+        <v>91030</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2398,21 +2403,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2422,10 +2427,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>433984</v>
+        <v>433661</v>
       </c>
       <c r="R18" t="n">
-        <v>6936073</v>
+        <v>6935941</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2458,11 +2463,6 @@
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-05-08</t>
-        </is>
-      </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>Mycket rikligt</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2489,7 +2489,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>124880275</v>
+        <v>124880299</v>
       </c>
       <c r="B19" t="n">
         <v>57513</v>
@@ -2529,10 +2529,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>432954</v>
+        <v>434112</v>
       </c>
       <c r="R19" t="n">
-        <v>6934982</v>
+        <v>6936130</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2596,10 +2596,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>124880326</v>
+        <v>124880318</v>
       </c>
       <c r="B20" t="n">
-        <v>91008</v>
+        <v>57513</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2612,21 +2612,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>1108</v>
+        <v>100109</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2636,10 +2636,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>434175</v>
+        <v>434664</v>
       </c>
       <c r="R20" t="n">
-        <v>6936309</v>
+        <v>6936929</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2672,6 +2672,11 @@
       <c r="AA20" t="inlineStr">
         <is>
           <t>2025-05-08</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2698,10 +2703,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>124880314</v>
+        <v>124880333</v>
       </c>
       <c r="B21" t="n">
-        <v>57513</v>
+        <v>91030</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2714,21 +2719,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2738,10 +2743,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>434484</v>
+        <v>433376</v>
       </c>
       <c r="R21" t="n">
-        <v>6936850</v>
+        <v>6935725</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2774,11 +2779,6 @@
       <c r="AA21" t="inlineStr">
         <is>
           <t>2025-05-08</t>
-        </is>
-      </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2805,10 +2805,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>124880360</v>
+        <v>124880324</v>
       </c>
       <c r="B22" t="n">
-        <v>78810</v>
+        <v>91008</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2821,21 +2821,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6425</v>
+        <v>1108</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2845,10 +2845,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>433248</v>
+        <v>433261</v>
       </c>
       <c r="R22" t="n">
-        <v>6935491</v>
+        <v>6935504</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2881,11 +2881,6 @@
       <c r="AA22" t="inlineStr">
         <is>
           <t>2025-05-08</t>
-        </is>
-      </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>Mycket rikligt</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2912,10 +2907,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>124880373</v>
+        <v>124880317</v>
       </c>
       <c r="B23" t="n">
-        <v>78810</v>
+        <v>57513</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2928,21 +2923,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2952,10 +2947,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>434482</v>
+        <v>434538</v>
       </c>
       <c r="R23" t="n">
-        <v>6936858</v>
+        <v>6936895</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2992,7 +2987,7 @@
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>Rikligt</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3126,10 +3121,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>124880344</v>
+        <v>124880326</v>
       </c>
       <c r="B25" t="n">
-        <v>91030</v>
+        <v>91008</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3142,21 +3137,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>5432</v>
+        <v>1108</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3166,10 +3161,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>434028</v>
+        <v>434175</v>
       </c>
       <c r="R25" t="n">
-        <v>6936084</v>
+        <v>6936309</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3228,7 +3223,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>124880310</v>
+        <v>124880314</v>
       </c>
       <c r="B26" t="n">
         <v>57513</v>
@@ -3268,10 +3263,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>434385</v>
+        <v>434484</v>
       </c>
       <c r="R26" t="n">
-        <v>6936814</v>
+        <v>6936850</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3335,10 +3330,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>124880364</v>
+        <v>124880316</v>
       </c>
       <c r="B27" t="n">
-        <v>78810</v>
+        <v>57513</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3351,21 +3346,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3375,10 +3370,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>433682</v>
+        <v>434532</v>
       </c>
       <c r="R27" t="n">
-        <v>6935955</v>
+        <v>6936893</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3415,7 +3410,7 @@
       </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>Mycket rikligt</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3442,7 +3437,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>124880288</v>
+        <v>124880278</v>
       </c>
       <c r="B28" t="n">
         <v>57513</v>
@@ -3482,10 +3477,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>433505</v>
+        <v>433331</v>
       </c>
       <c r="R28" t="n">
-        <v>6935809</v>
+        <v>6935597</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3549,10 +3544,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>124880316</v>
+        <v>124880365</v>
       </c>
       <c r="B29" t="n">
-        <v>57513</v>
+        <v>78810</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3565,21 +3560,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3589,10 +3584,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>434532</v>
+        <v>433755</v>
       </c>
       <c r="R29" t="n">
-        <v>6936893</v>
+        <v>6935995</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3629,7 +3624,7 @@
       </c>
       <c r="AC29" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3656,7 +3651,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>124880353</v>
+        <v>124880343</v>
       </c>
       <c r="B30" t="n">
         <v>91030</v>
@@ -3696,10 +3691,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>434173</v>
+        <v>433952</v>
       </c>
       <c r="R30" t="n">
-        <v>6936342</v>
+        <v>6936054</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3758,10 +3753,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>124880361</v>
+        <v>124880304</v>
       </c>
       <c r="B31" t="n">
-        <v>78810</v>
+        <v>57513</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3774,21 +3769,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3798,10 +3793,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>433311</v>
+        <v>434155</v>
       </c>
       <c r="R31" t="n">
-        <v>6935592</v>
+        <v>6936279</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3838,7 +3833,7 @@
       </c>
       <c r="AC31" t="inlineStr">
         <is>
-          <t>Rikligt</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3865,10 +3860,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>124880359</v>
+        <v>124880313</v>
       </c>
       <c r="B32" t="n">
-        <v>78810</v>
+        <v>57513</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3881,21 +3876,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3905,10 +3900,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>433093</v>
+        <v>434447</v>
       </c>
       <c r="R32" t="n">
-        <v>6935150</v>
+        <v>6936828</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3945,7 +3940,7 @@
       </c>
       <c r="AC32" t="inlineStr">
         <is>
-          <t>Rikligt</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3972,10 +3967,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>124880333</v>
+        <v>124880361</v>
       </c>
       <c r="B33" t="n">
-        <v>91030</v>
+        <v>78810</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -3988,21 +3983,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4012,10 +4007,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>433376</v>
+        <v>433311</v>
       </c>
       <c r="R33" t="n">
-        <v>6935725</v>
+        <v>6935592</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4048,6 +4043,11 @@
       <c r="AA33" t="inlineStr">
         <is>
           <t>2025-05-08</t>
+        </is>
+      </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4074,7 +4074,7 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>124880286</v>
+        <v>124880283</v>
       </c>
       <c r="B34" t="n">
         <v>57513</v>
@@ -4114,10 +4114,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>433434</v>
+        <v>433376</v>
       </c>
       <c r="R34" t="n">
-        <v>6935749</v>
+        <v>6935695</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4154,7 +4154,7 @@
       </c>
       <c r="AC34" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4181,7 +4181,7 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>124880313</v>
+        <v>124880319</v>
       </c>
       <c r="B35" t="n">
         <v>57513</v>
@@ -4221,10 +4221,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>434447</v>
+        <v>434789</v>
       </c>
       <c r="R35" t="n">
-        <v>6936828</v>
+        <v>6936947</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4261,7 +4261,7 @@
       </c>
       <c r="AC35" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4288,7 +4288,7 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>124880365</v>
+        <v>124880360</v>
       </c>
       <c r="B36" t="n">
         <v>78810</v>
@@ -4328,10 +4328,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>433755</v>
+        <v>433248</v>
       </c>
       <c r="R36" t="n">
-        <v>6935995</v>
+        <v>6935491</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4368,7 +4368,7 @@
       </c>
       <c r="AC36" t="inlineStr">
         <is>
-          <t>Rikligt</t>
+          <t>Mycket rikligt</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4395,10 +4395,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>124880343</v>
+        <v>124880296</v>
       </c>
       <c r="B37" t="n">
-        <v>91030</v>
+        <v>57513</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4411,21 +4411,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4435,10 +4435,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>433952</v>
+        <v>434019</v>
       </c>
       <c r="R37" t="n">
-        <v>6936054</v>
+        <v>6936070</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4471,6 +4471,11 @@
       <c r="AA37" t="inlineStr">
         <is>
           <t>2025-05-08</t>
+        </is>
+      </c>
+      <c r="AC37" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4497,10 +4502,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>124880283</v>
+        <v>124880367</v>
       </c>
       <c r="B38" t="n">
-        <v>57513</v>
+        <v>78810</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4513,21 +4518,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4537,10 +4542,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>433376</v>
+        <v>433984</v>
       </c>
       <c r="R38" t="n">
-        <v>6935695</v>
+        <v>6936073</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4577,7 +4582,7 @@
       </c>
       <c r="AC38" t="inlineStr">
         <is>
-          <t>Ringhack färska</t>
+          <t>Mycket rikligt</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4604,10 +4609,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>124880318</v>
+        <v>124880358</v>
       </c>
       <c r="B39" t="n">
-        <v>57513</v>
+        <v>78810</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4620,21 +4625,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4644,10 +4649,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>434664</v>
+        <v>433076</v>
       </c>
       <c r="R39" t="n">
-        <v>6936929</v>
+        <v>6935108</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4684,7 +4689,7 @@
       </c>
       <c r="AC39" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4711,10 +4716,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>124880278</v>
+        <v>124880355</v>
       </c>
       <c r="B40" t="n">
-        <v>57513</v>
+        <v>91030</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4727,21 +4732,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4751,10 +4756,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>433331</v>
+        <v>434478</v>
       </c>
       <c r="R40" t="n">
-        <v>6935597</v>
+        <v>6936874</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4787,11 +4792,6 @@
       <c r="AA40" t="inlineStr">
         <is>
           <t>2025-05-08</t>
-        </is>
-      </c>
-      <c r="AC40" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4818,10 +4818,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>124880355</v>
+        <v>124880288</v>
       </c>
       <c r="B41" t="n">
-        <v>91030</v>
+        <v>57513</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -4834,21 +4834,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4858,10 +4858,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>434478</v>
+        <v>433505</v>
       </c>
       <c r="R41" t="n">
-        <v>6936874</v>
+        <v>6935809</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4894,6 +4894,11 @@
       <c r="AA41" t="inlineStr">
         <is>
           <t>2025-05-08</t>
+        </is>
+      </c>
+      <c r="AC41" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4920,10 +4925,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>124880338</v>
+        <v>124880315</v>
       </c>
       <c r="B42" t="n">
-        <v>91030</v>
+        <v>57513</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -4936,21 +4941,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4960,10 +4965,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>433585</v>
+        <v>434466</v>
       </c>
       <c r="R42" t="n">
-        <v>6935882</v>
+        <v>6936862</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4996,6 +5001,11 @@
       <c r="AA42" t="inlineStr">
         <is>
           <t>2025-05-08</t>
+        </is>
+      </c>
+      <c r="AC42" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5022,7 +5032,7 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>124880371</v>
+        <v>124880359</v>
       </c>
       <c r="B43" t="n">
         <v>78810</v>
@@ -5062,10 +5072,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>434167</v>
+        <v>433093</v>
       </c>
       <c r="R43" t="n">
-        <v>6936378</v>
+        <v>6935150</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5102,7 +5112,7 @@
       </c>
       <c r="AC43" t="inlineStr">
         <is>
-          <t>Mycket rikligt</t>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5129,10 +5139,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>124880296</v>
+        <v>124880371</v>
       </c>
       <c r="B44" t="n">
-        <v>57513</v>
+        <v>78810</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5145,21 +5155,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5169,10 +5179,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>434019</v>
+        <v>434167</v>
       </c>
       <c r="R44" t="n">
-        <v>6936070</v>
+        <v>6936378</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5209,7 +5219,7 @@
       </c>
       <c r="AC44" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Mycket rikligt</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5236,7 +5246,7 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>124880329</v>
+        <v>124880332</v>
       </c>
       <c r="B45" t="n">
         <v>91030</v>
@@ -5276,10 +5286,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>433106</v>
+        <v>433197</v>
       </c>
       <c r="R45" t="n">
-        <v>6935174</v>
+        <v>6935385</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5338,7 +5348,7 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>124880295</v>
+        <v>124880305</v>
       </c>
       <c r="B46" t="n">
         <v>57513</v>
@@ -5378,10 +5388,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>433952</v>
+        <v>434128</v>
       </c>
       <c r="R46" t="n">
-        <v>6936043</v>
+        <v>6936677</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5445,10 +5455,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>124880317</v>
+        <v>124880369</v>
       </c>
       <c r="B47" t="n">
-        <v>57513</v>
+        <v>78810</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5461,21 +5471,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5485,10 +5495,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>434538</v>
+        <v>434091</v>
       </c>
       <c r="R47" t="n">
-        <v>6936895</v>
+        <v>6936122</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5525,7 +5535,7 @@
       </c>
       <c r="AC47" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Mycket rikligt</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5552,10 +5562,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>124880372</v>
+        <v>124880353</v>
       </c>
       <c r="B48" t="n">
-        <v>78810</v>
+        <v>91030</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5568,21 +5578,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5592,10 +5602,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>434443</v>
+        <v>434173</v>
       </c>
       <c r="R48" t="n">
-        <v>6936839</v>
+        <v>6936342</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5628,11 +5638,6 @@
       <c r="AA48" t="inlineStr">
         <is>
           <t>2025-05-08</t>
-        </is>
-      </c>
-      <c r="AC48" t="inlineStr">
-        <is>
-          <t>Mycket rikligt</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5659,10 +5664,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>124880319</v>
+        <v>124880345</v>
       </c>
       <c r="B49" t="n">
-        <v>57513</v>
+        <v>91030</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -5675,21 +5680,21 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5699,10 +5704,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>434789</v>
+        <v>434057</v>
       </c>
       <c r="R49" t="n">
-        <v>6936947</v>
+        <v>6936091</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5735,11 +5740,6 @@
       <c r="AA49" t="inlineStr">
         <is>
           <t>2025-05-08</t>
-        </is>
-      </c>
-      <c r="AC49" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5766,10 +5766,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>124880346</v>
+        <v>124880364</v>
       </c>
       <c r="B50" t="n">
-        <v>91030</v>
+        <v>78810</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -5782,21 +5782,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5806,10 +5806,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>434113</v>
+        <v>433682</v>
       </c>
       <c r="R50" t="n">
-        <v>6936148</v>
+        <v>6935955</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5842,6 +5842,11 @@
       <c r="AA50" t="inlineStr">
         <is>
           <t>2025-05-08</t>
+        </is>
+      </c>
+      <c r="AC50" t="inlineStr">
+        <is>
+          <t>Mycket rikligt</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -5868,10 +5873,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>124880304</v>
+        <v>124880329</v>
       </c>
       <c r="B51" t="n">
-        <v>57513</v>
+        <v>91030</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -5884,21 +5889,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5908,10 +5913,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>434155</v>
+        <v>433106</v>
       </c>
       <c r="R51" t="n">
-        <v>6936279</v>
+        <v>6935174</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5944,11 +5949,6 @@
       <c r="AA51" t="inlineStr">
         <is>
           <t>2025-05-08</t>
-        </is>
-      </c>
-      <c r="AC51" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -5975,7 +5975,7 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>124880331</v>
+        <v>124880337</v>
       </c>
       <c r="B52" t="n">
         <v>91030</v>
@@ -6015,10 +6015,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>433193</v>
+        <v>433534</v>
       </c>
       <c r="R52" t="n">
-        <v>6935352</v>
+        <v>6935858</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>

--- a/artfynd/A 9618-2025 artfynd.xlsx
+++ b/artfynd/A 9618-2025 artfynd.xlsx
@@ -2387,10 +2387,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>124880340</v>
+        <v>124880299</v>
       </c>
       <c r="B18" t="n">
-        <v>91030</v>
+        <v>57513</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2403,21 +2403,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2427,10 +2427,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>433661</v>
+        <v>434112</v>
       </c>
       <c r="R18" t="n">
-        <v>6935941</v>
+        <v>6936130</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2463,6 +2463,11 @@
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-05-08</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2489,7 +2494,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>124880299</v>
+        <v>124880318</v>
       </c>
       <c r="B19" t="n">
         <v>57513</v>
@@ -2529,10 +2534,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>434112</v>
+        <v>434664</v>
       </c>
       <c r="R19" t="n">
-        <v>6936130</v>
+        <v>6936929</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2596,10 +2601,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>124880318</v>
+        <v>124880340</v>
       </c>
       <c r="B20" t="n">
-        <v>57513</v>
+        <v>91030</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2612,21 +2617,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2636,10 +2641,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>434664</v>
+        <v>433661</v>
       </c>
       <c r="R20" t="n">
-        <v>6936929</v>
+        <v>6935941</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2672,11 +2677,6 @@
       <c r="AA20" t="inlineStr">
         <is>
           <t>2025-05-08</t>
-        </is>
-      </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2703,10 +2703,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>124880333</v>
+        <v>124880324</v>
       </c>
       <c r="B21" t="n">
-        <v>91030</v>
+        <v>91008</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2719,21 +2719,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>5432</v>
+        <v>1108</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2743,10 +2743,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>433376</v>
+        <v>433261</v>
       </c>
       <c r="R21" t="n">
-        <v>6935725</v>
+        <v>6935504</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2805,10 +2805,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>124880324</v>
+        <v>124880333</v>
       </c>
       <c r="B22" t="n">
-        <v>91008</v>
+        <v>91030</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2821,21 +2821,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>1108</v>
+        <v>5432</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2845,10 +2845,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>433261</v>
+        <v>433376</v>
       </c>
       <c r="R22" t="n">
-        <v>6935504</v>
+        <v>6935725</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>

--- a/artfynd/A 9618-2025 artfynd.xlsx
+++ b/artfynd/A 9618-2025 artfynd.xlsx
@@ -1755,10 +1755,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>124880275</v>
+        <v>124880237</v>
       </c>
       <c r="B12" t="n">
-        <v>57513</v>
+        <v>91012</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1771,21 +1771,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1795,10 +1795,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>432954</v>
+        <v>433636</v>
       </c>
       <c r="R12" t="n">
-        <v>6934982</v>
+        <v>6935914</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1831,11 +1831,6 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-05-08</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1862,7 +1857,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>124880310</v>
+        <v>124880275</v>
       </c>
       <c r="B13" t="n">
         <v>57513</v>
@@ -1902,10 +1897,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>434385</v>
+        <v>432954</v>
       </c>
       <c r="R13" t="n">
-        <v>6936814</v>
+        <v>6934982</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1969,10 +1964,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>124880237</v>
+        <v>124880310</v>
       </c>
       <c r="B14" t="n">
-        <v>91012</v>
+        <v>57513</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1985,21 +1980,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2009,10 +2004,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>433636</v>
+        <v>434385</v>
       </c>
       <c r="R14" t="n">
-        <v>6935914</v>
+        <v>6936814</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2045,6 +2040,11 @@
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-05-08</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2387,7 +2387,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>124880299</v>
+        <v>124880318</v>
       </c>
       <c r="B18" t="n">
         <v>57513</v>
@@ -2427,10 +2427,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>434112</v>
+        <v>434664</v>
       </c>
       <c r="R18" t="n">
-        <v>6936130</v>
+        <v>6936929</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2494,10 +2494,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>124880318</v>
+        <v>124880340</v>
       </c>
       <c r="B19" t="n">
-        <v>57513</v>
+        <v>91030</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2510,21 +2510,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2534,10 +2534,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>434664</v>
+        <v>433661</v>
       </c>
       <c r="R19" t="n">
-        <v>6936929</v>
+        <v>6935941</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2570,11 +2570,6 @@
       <c r="AA19" t="inlineStr">
         <is>
           <t>2025-05-08</t>
-        </is>
-      </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2601,10 +2596,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>124880340</v>
+        <v>124880299</v>
       </c>
       <c r="B20" t="n">
-        <v>91030</v>
+        <v>57513</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2617,21 +2612,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2641,10 +2636,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>433661</v>
+        <v>434112</v>
       </c>
       <c r="R20" t="n">
-        <v>6935941</v>
+        <v>6936130</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2677,6 +2672,11 @@
       <c r="AA20" t="inlineStr">
         <is>
           <t>2025-05-08</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2703,10 +2703,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>124880324</v>
+        <v>124880333</v>
       </c>
       <c r="B21" t="n">
-        <v>91008</v>
+        <v>91030</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2719,21 +2719,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>1108</v>
+        <v>5432</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2743,10 +2743,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>433261</v>
+        <v>433376</v>
       </c>
       <c r="R21" t="n">
-        <v>6935504</v>
+        <v>6935725</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2805,10 +2805,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>124880333</v>
+        <v>124880324</v>
       </c>
       <c r="B22" t="n">
-        <v>91030</v>
+        <v>91008</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2821,21 +2821,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>5432</v>
+        <v>1108</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2845,10 +2845,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>433376</v>
+        <v>433261</v>
       </c>
       <c r="R22" t="n">
-        <v>6935725</v>
+        <v>6935504</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>

--- a/artfynd/A 9618-2025 artfynd.xlsx
+++ b/artfynd/A 9618-2025 artfynd.xlsx
@@ -1026,7 +1026,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124880346</v>
+        <v>124880331</v>
       </c>
       <c r="B5" t="n">
         <v>91030</v>
@@ -1066,10 +1066,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>434113</v>
+        <v>433193</v>
       </c>
       <c r="R5" t="n">
-        <v>6936148</v>
+        <v>6935352</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1128,10 +1128,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124880331</v>
+        <v>124880303</v>
       </c>
       <c r="B6" t="n">
-        <v>91030</v>
+        <v>57513</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1144,21 +1144,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1168,10 +1168,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>433193</v>
+        <v>434113</v>
       </c>
       <c r="R6" t="n">
-        <v>6935352</v>
+        <v>6936181</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1204,6 +1204,11 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-05-08</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1230,7 +1235,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124880338</v>
+        <v>124880337</v>
       </c>
       <c r="B7" t="n">
         <v>91030</v>
@@ -1270,10 +1275,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>433585</v>
+        <v>433534</v>
       </c>
       <c r="R7" t="n">
-        <v>6935882</v>
+        <v>6935858</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1332,10 +1337,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124880303</v>
+        <v>124880367</v>
       </c>
       <c r="B8" t="n">
-        <v>57513</v>
+        <v>78810</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1348,21 +1353,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1372,10 +1377,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>434113</v>
+        <v>433984</v>
       </c>
       <c r="R8" t="n">
-        <v>6936181</v>
+        <v>6936073</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1412,7 +1417,7 @@
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Mycket rikligt</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1439,10 +1444,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124880295</v>
+        <v>124880324</v>
       </c>
       <c r="B9" t="n">
-        <v>57513</v>
+        <v>91008</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1455,21 +1460,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100109</v>
+        <v>1108</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1479,10 +1484,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>433952</v>
+        <v>433261</v>
       </c>
       <c r="R9" t="n">
-        <v>6936043</v>
+        <v>6935504</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1515,11 +1520,6 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-05-08</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1546,7 +1546,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124880286</v>
+        <v>124880275</v>
       </c>
       <c r="B10" t="n">
         <v>57513</v>
@@ -1586,10 +1586,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>433434</v>
+        <v>432954</v>
       </c>
       <c r="R10" t="n">
-        <v>6935749</v>
+        <v>6934982</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1626,7 +1626,7 @@
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1653,10 +1653,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124880344</v>
+        <v>124880310</v>
       </c>
       <c r="B11" t="n">
-        <v>91030</v>
+        <v>57513</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1669,21 +1669,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1693,10 +1693,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>434028</v>
+        <v>434385</v>
       </c>
       <c r="R11" t="n">
-        <v>6936084</v>
+        <v>6936814</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1729,6 +1729,11 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-05-08</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1755,10 +1760,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>124880237</v>
+        <v>124880319</v>
       </c>
       <c r="B12" t="n">
-        <v>91012</v>
+        <v>57513</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1771,21 +1776,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1795,10 +1800,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>433636</v>
+        <v>434789</v>
       </c>
       <c r="R12" t="n">
-        <v>6935914</v>
+        <v>6936947</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1831,6 +1836,11 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-05-08</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1857,7 +1867,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>124880275</v>
+        <v>124880318</v>
       </c>
       <c r="B13" t="n">
         <v>57513</v>
@@ -1897,10 +1907,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>432954</v>
+        <v>434664</v>
       </c>
       <c r="R13" t="n">
-        <v>6934982</v>
+        <v>6936929</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1964,7 +1974,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>124880310</v>
+        <v>124880283</v>
       </c>
       <c r="B14" t="n">
         <v>57513</v>
@@ -2004,10 +2014,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>434385</v>
+        <v>433376</v>
       </c>
       <c r="R14" t="n">
-        <v>6936814</v>
+        <v>6935695</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2044,7 +2054,7 @@
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2071,10 +2081,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>124880372</v>
+        <v>124880296</v>
       </c>
       <c r="B15" t="n">
-        <v>78810</v>
+        <v>57513</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2087,21 +2097,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2111,10 +2121,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>434443</v>
+        <v>434019</v>
       </c>
       <c r="R15" t="n">
-        <v>6936839</v>
+        <v>6936070</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2151,7 +2161,7 @@
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>Mycket rikligt</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2178,10 +2188,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>124880350</v>
+        <v>124880365</v>
       </c>
       <c r="B16" t="n">
-        <v>91030</v>
+        <v>78810</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2194,21 +2204,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2218,10 +2228,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>434118</v>
+        <v>433755</v>
       </c>
       <c r="R16" t="n">
-        <v>6936187</v>
+        <v>6935995</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2254,6 +2264,11 @@
       <c r="AA16" t="inlineStr">
         <is>
           <t>2025-05-08</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2280,10 +2295,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>124880373</v>
+        <v>124880286</v>
       </c>
       <c r="B17" t="n">
-        <v>78810</v>
+        <v>57513</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2296,21 +2311,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2320,10 +2335,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>434482</v>
+        <v>433434</v>
       </c>
       <c r="R17" t="n">
-        <v>6936858</v>
+        <v>6935749</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2360,7 +2375,7 @@
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>Rikligt</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2387,10 +2402,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>124880318</v>
+        <v>124880364</v>
       </c>
       <c r="B18" t="n">
-        <v>57513</v>
+        <v>78810</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2403,21 +2418,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2427,10 +2442,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>434664</v>
+        <v>433682</v>
       </c>
       <c r="R18" t="n">
-        <v>6936929</v>
+        <v>6935955</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2467,7 +2482,7 @@
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Mycket rikligt</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2494,10 +2509,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>124880340</v>
+        <v>124880305</v>
       </c>
       <c r="B19" t="n">
-        <v>91030</v>
+        <v>57513</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2510,21 +2525,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2534,10 +2549,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>433661</v>
+        <v>434128</v>
       </c>
       <c r="R19" t="n">
-        <v>6935941</v>
+        <v>6936677</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2570,6 +2585,11 @@
       <c r="AA19" t="inlineStr">
         <is>
           <t>2025-05-08</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2596,10 +2616,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>124880299</v>
+        <v>124880343</v>
       </c>
       <c r="B20" t="n">
-        <v>57513</v>
+        <v>91030</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2612,21 +2632,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2636,10 +2656,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>434112</v>
+        <v>433952</v>
       </c>
       <c r="R20" t="n">
-        <v>6936130</v>
+        <v>6936054</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2672,11 +2692,6 @@
       <c r="AA20" t="inlineStr">
         <is>
           <t>2025-05-08</t>
-        </is>
-      </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2703,7 +2718,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>124880333</v>
+        <v>124880340</v>
       </c>
       <c r="B21" t="n">
         <v>91030</v>
@@ -2743,10 +2758,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>433376</v>
+        <v>433661</v>
       </c>
       <c r="R21" t="n">
-        <v>6935725</v>
+        <v>6935941</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2805,10 +2820,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>124880324</v>
+        <v>124880355</v>
       </c>
       <c r="B22" t="n">
-        <v>91008</v>
+        <v>91030</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2821,21 +2836,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>1108</v>
+        <v>5432</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2845,10 +2860,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>433261</v>
+        <v>434478</v>
       </c>
       <c r="R22" t="n">
-        <v>6935504</v>
+        <v>6936874</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2907,10 +2922,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>124880317</v>
+        <v>124880359</v>
       </c>
       <c r="B23" t="n">
-        <v>57513</v>
+        <v>78810</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2923,21 +2938,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2947,10 +2962,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>434538</v>
+        <v>433093</v>
       </c>
       <c r="R23" t="n">
-        <v>6936895</v>
+        <v>6935150</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2987,7 +3002,7 @@
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3014,10 +3029,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>124880290</v>
+        <v>124880372</v>
       </c>
       <c r="B24" t="n">
-        <v>57513</v>
+        <v>78810</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3030,21 +3045,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3054,10 +3069,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>433820</v>
+        <v>434443</v>
       </c>
       <c r="R24" t="n">
-        <v>6936000</v>
+        <v>6936839</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3094,7 +3109,7 @@
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Mycket rikligt</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3121,10 +3136,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>124880326</v>
+        <v>124880237</v>
       </c>
       <c r="B25" t="n">
-        <v>91008</v>
+        <v>91012</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3137,21 +3152,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>1108</v>
+        <v>1202</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3161,10 +3176,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>434175</v>
+        <v>433636</v>
       </c>
       <c r="R25" t="n">
-        <v>6936309</v>
+        <v>6935914</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3223,10 +3238,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>124880314</v>
+        <v>124880361</v>
       </c>
       <c r="B26" t="n">
-        <v>57513</v>
+        <v>78810</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3239,21 +3254,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3263,10 +3278,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>434484</v>
+        <v>433311</v>
       </c>
       <c r="R26" t="n">
-        <v>6936850</v>
+        <v>6935592</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3303,7 +3318,7 @@
       </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3330,7 +3345,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>124880316</v>
+        <v>124880299</v>
       </c>
       <c r="B27" t="n">
         <v>57513</v>
@@ -3370,10 +3385,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>434532</v>
+        <v>434112</v>
       </c>
       <c r="R27" t="n">
-        <v>6936893</v>
+        <v>6936130</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3437,7 +3452,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>124880278</v>
+        <v>124880295</v>
       </c>
       <c r="B28" t="n">
         <v>57513</v>
@@ -3477,10 +3492,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>433331</v>
+        <v>433952</v>
       </c>
       <c r="R28" t="n">
-        <v>6935597</v>
+        <v>6936043</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3544,10 +3559,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>124880365</v>
+        <v>124880304</v>
       </c>
       <c r="B29" t="n">
-        <v>78810</v>
+        <v>57513</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3560,21 +3575,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3584,10 +3599,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>433755</v>
+        <v>434155</v>
       </c>
       <c r="R29" t="n">
-        <v>6935995</v>
+        <v>6936279</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3624,7 +3639,7 @@
       </c>
       <c r="AC29" t="inlineStr">
         <is>
-          <t>Rikligt</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3651,10 +3666,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>124880343</v>
+        <v>124880369</v>
       </c>
       <c r="B30" t="n">
-        <v>91030</v>
+        <v>78810</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3667,21 +3682,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3691,10 +3706,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>433952</v>
+        <v>434091</v>
       </c>
       <c r="R30" t="n">
-        <v>6936054</v>
+        <v>6936122</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3727,6 +3742,11 @@
       <c r="AA30" t="inlineStr">
         <is>
           <t>2025-05-08</t>
+        </is>
+      </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>Mycket rikligt</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3753,10 +3773,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>124880304</v>
+        <v>124880326</v>
       </c>
       <c r="B31" t="n">
-        <v>57513</v>
+        <v>91008</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3769,21 +3789,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>100109</v>
+        <v>1108</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3793,10 +3813,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>434155</v>
+        <v>434175</v>
       </c>
       <c r="R31" t="n">
-        <v>6936279</v>
+        <v>6936309</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3829,11 +3849,6 @@
       <c r="AA31" t="inlineStr">
         <is>
           <t>2025-05-08</t>
-        </is>
-      </c>
-      <c r="AC31" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3860,10 +3875,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>124880313</v>
+        <v>124880329</v>
       </c>
       <c r="B32" t="n">
-        <v>57513</v>
+        <v>91030</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3876,21 +3891,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3900,10 +3915,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>434447</v>
+        <v>433106</v>
       </c>
       <c r="R32" t="n">
-        <v>6936828</v>
+        <v>6935174</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3936,11 +3951,6 @@
       <c r="AA32" t="inlineStr">
         <is>
           <t>2025-05-08</t>
-        </is>
-      </c>
-      <c r="AC32" t="inlineStr">
-        <is>
-          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3967,7 +3977,7 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>124880361</v>
+        <v>124880360</v>
       </c>
       <c r="B33" t="n">
         <v>78810</v>
@@ -4007,10 +4017,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>433311</v>
+        <v>433248</v>
       </c>
       <c r="R33" t="n">
-        <v>6935592</v>
+        <v>6935491</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4047,7 +4057,7 @@
       </c>
       <c r="AC33" t="inlineStr">
         <is>
-          <t>Rikligt</t>
+          <t>Mycket rikligt</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4074,7 +4084,7 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>124880283</v>
+        <v>124880317</v>
       </c>
       <c r="B34" t="n">
         <v>57513</v>
@@ -4114,10 +4124,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>433376</v>
+        <v>434538</v>
       </c>
       <c r="R34" t="n">
-        <v>6935695</v>
+        <v>6936895</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4154,7 +4164,7 @@
       </c>
       <c r="AC34" t="inlineStr">
         <is>
-          <t>Ringhack färska</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4181,10 +4191,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>124880319</v>
+        <v>124880345</v>
       </c>
       <c r="B35" t="n">
-        <v>57513</v>
+        <v>91030</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4197,21 +4207,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4221,10 +4231,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>434789</v>
+        <v>434057</v>
       </c>
       <c r="R35" t="n">
-        <v>6936947</v>
+        <v>6936091</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4257,11 +4267,6 @@
       <c r="AA35" t="inlineStr">
         <is>
           <t>2025-05-08</t>
-        </is>
-      </c>
-      <c r="AC35" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4288,10 +4293,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>124880360</v>
+        <v>124880333</v>
       </c>
       <c r="B36" t="n">
-        <v>78810</v>
+        <v>91030</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4304,21 +4309,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4328,10 +4333,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>433248</v>
+        <v>433376</v>
       </c>
       <c r="R36" t="n">
-        <v>6935491</v>
+        <v>6935725</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4364,11 +4369,6 @@
       <c r="AA36" t="inlineStr">
         <is>
           <t>2025-05-08</t>
-        </is>
-      </c>
-      <c r="AC36" t="inlineStr">
-        <is>
-          <t>Mycket rikligt</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4395,10 +4395,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>124880296</v>
+        <v>124880350</v>
       </c>
       <c r="B37" t="n">
-        <v>57513</v>
+        <v>91030</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4411,21 +4411,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4435,10 +4435,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>434019</v>
+        <v>434118</v>
       </c>
       <c r="R37" t="n">
-        <v>6936070</v>
+        <v>6936187</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4471,11 +4471,6 @@
       <c r="AA37" t="inlineStr">
         <is>
           <t>2025-05-08</t>
-        </is>
-      </c>
-      <c r="AC37" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4502,10 +4497,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>124880367</v>
+        <v>124880315</v>
       </c>
       <c r="B38" t="n">
-        <v>78810</v>
+        <v>57513</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4518,21 +4513,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4542,10 +4537,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>433984</v>
+        <v>434466</v>
       </c>
       <c r="R38" t="n">
-        <v>6936073</v>
+        <v>6936862</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4582,7 +4577,7 @@
       </c>
       <c r="AC38" t="inlineStr">
         <is>
-          <t>Mycket rikligt</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4609,10 +4604,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>124880358</v>
+        <v>124880313</v>
       </c>
       <c r="B39" t="n">
-        <v>78810</v>
+        <v>57513</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4625,21 +4620,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4649,10 +4644,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>433076</v>
+        <v>434447</v>
       </c>
       <c r="R39" t="n">
-        <v>6935108</v>
+        <v>6936828</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4689,7 +4684,7 @@
       </c>
       <c r="AC39" t="inlineStr">
         <is>
-          <t>Rikligt</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4716,7 +4711,7 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>124880355</v>
+        <v>124880332</v>
       </c>
       <c r="B40" t="n">
         <v>91030</v>
@@ -4756,10 +4751,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>434478</v>
+        <v>433197</v>
       </c>
       <c r="R40" t="n">
-        <v>6936874</v>
+        <v>6935385</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4818,10 +4813,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>124880288</v>
+        <v>124880353</v>
       </c>
       <c r="B41" t="n">
-        <v>57513</v>
+        <v>91030</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -4834,21 +4829,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4858,10 +4853,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>433505</v>
+        <v>434173</v>
       </c>
       <c r="R41" t="n">
-        <v>6935809</v>
+        <v>6936342</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4894,11 +4889,6 @@
       <c r="AA41" t="inlineStr">
         <is>
           <t>2025-05-08</t>
-        </is>
-      </c>
-      <c r="AC41" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4925,10 +4915,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>124880315</v>
+        <v>124880358</v>
       </c>
       <c r="B42" t="n">
-        <v>57513</v>
+        <v>78810</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -4941,21 +4931,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4965,10 +4955,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>434466</v>
+        <v>433076</v>
       </c>
       <c r="R42" t="n">
-        <v>6936862</v>
+        <v>6935108</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5005,7 +4995,7 @@
       </c>
       <c r="AC42" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5032,10 +5022,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>124880359</v>
+        <v>124880290</v>
       </c>
       <c r="B43" t="n">
-        <v>78810</v>
+        <v>57513</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5048,21 +5038,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5072,10 +5062,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>433093</v>
+        <v>433820</v>
       </c>
       <c r="R43" t="n">
-        <v>6935150</v>
+        <v>6936000</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5112,7 +5102,7 @@
       </c>
       <c r="AC43" t="inlineStr">
         <is>
-          <t>Rikligt</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5139,10 +5129,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>124880371</v>
+        <v>124880314</v>
       </c>
       <c r="B44" t="n">
-        <v>78810</v>
+        <v>57513</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5155,21 +5145,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5179,10 +5169,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>434167</v>
+        <v>434484</v>
       </c>
       <c r="R44" t="n">
-        <v>6936378</v>
+        <v>6936850</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5219,7 +5209,7 @@
       </c>
       <c r="AC44" t="inlineStr">
         <is>
-          <t>Mycket rikligt</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5246,10 +5236,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>124880332</v>
+        <v>124880316</v>
       </c>
       <c r="B45" t="n">
-        <v>91030</v>
+        <v>57513</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5262,21 +5252,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5286,10 +5276,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>433197</v>
+        <v>434532</v>
       </c>
       <c r="R45" t="n">
-        <v>6935385</v>
+        <v>6936893</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5322,6 +5312,11 @@
       <c r="AA45" t="inlineStr">
         <is>
           <t>2025-05-08</t>
+        </is>
+      </c>
+      <c r="AC45" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5348,10 +5343,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>124880305</v>
+        <v>124880344</v>
       </c>
       <c r="B46" t="n">
-        <v>57513</v>
+        <v>91030</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5364,21 +5359,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5388,10 +5383,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>434128</v>
+        <v>434028</v>
       </c>
       <c r="R46" t="n">
-        <v>6936677</v>
+        <v>6936084</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5424,11 +5419,6 @@
       <c r="AA46" t="inlineStr">
         <is>
           <t>2025-05-08</t>
-        </is>
-      </c>
-      <c r="AC46" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5455,10 +5445,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>124880369</v>
+        <v>124880338</v>
       </c>
       <c r="B47" t="n">
-        <v>78810</v>
+        <v>91030</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5471,21 +5461,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5495,10 +5485,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>434091</v>
+        <v>433585</v>
       </c>
       <c r="R47" t="n">
-        <v>6936122</v>
+        <v>6935882</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5531,11 +5521,6 @@
       <c r="AA47" t="inlineStr">
         <is>
           <t>2025-05-08</t>
-        </is>
-      </c>
-      <c r="AC47" t="inlineStr">
-        <is>
-          <t>Mycket rikligt</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5562,10 +5547,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>124880353</v>
+        <v>124880371</v>
       </c>
       <c r="B48" t="n">
-        <v>91030</v>
+        <v>78810</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5578,21 +5563,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5602,10 +5587,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>434173</v>
+        <v>434167</v>
       </c>
       <c r="R48" t="n">
-        <v>6936342</v>
+        <v>6936378</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5638,6 +5623,11 @@
       <c r="AA48" t="inlineStr">
         <is>
           <t>2025-05-08</t>
+        </is>
+      </c>
+      <c r="AC48" t="inlineStr">
+        <is>
+          <t>Mycket rikligt</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5664,10 +5654,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>124880345</v>
+        <v>124880373</v>
       </c>
       <c r="B49" t="n">
-        <v>91030</v>
+        <v>78810</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -5680,21 +5670,21 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5704,10 +5694,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>434057</v>
+        <v>434482</v>
       </c>
       <c r="R49" t="n">
-        <v>6936091</v>
+        <v>6936858</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5740,6 +5730,11 @@
       <c r="AA49" t="inlineStr">
         <is>
           <t>2025-05-08</t>
+        </is>
+      </c>
+      <c r="AC49" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5766,10 +5761,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>124880364</v>
+        <v>124880288</v>
       </c>
       <c r="B50" t="n">
-        <v>78810</v>
+        <v>57513</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -5782,21 +5777,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5806,10 +5801,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>433682</v>
+        <v>433505</v>
       </c>
       <c r="R50" t="n">
-        <v>6935955</v>
+        <v>6935809</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5846,7 +5841,7 @@
       </c>
       <c r="AC50" t="inlineStr">
         <is>
-          <t>Mycket rikligt</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -5873,10 +5868,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>124880329</v>
+        <v>124880278</v>
       </c>
       <c r="B51" t="n">
-        <v>91030</v>
+        <v>57513</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -5889,21 +5884,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5913,10 +5908,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>433106</v>
+        <v>433331</v>
       </c>
       <c r="R51" t="n">
-        <v>6935174</v>
+        <v>6935597</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5949,6 +5944,11 @@
       <c r="AA51" t="inlineStr">
         <is>
           <t>2025-05-08</t>
+        </is>
+      </c>
+      <c r="AC51" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -5975,7 +5975,7 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>124880337</v>
+        <v>124880346</v>
       </c>
       <c r="B52" t="n">
         <v>91030</v>
@@ -6015,10 +6015,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>433534</v>
+        <v>434113</v>
       </c>
       <c r="R52" t="n">
-        <v>6935858</v>
+        <v>6936148</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>

--- a/artfynd/A 9618-2025 artfynd.xlsx
+++ b/artfynd/A 9618-2025 artfynd.xlsx
@@ -1026,7 +1026,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124880331</v>
+        <v>124880350</v>
       </c>
       <c r="B5" t="n">
         <v>91030</v>
@@ -1066,10 +1066,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>433193</v>
+        <v>434118</v>
       </c>
       <c r="R5" t="n">
-        <v>6935352</v>
+        <v>6936187</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1128,10 +1128,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124880303</v>
+        <v>124880329</v>
       </c>
       <c r="B6" t="n">
-        <v>57513</v>
+        <v>91030</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1144,21 +1144,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1168,10 +1168,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>434113</v>
+        <v>433106</v>
       </c>
       <c r="R6" t="n">
-        <v>6936181</v>
+        <v>6935174</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1204,11 +1204,6 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-05-08</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1235,10 +1230,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124880337</v>
+        <v>124880359</v>
       </c>
       <c r="B7" t="n">
-        <v>91030</v>
+        <v>78810</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1251,21 +1246,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1275,10 +1270,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>433534</v>
+        <v>433093</v>
       </c>
       <c r="R7" t="n">
-        <v>6935858</v>
+        <v>6935150</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1311,6 +1306,11 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-05-08</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1337,10 +1337,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124880367</v>
+        <v>124880333</v>
       </c>
       <c r="B8" t="n">
-        <v>78810</v>
+        <v>91030</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1353,21 +1353,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1377,10 +1377,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>433984</v>
+        <v>433376</v>
       </c>
       <c r="R8" t="n">
-        <v>6936073</v>
+        <v>6935725</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1413,11 +1413,6 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-05-08</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Mycket rikligt</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1444,10 +1439,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124880324</v>
+        <v>124880313</v>
       </c>
       <c r="B9" t="n">
-        <v>91008</v>
+        <v>57513</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1460,21 +1455,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1108</v>
+        <v>100109</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1484,10 +1479,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>433261</v>
+        <v>434447</v>
       </c>
       <c r="R9" t="n">
-        <v>6935504</v>
+        <v>6936828</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1520,6 +1515,11 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-05-08</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1546,7 +1546,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124880275</v>
+        <v>124880310</v>
       </c>
       <c r="B10" t="n">
         <v>57513</v>
@@ -1586,10 +1586,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>432954</v>
+        <v>434385</v>
       </c>
       <c r="R10" t="n">
-        <v>6934982</v>
+        <v>6936814</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1653,7 +1653,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124880310</v>
+        <v>124880278</v>
       </c>
       <c r="B11" t="n">
         <v>57513</v>
@@ -1693,10 +1693,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>434385</v>
+        <v>433331</v>
       </c>
       <c r="R11" t="n">
-        <v>6936814</v>
+        <v>6935597</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1760,7 +1760,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>124880319</v>
+        <v>124880290</v>
       </c>
       <c r="B12" t="n">
         <v>57513</v>
@@ -1800,10 +1800,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>434789</v>
+        <v>433820</v>
       </c>
       <c r="R12" t="n">
-        <v>6936947</v>
+        <v>6936000</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1867,10 +1867,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>124880318</v>
+        <v>124880355</v>
       </c>
       <c r="B13" t="n">
-        <v>57513</v>
+        <v>91030</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1883,21 +1883,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1907,10 +1907,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>434664</v>
+        <v>434478</v>
       </c>
       <c r="R13" t="n">
-        <v>6936929</v>
+        <v>6936874</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1943,11 +1943,6 @@
       <c r="AA13" t="inlineStr">
         <is>
           <t>2025-05-08</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1974,10 +1969,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>124880283</v>
+        <v>124880324</v>
       </c>
       <c r="B14" t="n">
-        <v>57513</v>
+        <v>91008</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1990,21 +1985,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100109</v>
+        <v>1108</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2014,10 +2009,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>433376</v>
+        <v>433261</v>
       </c>
       <c r="R14" t="n">
-        <v>6935695</v>
+        <v>6935504</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2050,11 +2045,6 @@
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-05-08</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2081,10 +2071,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>124880296</v>
+        <v>124880371</v>
       </c>
       <c r="B15" t="n">
-        <v>57513</v>
+        <v>78810</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2097,21 +2087,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2121,10 +2111,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>434019</v>
+        <v>434167</v>
       </c>
       <c r="R15" t="n">
-        <v>6936070</v>
+        <v>6936378</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2161,7 +2151,7 @@
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Mycket rikligt</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2188,10 +2178,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>124880365</v>
+        <v>124880296</v>
       </c>
       <c r="B16" t="n">
-        <v>78810</v>
+        <v>57513</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2204,21 +2194,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2228,10 +2218,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>433755</v>
+        <v>434019</v>
       </c>
       <c r="R16" t="n">
-        <v>6935995</v>
+        <v>6936070</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2268,7 +2258,7 @@
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>Rikligt</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2295,7 +2285,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>124880286</v>
+        <v>124880305</v>
       </c>
       <c r="B17" t="n">
         <v>57513</v>
@@ -2335,10 +2325,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>433434</v>
+        <v>434128</v>
       </c>
       <c r="R17" t="n">
-        <v>6935749</v>
+        <v>6936677</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2375,7 +2365,7 @@
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2402,7 +2392,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>124880364</v>
+        <v>124880361</v>
       </c>
       <c r="B18" t="n">
         <v>78810</v>
@@ -2442,10 +2432,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>433682</v>
+        <v>433311</v>
       </c>
       <c r="R18" t="n">
-        <v>6935955</v>
+        <v>6935592</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2482,7 +2472,7 @@
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>Mycket rikligt</t>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2509,10 +2499,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>124880305</v>
+        <v>124880364</v>
       </c>
       <c r="B19" t="n">
-        <v>57513</v>
+        <v>78810</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2525,21 +2515,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2549,10 +2539,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>434128</v>
+        <v>433682</v>
       </c>
       <c r="R19" t="n">
-        <v>6936677</v>
+        <v>6935955</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2589,7 +2579,7 @@
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Mycket rikligt</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2616,10 +2606,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>124880343</v>
+        <v>124880373</v>
       </c>
       <c r="B20" t="n">
-        <v>91030</v>
+        <v>78810</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2632,21 +2622,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2656,10 +2646,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>433952</v>
+        <v>434482</v>
       </c>
       <c r="R20" t="n">
-        <v>6936054</v>
+        <v>6936858</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2692,6 +2682,11 @@
       <c r="AA20" t="inlineStr">
         <is>
           <t>2025-05-08</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2718,10 +2713,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>124880340</v>
+        <v>124880358</v>
       </c>
       <c r="B21" t="n">
-        <v>91030</v>
+        <v>78810</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2734,21 +2729,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2758,10 +2753,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>433661</v>
+        <v>433076</v>
       </c>
       <c r="R21" t="n">
-        <v>6935941</v>
+        <v>6935108</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2794,6 +2789,11 @@
       <c r="AA21" t="inlineStr">
         <is>
           <t>2025-05-08</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2820,10 +2820,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>124880355</v>
+        <v>124880314</v>
       </c>
       <c r="B22" t="n">
-        <v>91030</v>
+        <v>57513</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2836,21 +2836,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2860,10 +2860,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>434478</v>
+        <v>434484</v>
       </c>
       <c r="R22" t="n">
-        <v>6936874</v>
+        <v>6936850</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2896,6 +2896,11 @@
       <c r="AA22" t="inlineStr">
         <is>
           <t>2025-05-08</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2922,10 +2927,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>124880359</v>
+        <v>124880338</v>
       </c>
       <c r="B23" t="n">
-        <v>78810</v>
+        <v>91030</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2938,21 +2943,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2962,10 +2967,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>433093</v>
+        <v>433585</v>
       </c>
       <c r="R23" t="n">
-        <v>6935150</v>
+        <v>6935882</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2998,11 +3003,6 @@
       <c r="AA23" t="inlineStr">
         <is>
           <t>2025-05-08</t>
-        </is>
-      </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3029,10 +3029,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>124880372</v>
+        <v>124880353</v>
       </c>
       <c r="B24" t="n">
-        <v>78810</v>
+        <v>91030</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3045,21 +3045,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3069,10 +3069,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>434443</v>
+        <v>434173</v>
       </c>
       <c r="R24" t="n">
-        <v>6936839</v>
+        <v>6936342</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3105,11 +3105,6 @@
       <c r="AA24" t="inlineStr">
         <is>
           <t>2025-05-08</t>
-        </is>
-      </c>
-      <c r="AC24" t="inlineStr">
-        <is>
-          <t>Mycket rikligt</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3238,10 +3233,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>124880361</v>
+        <v>124880315</v>
       </c>
       <c r="B26" t="n">
-        <v>78810</v>
+        <v>57513</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3254,21 +3249,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3278,10 +3273,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>433311</v>
+        <v>434466</v>
       </c>
       <c r="R26" t="n">
-        <v>6935592</v>
+        <v>6936862</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3318,7 +3313,7 @@
       </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>Rikligt</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3345,7 +3340,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>124880299</v>
+        <v>124880318</v>
       </c>
       <c r="B27" t="n">
         <v>57513</v>
@@ -3385,10 +3380,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>434112</v>
+        <v>434664</v>
       </c>
       <c r="R27" t="n">
-        <v>6936130</v>
+        <v>6936929</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3452,7 +3447,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>124880295</v>
+        <v>124880299</v>
       </c>
       <c r="B28" t="n">
         <v>57513</v>
@@ -3492,10 +3487,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>433952</v>
+        <v>434112</v>
       </c>
       <c r="R28" t="n">
-        <v>6936043</v>
+        <v>6936130</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3559,10 +3554,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>124880304</v>
+        <v>124880326</v>
       </c>
       <c r="B29" t="n">
-        <v>57513</v>
+        <v>91008</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3575,21 +3570,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>100109</v>
+        <v>1108</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3599,10 +3594,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>434155</v>
+        <v>434175</v>
       </c>
       <c r="R29" t="n">
-        <v>6936279</v>
+        <v>6936309</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3635,11 +3630,6 @@
       <c r="AA29" t="inlineStr">
         <is>
           <t>2025-05-08</t>
-        </is>
-      </c>
-      <c r="AC29" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3666,7 +3656,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>124880369</v>
+        <v>124880360</v>
       </c>
       <c r="B30" t="n">
         <v>78810</v>
@@ -3706,10 +3696,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>434091</v>
+        <v>433248</v>
       </c>
       <c r="R30" t="n">
-        <v>6936122</v>
+        <v>6935491</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3773,10 +3763,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>124880326</v>
+        <v>124880340</v>
       </c>
       <c r="B31" t="n">
-        <v>91008</v>
+        <v>91030</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3789,21 +3779,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>1108</v>
+        <v>5432</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3813,10 +3803,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>434175</v>
+        <v>433661</v>
       </c>
       <c r="R31" t="n">
-        <v>6936309</v>
+        <v>6935941</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3875,10 +3865,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>124880329</v>
+        <v>124880369</v>
       </c>
       <c r="B32" t="n">
-        <v>91030</v>
+        <v>78810</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3891,21 +3881,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3915,10 +3905,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>433106</v>
+        <v>434091</v>
       </c>
       <c r="R32" t="n">
-        <v>6935174</v>
+        <v>6936122</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3951,6 +3941,11 @@
       <c r="AA32" t="inlineStr">
         <is>
           <t>2025-05-08</t>
+        </is>
+      </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>Mycket rikligt</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3977,10 +3972,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>124880360</v>
+        <v>124880283</v>
       </c>
       <c r="B33" t="n">
-        <v>78810</v>
+        <v>57513</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -3993,21 +3988,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4017,10 +4012,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>433248</v>
+        <v>433376</v>
       </c>
       <c r="R33" t="n">
-        <v>6935491</v>
+        <v>6935695</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4057,7 +4052,7 @@
       </c>
       <c r="AC33" t="inlineStr">
         <is>
-          <t>Mycket rikligt</t>
+          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4084,10 +4079,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>124880317</v>
+        <v>124880331</v>
       </c>
       <c r="B34" t="n">
-        <v>57513</v>
+        <v>91030</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4100,21 +4095,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4124,10 +4119,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>434538</v>
+        <v>433193</v>
       </c>
       <c r="R34" t="n">
-        <v>6936895</v>
+        <v>6935352</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4160,11 +4155,6 @@
       <c r="AA34" t="inlineStr">
         <is>
           <t>2025-05-08</t>
-        </is>
-      </c>
-      <c r="AC34" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4191,10 +4181,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>124880345</v>
+        <v>124880372</v>
       </c>
       <c r="B35" t="n">
-        <v>91030</v>
+        <v>78810</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4207,21 +4197,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4231,10 +4221,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>434057</v>
+        <v>434443</v>
       </c>
       <c r="R35" t="n">
-        <v>6936091</v>
+        <v>6936839</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4267,6 +4257,11 @@
       <c r="AA35" t="inlineStr">
         <is>
           <t>2025-05-08</t>
+        </is>
+      </c>
+      <c r="AC35" t="inlineStr">
+        <is>
+          <t>Mycket rikligt</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4293,10 +4288,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>124880333</v>
+        <v>124880365</v>
       </c>
       <c r="B36" t="n">
-        <v>91030</v>
+        <v>78810</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4309,21 +4304,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4333,10 +4328,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>433376</v>
+        <v>433755</v>
       </c>
       <c r="R36" t="n">
-        <v>6935725</v>
+        <v>6935995</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4369,6 +4364,11 @@
       <c r="AA36" t="inlineStr">
         <is>
           <t>2025-05-08</t>
+        </is>
+      </c>
+      <c r="AC36" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4395,10 +4395,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>124880350</v>
+        <v>124880319</v>
       </c>
       <c r="B37" t="n">
-        <v>91030</v>
+        <v>57513</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4411,21 +4411,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4435,10 +4435,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>434118</v>
+        <v>434789</v>
       </c>
       <c r="R37" t="n">
-        <v>6936187</v>
+        <v>6936947</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4471,6 +4471,11 @@
       <c r="AA37" t="inlineStr">
         <is>
           <t>2025-05-08</t>
+        </is>
+      </c>
+      <c r="AC37" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4497,7 +4502,7 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>124880315</v>
+        <v>124880288</v>
       </c>
       <c r="B38" t="n">
         <v>57513</v>
@@ -4537,10 +4542,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>434466</v>
+        <v>433505</v>
       </c>
       <c r="R38" t="n">
-        <v>6936862</v>
+        <v>6935809</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4604,10 +4609,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>124880313</v>
+        <v>124880367</v>
       </c>
       <c r="B39" t="n">
-        <v>57513</v>
+        <v>78810</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4620,21 +4625,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4644,10 +4649,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>434447</v>
+        <v>433984</v>
       </c>
       <c r="R39" t="n">
-        <v>6936828</v>
+        <v>6936073</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4684,7 +4689,7 @@
       </c>
       <c r="AC39" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Mycket rikligt</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4711,10 +4716,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>124880332</v>
+        <v>124880295</v>
       </c>
       <c r="B40" t="n">
-        <v>91030</v>
+        <v>57513</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4727,21 +4732,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4751,10 +4756,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>433197</v>
+        <v>433952</v>
       </c>
       <c r="R40" t="n">
-        <v>6935385</v>
+        <v>6936043</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4787,6 +4792,11 @@
       <c r="AA40" t="inlineStr">
         <is>
           <t>2025-05-08</t>
+        </is>
+      </c>
+      <c r="AC40" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4813,10 +4823,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>124880353</v>
+        <v>124880304</v>
       </c>
       <c r="B41" t="n">
-        <v>91030</v>
+        <v>57513</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -4829,21 +4839,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4853,10 +4863,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>434173</v>
+        <v>434155</v>
       </c>
       <c r="R41" t="n">
-        <v>6936342</v>
+        <v>6936279</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4889,6 +4899,11 @@
       <c r="AA41" t="inlineStr">
         <is>
           <t>2025-05-08</t>
+        </is>
+      </c>
+      <c r="AC41" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4915,10 +4930,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>124880358</v>
+        <v>124880344</v>
       </c>
       <c r="B42" t="n">
-        <v>78810</v>
+        <v>91030</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -4931,21 +4946,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4955,10 +4970,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>433076</v>
+        <v>434028</v>
       </c>
       <c r="R42" t="n">
-        <v>6935108</v>
+        <v>6936084</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4991,11 +5006,6 @@
       <c r="AA42" t="inlineStr">
         <is>
           <t>2025-05-08</t>
-        </is>
-      </c>
-      <c r="AC42" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5022,10 +5032,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>124880290</v>
+        <v>124880345</v>
       </c>
       <c r="B43" t="n">
-        <v>57513</v>
+        <v>91030</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5038,21 +5048,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5062,10 +5072,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>433820</v>
+        <v>434057</v>
       </c>
       <c r="R43" t="n">
-        <v>6936000</v>
+        <v>6936091</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5098,11 +5108,6 @@
       <c r="AA43" t="inlineStr">
         <is>
           <t>2025-05-08</t>
-        </is>
-      </c>
-      <c r="AC43" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5129,7 +5134,7 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>124880314</v>
+        <v>124880316</v>
       </c>
       <c r="B44" t="n">
         <v>57513</v>
@@ -5169,10 +5174,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>434484</v>
+        <v>434532</v>
       </c>
       <c r="R44" t="n">
-        <v>6936850</v>
+        <v>6936893</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5236,7 +5241,7 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>124880316</v>
+        <v>124880317</v>
       </c>
       <c r="B45" t="n">
         <v>57513</v>
@@ -5276,10 +5281,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>434532</v>
+        <v>434538</v>
       </c>
       <c r="R45" t="n">
-        <v>6936893</v>
+        <v>6936895</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5316,7 +5321,7 @@
       </c>
       <c r="AC45" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5343,7 +5348,7 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>124880344</v>
+        <v>124880346</v>
       </c>
       <c r="B46" t="n">
         <v>91030</v>
@@ -5383,10 +5388,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>434028</v>
+        <v>434113</v>
       </c>
       <c r="R46" t="n">
-        <v>6936084</v>
+        <v>6936148</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5445,10 +5450,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>124880338</v>
+        <v>124880303</v>
       </c>
       <c r="B47" t="n">
-        <v>91030</v>
+        <v>57513</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5461,21 +5466,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5485,10 +5490,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>433585</v>
+        <v>434113</v>
       </c>
       <c r="R47" t="n">
-        <v>6935882</v>
+        <v>6936181</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5521,6 +5526,11 @@
       <c r="AA47" t="inlineStr">
         <is>
           <t>2025-05-08</t>
+        </is>
+      </c>
+      <c r="AC47" t="inlineStr">
+        <is>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5547,10 +5557,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>124880371</v>
+        <v>124880286</v>
       </c>
       <c r="B48" t="n">
-        <v>78810</v>
+        <v>57513</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5563,21 +5573,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5587,10 +5597,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>434167</v>
+        <v>433434</v>
       </c>
       <c r="R48" t="n">
-        <v>6936378</v>
+        <v>6935749</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5627,7 +5637,7 @@
       </c>
       <c r="AC48" t="inlineStr">
         <is>
-          <t>Mycket rikligt</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5654,10 +5664,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>124880373</v>
+        <v>124880332</v>
       </c>
       <c r="B49" t="n">
-        <v>78810</v>
+        <v>91030</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -5670,21 +5680,21 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5694,10 +5704,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>434482</v>
+        <v>433197</v>
       </c>
       <c r="R49" t="n">
-        <v>6936858</v>
+        <v>6935385</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5730,11 +5740,6 @@
       <c r="AA49" t="inlineStr">
         <is>
           <t>2025-05-08</t>
-        </is>
-      </c>
-      <c r="AC49" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5761,7 +5766,7 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>124880288</v>
+        <v>124880275</v>
       </c>
       <c r="B50" t="n">
         <v>57513</v>
@@ -5801,10 +5806,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>433505</v>
+        <v>432954</v>
       </c>
       <c r="R50" t="n">
-        <v>6935809</v>
+        <v>6934982</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5868,10 +5873,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>124880278</v>
+        <v>124880343</v>
       </c>
       <c r="B51" t="n">
-        <v>57513</v>
+        <v>91030</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -5884,21 +5889,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5908,10 +5913,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>433331</v>
+        <v>433952</v>
       </c>
       <c r="R51" t="n">
-        <v>6935597</v>
+        <v>6936054</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5944,11 +5949,6 @@
       <c r="AA51" t="inlineStr">
         <is>
           <t>2025-05-08</t>
-        </is>
-      </c>
-      <c r="AC51" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -5975,7 +5975,7 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>124880346</v>
+        <v>124880337</v>
       </c>
       <c r="B52" t="n">
         <v>91030</v>
@@ -6015,10 +6015,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>434113</v>
+        <v>433534</v>
       </c>
       <c r="R52" t="n">
-        <v>6936148</v>
+        <v>6935858</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>

--- a/artfynd/A 9618-2025 artfynd.xlsx
+++ b/artfynd/A 9618-2025 artfynd.xlsx
@@ -2392,7 +2392,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>124880361</v>
+        <v>124880358</v>
       </c>
       <c r="B18" t="n">
         <v>78810</v>
@@ -2432,10 +2432,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>433311</v>
+        <v>433076</v>
       </c>
       <c r="R18" t="n">
-        <v>6935592</v>
+        <v>6935108</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2499,7 +2499,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>124880364</v>
+        <v>124880361</v>
       </c>
       <c r="B19" t="n">
         <v>78810</v>
@@ -2539,10 +2539,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>433682</v>
+        <v>433311</v>
       </c>
       <c r="R19" t="n">
-        <v>6935955</v>
+        <v>6935592</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2579,7 +2579,7 @@
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>Mycket rikligt</t>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2606,7 +2606,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>124880373</v>
+        <v>124880364</v>
       </c>
       <c r="B20" t="n">
         <v>78810</v>
@@ -2646,10 +2646,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>434482</v>
+        <v>433682</v>
       </c>
       <c r="R20" t="n">
-        <v>6936858</v>
+        <v>6935955</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2686,7 +2686,7 @@
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>Rikligt</t>
+          <t>Mycket rikligt</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2713,7 +2713,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>124880358</v>
+        <v>124880373</v>
       </c>
       <c r="B21" t="n">
         <v>78810</v>
@@ -2753,10 +2753,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>433076</v>
+        <v>434482</v>
       </c>
       <c r="R21" t="n">
-        <v>6935108</v>
+        <v>6936858</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -3233,7 +3233,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>124880315</v>
+        <v>124880318</v>
       </c>
       <c r="B26" t="n">
         <v>57513</v>
@@ -3273,10 +3273,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>434466</v>
+        <v>434664</v>
       </c>
       <c r="R26" t="n">
-        <v>6936862</v>
+        <v>6936929</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3340,7 +3340,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>124880318</v>
+        <v>124880299</v>
       </c>
       <c r="B27" t="n">
         <v>57513</v>
@@ -3380,10 +3380,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>434664</v>
+        <v>434112</v>
       </c>
       <c r="R27" t="n">
-        <v>6936929</v>
+        <v>6936130</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3447,7 +3447,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>124880299</v>
+        <v>124880315</v>
       </c>
       <c r="B28" t="n">
         <v>57513</v>
@@ -3487,10 +3487,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>434112</v>
+        <v>434466</v>
       </c>
       <c r="R28" t="n">
-        <v>6936130</v>
+        <v>6936862</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3656,10 +3656,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>124880360</v>
+        <v>124880340</v>
       </c>
       <c r="B30" t="n">
-        <v>78810</v>
+        <v>91030</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3672,21 +3672,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3696,10 +3696,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>433248</v>
+        <v>433661</v>
       </c>
       <c r="R30" t="n">
-        <v>6935491</v>
+        <v>6935941</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3732,11 +3732,6 @@
       <c r="AA30" t="inlineStr">
         <is>
           <t>2025-05-08</t>
-        </is>
-      </c>
-      <c r="AC30" t="inlineStr">
-        <is>
-          <t>Mycket rikligt</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3763,10 +3758,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>124880340</v>
+        <v>124880360</v>
       </c>
       <c r="B31" t="n">
-        <v>91030</v>
+        <v>78810</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3779,21 +3774,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3803,10 +3798,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>433661</v>
+        <v>433248</v>
       </c>
       <c r="R31" t="n">
-        <v>6935941</v>
+        <v>6935491</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3839,6 +3834,11 @@
       <c r="AA31" t="inlineStr">
         <is>
           <t>2025-05-08</t>
+        </is>
+      </c>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>Mycket rikligt</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -5450,10 +5450,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>124880303</v>
+        <v>124880332</v>
       </c>
       <c r="B47" t="n">
-        <v>57513</v>
+        <v>91030</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5466,21 +5466,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5490,10 +5490,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>434113</v>
+        <v>433197</v>
       </c>
       <c r="R47" t="n">
-        <v>6936181</v>
+        <v>6935385</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5526,11 +5526,6 @@
       <c r="AA47" t="inlineStr">
         <is>
           <t>2025-05-08</t>
-        </is>
-      </c>
-      <c r="AC47" t="inlineStr">
-        <is>
-          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5557,7 +5552,7 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>124880286</v>
+        <v>124880303</v>
       </c>
       <c r="B48" t="n">
         <v>57513</v>
@@ -5597,10 +5592,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>433434</v>
+        <v>434113</v>
       </c>
       <c r="R48" t="n">
-        <v>6935749</v>
+        <v>6936181</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5664,10 +5659,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>124880332</v>
+        <v>124880286</v>
       </c>
       <c r="B49" t="n">
-        <v>91030</v>
+        <v>57513</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -5680,21 +5675,21 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5704,10 +5699,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>433197</v>
+        <v>433434</v>
       </c>
       <c r="R49" t="n">
-        <v>6935385</v>
+        <v>6935749</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5740,6 +5735,11 @@
       <c r="AA49" t="inlineStr">
         <is>
           <t>2025-05-08</t>
+        </is>
+      </c>
+      <c r="AC49" t="inlineStr">
+        <is>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD49" t="b">

--- a/artfynd/A 9618-2025 artfynd.xlsx
+++ b/artfynd/A 9618-2025 artfynd.xlsx
@@ -1026,10 +1026,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124880350</v>
+        <v>124880316</v>
       </c>
       <c r="B5" t="n">
-        <v>91030</v>
+        <v>57513</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1042,21 +1042,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1066,10 +1066,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>434118</v>
+        <v>434532</v>
       </c>
       <c r="R5" t="n">
-        <v>6936187</v>
+        <v>6936893</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1102,6 +1102,11 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-05-08</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1128,10 +1133,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124880329</v>
+        <v>124880324</v>
       </c>
       <c r="B6" t="n">
-        <v>91030</v>
+        <v>91008</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1144,21 +1149,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>5432</v>
+        <v>1108</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1168,10 +1173,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>433106</v>
+        <v>433261</v>
       </c>
       <c r="R6" t="n">
-        <v>6935174</v>
+        <v>6935504</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1230,10 +1235,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124880359</v>
+        <v>124880345</v>
       </c>
       <c r="B7" t="n">
-        <v>78810</v>
+        <v>91030</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1246,21 +1251,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1270,10 +1275,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>433093</v>
+        <v>434057</v>
       </c>
       <c r="R7" t="n">
-        <v>6935150</v>
+        <v>6936091</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1306,11 +1311,6 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-05-08</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1337,10 +1337,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124880333</v>
+        <v>124880286</v>
       </c>
       <c r="B8" t="n">
-        <v>91030</v>
+        <v>57513</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1353,21 +1353,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1377,10 +1377,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>433376</v>
+        <v>433434</v>
       </c>
       <c r="R8" t="n">
-        <v>6935725</v>
+        <v>6935749</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1413,6 +1413,11 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-05-08</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1439,7 +1444,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124880313</v>
+        <v>124880305</v>
       </c>
       <c r="B9" t="n">
         <v>57513</v>
@@ -1479,10 +1484,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>434447</v>
+        <v>434128</v>
       </c>
       <c r="R9" t="n">
-        <v>6936828</v>
+        <v>6936677</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1519,7 +1524,7 @@
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1546,10 +1551,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124880310</v>
+        <v>124880350</v>
       </c>
       <c r="B10" t="n">
-        <v>57513</v>
+        <v>91030</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1562,21 +1567,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1586,10 +1591,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>434385</v>
+        <v>434118</v>
       </c>
       <c r="R10" t="n">
-        <v>6936814</v>
+        <v>6936187</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1622,11 +1627,6 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-05-08</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1653,10 +1653,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124880278</v>
+        <v>124880355</v>
       </c>
       <c r="B11" t="n">
-        <v>57513</v>
+        <v>91030</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1669,21 +1669,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1693,10 +1693,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>433331</v>
+        <v>434478</v>
       </c>
       <c r="R11" t="n">
-        <v>6935597</v>
+        <v>6936874</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1729,11 +1729,6 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-05-08</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1760,10 +1755,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>124880290</v>
+        <v>124880365</v>
       </c>
       <c r="B12" t="n">
-        <v>57513</v>
+        <v>78810</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1776,21 +1771,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1800,10 +1795,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>433820</v>
+        <v>433755</v>
       </c>
       <c r="R12" t="n">
-        <v>6936000</v>
+        <v>6935995</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1840,7 +1835,7 @@
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1867,7 +1862,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>124880355</v>
+        <v>124880332</v>
       </c>
       <c r="B13" t="n">
         <v>91030</v>
@@ -1907,10 +1902,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>434478</v>
+        <v>433197</v>
       </c>
       <c r="R13" t="n">
-        <v>6936874</v>
+        <v>6935385</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1969,10 +1964,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>124880324</v>
+        <v>124880331</v>
       </c>
       <c r="B14" t="n">
-        <v>91008</v>
+        <v>91030</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1985,21 +1980,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1108</v>
+        <v>5432</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2009,10 +2004,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>433261</v>
+        <v>433193</v>
       </c>
       <c r="R14" t="n">
-        <v>6935504</v>
+        <v>6935352</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2071,10 +2066,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>124880371</v>
+        <v>124880278</v>
       </c>
       <c r="B15" t="n">
-        <v>78810</v>
+        <v>57513</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2087,21 +2082,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2111,10 +2106,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>434167</v>
+        <v>433331</v>
       </c>
       <c r="R15" t="n">
-        <v>6936378</v>
+        <v>6935597</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2151,7 +2146,7 @@
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>Mycket rikligt</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2178,10 +2173,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>124880296</v>
+        <v>124880369</v>
       </c>
       <c r="B16" t="n">
-        <v>57513</v>
+        <v>78810</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2194,21 +2189,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2218,10 +2213,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>434019</v>
+        <v>434091</v>
       </c>
       <c r="R16" t="n">
-        <v>6936070</v>
+        <v>6936122</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2258,7 +2253,7 @@
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Mycket rikligt</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2285,7 +2280,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>124880305</v>
+        <v>124880314</v>
       </c>
       <c r="B17" t="n">
         <v>57513</v>
@@ -2325,10 +2320,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>434128</v>
+        <v>434484</v>
       </c>
       <c r="R17" t="n">
-        <v>6936677</v>
+        <v>6936850</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2392,10 +2387,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>124880358</v>
+        <v>124880317</v>
       </c>
       <c r="B18" t="n">
-        <v>78810</v>
+        <v>57513</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2408,21 +2403,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2432,10 +2427,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>433076</v>
+        <v>434538</v>
       </c>
       <c r="R18" t="n">
-        <v>6935108</v>
+        <v>6936895</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2472,7 +2467,7 @@
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>Rikligt</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2499,10 +2494,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>124880361</v>
+        <v>124880313</v>
       </c>
       <c r="B19" t="n">
-        <v>78810</v>
+        <v>57513</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2515,21 +2510,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2539,10 +2534,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>433311</v>
+        <v>434447</v>
       </c>
       <c r="R19" t="n">
-        <v>6935592</v>
+        <v>6936828</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2579,7 +2574,7 @@
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>Rikligt</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2606,7 +2601,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>124880364</v>
+        <v>124880371</v>
       </c>
       <c r="B20" t="n">
         <v>78810</v>
@@ -2646,10 +2641,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>433682</v>
+        <v>434167</v>
       </c>
       <c r="R20" t="n">
-        <v>6935955</v>
+        <v>6936378</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2713,10 +2708,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>124880373</v>
+        <v>124880337</v>
       </c>
       <c r="B21" t="n">
-        <v>78810</v>
+        <v>91030</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2729,21 +2724,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2753,10 +2748,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>434482</v>
+        <v>433534</v>
       </c>
       <c r="R21" t="n">
-        <v>6936858</v>
+        <v>6935858</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2789,11 +2784,6 @@
       <c r="AA21" t="inlineStr">
         <is>
           <t>2025-05-08</t>
-        </is>
-      </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2820,10 +2810,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>124880314</v>
+        <v>124880373</v>
       </c>
       <c r="B22" t="n">
-        <v>57513</v>
+        <v>78810</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2836,21 +2826,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2860,10 +2850,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>434484</v>
+        <v>434482</v>
       </c>
       <c r="R22" t="n">
-        <v>6936850</v>
+        <v>6936858</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2900,7 +2890,7 @@
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2927,10 +2917,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>124880338</v>
+        <v>124880237</v>
       </c>
       <c r="B23" t="n">
-        <v>91030</v>
+        <v>91012</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2943,21 +2933,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>5432</v>
+        <v>1202</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2967,10 +2957,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>433585</v>
+        <v>433636</v>
       </c>
       <c r="R23" t="n">
-        <v>6935882</v>
+        <v>6935914</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3029,10 +3019,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>124880353</v>
+        <v>124880358</v>
       </c>
       <c r="B24" t="n">
-        <v>91030</v>
+        <v>78810</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3045,21 +3035,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3069,10 +3059,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>434173</v>
+        <v>433076</v>
       </c>
       <c r="R24" t="n">
-        <v>6936342</v>
+        <v>6935108</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3105,6 +3095,11 @@
       <c r="AA24" t="inlineStr">
         <is>
           <t>2025-05-08</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3131,10 +3126,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>124880237</v>
+        <v>124880295</v>
       </c>
       <c r="B25" t="n">
-        <v>91012</v>
+        <v>57513</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3147,21 +3142,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3171,10 +3166,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>433636</v>
+        <v>433952</v>
       </c>
       <c r="R25" t="n">
-        <v>6935914</v>
+        <v>6936043</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3207,6 +3202,11 @@
       <c r="AA25" t="inlineStr">
         <is>
           <t>2025-05-08</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3233,7 +3233,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>124880318</v>
+        <v>124880283</v>
       </c>
       <c r="B26" t="n">
         <v>57513</v>
@@ -3273,10 +3273,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>434664</v>
+        <v>433376</v>
       </c>
       <c r="R26" t="n">
-        <v>6936929</v>
+        <v>6935695</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3313,7 +3313,7 @@
       </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3340,7 +3340,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>124880299</v>
+        <v>124880304</v>
       </c>
       <c r="B27" t="n">
         <v>57513</v>
@@ -3380,10 +3380,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>434112</v>
+        <v>434155</v>
       </c>
       <c r="R27" t="n">
-        <v>6936130</v>
+        <v>6936279</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3447,10 +3447,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>124880315</v>
+        <v>124880359</v>
       </c>
       <c r="B28" t="n">
-        <v>57513</v>
+        <v>78810</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3463,21 +3463,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3487,10 +3487,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>434466</v>
+        <v>433093</v>
       </c>
       <c r="R28" t="n">
-        <v>6936862</v>
+        <v>6935150</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3527,7 +3527,7 @@
       </c>
       <c r="AC28" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3554,10 +3554,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>124880326</v>
+        <v>124880299</v>
       </c>
       <c r="B29" t="n">
-        <v>91008</v>
+        <v>57513</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3570,21 +3570,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>1108</v>
+        <v>100109</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3594,10 +3594,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>434175</v>
+        <v>434112</v>
       </c>
       <c r="R29" t="n">
-        <v>6936309</v>
+        <v>6936130</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3630,6 +3630,11 @@
       <c r="AA29" t="inlineStr">
         <is>
           <t>2025-05-08</t>
+        </is>
+      </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3656,10 +3661,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>124880340</v>
+        <v>124880310</v>
       </c>
       <c r="B30" t="n">
-        <v>91030</v>
+        <v>57513</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3672,21 +3677,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3696,10 +3701,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>433661</v>
+        <v>434385</v>
       </c>
       <c r="R30" t="n">
-        <v>6935941</v>
+        <v>6936814</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3732,6 +3737,11 @@
       <c r="AA30" t="inlineStr">
         <is>
           <t>2025-05-08</t>
+        </is>
+      </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3758,10 +3768,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>124880360</v>
+        <v>124880288</v>
       </c>
       <c r="B31" t="n">
-        <v>78810</v>
+        <v>57513</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3774,21 +3784,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3798,10 +3808,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>433248</v>
+        <v>433505</v>
       </c>
       <c r="R31" t="n">
-        <v>6935491</v>
+        <v>6935809</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3838,7 +3848,7 @@
       </c>
       <c r="AC31" t="inlineStr">
         <is>
-          <t>Mycket rikligt</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3865,10 +3875,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>124880369</v>
+        <v>124880290</v>
       </c>
       <c r="B32" t="n">
-        <v>78810</v>
+        <v>57513</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3881,21 +3891,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3905,10 +3915,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>434091</v>
+        <v>433820</v>
       </c>
       <c r="R32" t="n">
-        <v>6936122</v>
+        <v>6936000</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3945,7 +3955,7 @@
       </c>
       <c r="AC32" t="inlineStr">
         <is>
-          <t>Mycket rikligt</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3972,7 +3982,7 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>124880283</v>
+        <v>124880275</v>
       </c>
       <c r="B33" t="n">
         <v>57513</v>
@@ -4012,10 +4022,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>433376</v>
+        <v>432954</v>
       </c>
       <c r="R33" t="n">
-        <v>6935695</v>
+        <v>6934982</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4052,7 +4062,7 @@
       </c>
       <c r="AC33" t="inlineStr">
         <is>
-          <t>Ringhack färska</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4079,7 +4089,7 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>124880331</v>
+        <v>124880340</v>
       </c>
       <c r="B34" t="n">
         <v>91030</v>
@@ -4119,10 +4129,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>433193</v>
+        <v>433661</v>
       </c>
       <c r="R34" t="n">
-        <v>6935352</v>
+        <v>6935941</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4181,10 +4191,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>124880372</v>
+        <v>124880333</v>
       </c>
       <c r="B35" t="n">
-        <v>78810</v>
+        <v>91030</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4197,21 +4207,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4221,10 +4231,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>434443</v>
+        <v>433376</v>
       </c>
       <c r="R35" t="n">
-        <v>6936839</v>
+        <v>6935725</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4257,11 +4267,6 @@
       <c r="AA35" t="inlineStr">
         <is>
           <t>2025-05-08</t>
-        </is>
-      </c>
-      <c r="AC35" t="inlineStr">
-        <is>
-          <t>Mycket rikligt</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4288,10 +4293,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>124880365</v>
+        <v>124880338</v>
       </c>
       <c r="B36" t="n">
-        <v>78810</v>
+        <v>91030</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4304,21 +4309,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4328,10 +4333,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>433755</v>
+        <v>433585</v>
       </c>
       <c r="R36" t="n">
-        <v>6935995</v>
+        <v>6935882</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4364,11 +4369,6 @@
       <c r="AA36" t="inlineStr">
         <is>
           <t>2025-05-08</t>
-        </is>
-      </c>
-      <c r="AC36" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4395,10 +4395,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>124880319</v>
+        <v>124880329</v>
       </c>
       <c r="B37" t="n">
-        <v>57513</v>
+        <v>91030</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4411,21 +4411,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4435,10 +4435,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>434789</v>
+        <v>433106</v>
       </c>
       <c r="R37" t="n">
-        <v>6936947</v>
+        <v>6935174</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4471,11 +4471,6 @@
       <c r="AA37" t="inlineStr">
         <is>
           <t>2025-05-08</t>
-        </is>
-      </c>
-      <c r="AC37" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4502,10 +4497,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>124880288</v>
+        <v>124880343</v>
       </c>
       <c r="B38" t="n">
-        <v>57513</v>
+        <v>91030</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4518,21 +4513,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4542,10 +4537,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>433505</v>
+        <v>433952</v>
       </c>
       <c r="R38" t="n">
-        <v>6935809</v>
+        <v>6936054</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4578,11 +4573,6 @@
       <c r="AA38" t="inlineStr">
         <is>
           <t>2025-05-08</t>
-        </is>
-      </c>
-      <c r="AC38" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4716,7 +4706,7 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>124880295</v>
+        <v>124880303</v>
       </c>
       <c r="B40" t="n">
         <v>57513</v>
@@ -4756,10 +4746,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>433952</v>
+        <v>434113</v>
       </c>
       <c r="R40" t="n">
-        <v>6936043</v>
+        <v>6936181</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4796,7 +4786,7 @@
       </c>
       <c r="AC40" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4823,7 +4813,7 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>124880304</v>
+        <v>124880315</v>
       </c>
       <c r="B41" t="n">
         <v>57513</v>
@@ -4863,10 +4853,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>434155</v>
+        <v>434466</v>
       </c>
       <c r="R41" t="n">
-        <v>6936279</v>
+        <v>6936862</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4930,10 +4920,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>124880344</v>
+        <v>124880326</v>
       </c>
       <c r="B42" t="n">
-        <v>91030</v>
+        <v>91008</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -4946,21 +4936,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>5432</v>
+        <v>1108</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4970,10 +4960,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>434028</v>
+        <v>434175</v>
       </c>
       <c r="R42" t="n">
-        <v>6936084</v>
+        <v>6936309</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5032,7 +5022,7 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>124880345</v>
+        <v>124880344</v>
       </c>
       <c r="B43" t="n">
         <v>91030</v>
@@ -5072,10 +5062,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>434057</v>
+        <v>434028</v>
       </c>
       <c r="R43" t="n">
-        <v>6936091</v>
+        <v>6936084</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5134,10 +5124,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>124880316</v>
+        <v>124880361</v>
       </c>
       <c r="B44" t="n">
-        <v>57513</v>
+        <v>78810</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5150,21 +5140,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5174,10 +5164,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>434532</v>
+        <v>433311</v>
       </c>
       <c r="R44" t="n">
-        <v>6936893</v>
+        <v>6935592</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5214,7 +5204,7 @@
       </c>
       <c r="AC44" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5241,7 +5231,7 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>124880317</v>
+        <v>124880296</v>
       </c>
       <c r="B45" t="n">
         <v>57513</v>
@@ -5281,10 +5271,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>434538</v>
+        <v>434019</v>
       </c>
       <c r="R45" t="n">
-        <v>6936895</v>
+        <v>6936070</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5321,7 +5311,7 @@
       </c>
       <c r="AC45" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5348,10 +5338,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>124880346</v>
+        <v>124880319</v>
       </c>
       <c r="B46" t="n">
-        <v>91030</v>
+        <v>57513</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5364,21 +5354,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5388,10 +5378,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>434113</v>
+        <v>434789</v>
       </c>
       <c r="R46" t="n">
-        <v>6936148</v>
+        <v>6936947</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5424,6 +5414,11 @@
       <c r="AA46" t="inlineStr">
         <is>
           <t>2025-05-08</t>
+        </is>
+      </c>
+      <c r="AC46" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5450,10 +5445,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>124880332</v>
+        <v>124880364</v>
       </c>
       <c r="B47" t="n">
-        <v>91030</v>
+        <v>78810</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5466,21 +5461,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5490,10 +5485,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>433197</v>
+        <v>433682</v>
       </c>
       <c r="R47" t="n">
-        <v>6935385</v>
+        <v>6935955</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5526,6 +5521,11 @@
       <c r="AA47" t="inlineStr">
         <is>
           <t>2025-05-08</t>
+        </is>
+      </c>
+      <c r="AC47" t="inlineStr">
+        <is>
+          <t>Mycket rikligt</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5552,10 +5552,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>124880303</v>
+        <v>124880372</v>
       </c>
       <c r="B48" t="n">
-        <v>57513</v>
+        <v>78810</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5568,21 +5568,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5592,10 +5592,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>434113</v>
+        <v>434443</v>
       </c>
       <c r="R48" t="n">
-        <v>6936181</v>
+        <v>6936839</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5632,7 +5632,7 @@
       </c>
       <c r="AC48" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Mycket rikligt</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5659,10 +5659,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>124880286</v>
+        <v>124880346</v>
       </c>
       <c r="B49" t="n">
-        <v>57513</v>
+        <v>91030</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -5675,21 +5675,21 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5699,10 +5699,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>433434</v>
+        <v>434113</v>
       </c>
       <c r="R49" t="n">
-        <v>6935749</v>
+        <v>6936148</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5735,11 +5735,6 @@
       <c r="AA49" t="inlineStr">
         <is>
           <t>2025-05-08</t>
-        </is>
-      </c>
-      <c r="AC49" t="inlineStr">
-        <is>
-          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5766,10 +5761,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>124880275</v>
+        <v>124880360</v>
       </c>
       <c r="B50" t="n">
-        <v>57513</v>
+        <v>78810</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -5782,21 +5777,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5806,10 +5801,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>432954</v>
+        <v>433248</v>
       </c>
       <c r="R50" t="n">
-        <v>6934982</v>
+        <v>6935491</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5846,7 +5841,7 @@
       </c>
       <c r="AC50" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Mycket rikligt</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -5873,7 +5868,7 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>124880343</v>
+        <v>124880353</v>
       </c>
       <c r="B51" t="n">
         <v>91030</v>
@@ -5913,10 +5908,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>433952</v>
+        <v>434173</v>
       </c>
       <c r="R51" t="n">
-        <v>6936054</v>
+        <v>6936342</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5975,10 +5970,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>124880337</v>
+        <v>124880318</v>
       </c>
       <c r="B52" t="n">
-        <v>91030</v>
+        <v>57513</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -5991,21 +5986,21 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -6015,10 +6010,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>433534</v>
+        <v>434664</v>
       </c>
       <c r="R52" t="n">
-        <v>6935858</v>
+        <v>6936929</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6051,6 +6046,11 @@
       <c r="AA52" t="inlineStr">
         <is>
           <t>2025-05-08</t>
+        </is>
+      </c>
+      <c r="AC52" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD52" t="b">

--- a/artfynd/A 9618-2025 artfynd.xlsx
+++ b/artfynd/A 9618-2025 artfynd.xlsx
@@ -3875,10 +3875,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>124880290</v>
+        <v>124880340</v>
       </c>
       <c r="B32" t="n">
-        <v>57513</v>
+        <v>91030</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3891,21 +3891,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3915,10 +3915,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>433820</v>
+        <v>433661</v>
       </c>
       <c r="R32" t="n">
-        <v>6936000</v>
+        <v>6935941</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3951,11 +3951,6 @@
       <c r="AA32" t="inlineStr">
         <is>
           <t>2025-05-08</t>
-        </is>
-      </c>
-      <c r="AC32" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3982,10 +3977,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>124880275</v>
+        <v>124880333</v>
       </c>
       <c r="B33" t="n">
-        <v>57513</v>
+        <v>91030</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -3998,21 +3993,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4022,10 +4017,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>432954</v>
+        <v>433376</v>
       </c>
       <c r="R33" t="n">
-        <v>6934982</v>
+        <v>6935725</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4058,11 +4053,6 @@
       <c r="AA33" t="inlineStr">
         <is>
           <t>2025-05-08</t>
-        </is>
-      </c>
-      <c r="AC33" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4089,10 +4079,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>124880340</v>
+        <v>124880290</v>
       </c>
       <c r="B34" t="n">
-        <v>91030</v>
+        <v>57513</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4105,21 +4095,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4129,10 +4119,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>433661</v>
+        <v>433820</v>
       </c>
       <c r="R34" t="n">
-        <v>6935941</v>
+        <v>6936000</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4165,6 +4155,11 @@
       <c r="AA34" t="inlineStr">
         <is>
           <t>2025-05-08</t>
+        </is>
+      </c>
+      <c r="AC34" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4191,10 +4186,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>124880333</v>
+        <v>124880275</v>
       </c>
       <c r="B35" t="n">
-        <v>91030</v>
+        <v>57513</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4207,21 +4202,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4231,10 +4226,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>433376</v>
+        <v>432954</v>
       </c>
       <c r="R35" t="n">
-        <v>6935725</v>
+        <v>6934982</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4267,6 +4262,11 @@
       <c r="AA35" t="inlineStr">
         <is>
           <t>2025-05-08</t>
+        </is>
+      </c>
+      <c r="AC35" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD35" t="b">

--- a/artfynd/A 9618-2025 artfynd.xlsx
+++ b/artfynd/A 9618-2025 artfynd.xlsx
@@ -1026,10 +1026,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124880316</v>
+        <v>124880373</v>
       </c>
       <c r="B5" t="n">
-        <v>57513</v>
+        <v>78810</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1042,21 +1042,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1066,10 +1066,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>434532</v>
+        <v>434482</v>
       </c>
       <c r="R5" t="n">
-        <v>6936893</v>
+        <v>6936858</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1106,7 +1106,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1133,10 +1133,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124880324</v>
+        <v>124880365</v>
       </c>
       <c r="B6" t="n">
-        <v>91008</v>
+        <v>78810</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1149,21 +1149,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1108</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1173,10 +1173,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>433261</v>
+        <v>433755</v>
       </c>
       <c r="R6" t="n">
-        <v>6935504</v>
+        <v>6935995</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1209,6 +1209,11 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-05-08</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1235,7 +1240,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124880345</v>
+        <v>124880353</v>
       </c>
       <c r="B7" t="n">
         <v>91030</v>
@@ -1275,10 +1280,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>434057</v>
+        <v>434173</v>
       </c>
       <c r="R7" t="n">
-        <v>6936091</v>
+        <v>6936342</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1337,10 +1342,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124880286</v>
+        <v>124880337</v>
       </c>
       <c r="B8" t="n">
-        <v>57513</v>
+        <v>91030</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1353,21 +1358,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1377,10 +1382,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>433434</v>
+        <v>433534</v>
       </c>
       <c r="R8" t="n">
-        <v>6935749</v>
+        <v>6935858</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1413,11 +1418,6 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-05-08</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1444,10 +1444,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124880305</v>
+        <v>124880371</v>
       </c>
       <c r="B9" t="n">
-        <v>57513</v>
+        <v>78810</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1460,21 +1460,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1484,10 +1484,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>434128</v>
+        <v>434167</v>
       </c>
       <c r="R9" t="n">
-        <v>6936677</v>
+        <v>6936378</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1524,7 +1524,7 @@
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Mycket rikligt</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1551,10 +1551,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124880350</v>
+        <v>124880361</v>
       </c>
       <c r="B10" t="n">
-        <v>91030</v>
+        <v>78810</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1567,21 +1567,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1591,10 +1591,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>434118</v>
+        <v>433311</v>
       </c>
       <c r="R10" t="n">
-        <v>6936187</v>
+        <v>6935592</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1627,6 +1627,11 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-05-08</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1653,10 +1658,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124880355</v>
+        <v>124880359</v>
       </c>
       <c r="B11" t="n">
-        <v>91030</v>
+        <v>78810</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1669,21 +1674,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1693,10 +1698,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>434478</v>
+        <v>433093</v>
       </c>
       <c r="R11" t="n">
-        <v>6936874</v>
+        <v>6935150</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1729,6 +1734,11 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-05-08</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1755,10 +1765,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>124880365</v>
+        <v>124880278</v>
       </c>
       <c r="B12" t="n">
-        <v>78810</v>
+        <v>57513</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1771,21 +1781,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1795,10 +1805,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>433755</v>
+        <v>433331</v>
       </c>
       <c r="R12" t="n">
-        <v>6935995</v>
+        <v>6935597</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1835,7 +1845,7 @@
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>Rikligt</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1862,10 +1872,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>124880332</v>
+        <v>124880315</v>
       </c>
       <c r="B13" t="n">
-        <v>91030</v>
+        <v>57513</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1878,21 +1888,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1902,10 +1912,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>433197</v>
+        <v>434466</v>
       </c>
       <c r="R13" t="n">
-        <v>6935385</v>
+        <v>6936862</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1938,6 +1948,11 @@
       <c r="AA13" t="inlineStr">
         <is>
           <t>2025-05-08</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1964,10 +1979,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>124880331</v>
+        <v>124880319</v>
       </c>
       <c r="B14" t="n">
-        <v>91030</v>
+        <v>57513</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1980,21 +1995,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2004,10 +2019,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>433193</v>
+        <v>434789</v>
       </c>
       <c r="R14" t="n">
-        <v>6935352</v>
+        <v>6936947</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2040,6 +2055,11 @@
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-05-08</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2066,10 +2086,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>124880278</v>
+        <v>124880338</v>
       </c>
       <c r="B15" t="n">
-        <v>57513</v>
+        <v>91030</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2082,21 +2102,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2106,10 +2126,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>433331</v>
+        <v>433585</v>
       </c>
       <c r="R15" t="n">
-        <v>6935597</v>
+        <v>6935882</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2142,11 +2162,6 @@
       <c r="AA15" t="inlineStr">
         <is>
           <t>2025-05-08</t>
-        </is>
-      </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2173,7 +2188,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>124880369</v>
+        <v>124880367</v>
       </c>
       <c r="B16" t="n">
         <v>78810</v>
@@ -2213,10 +2228,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>434091</v>
+        <v>433984</v>
       </c>
       <c r="R16" t="n">
-        <v>6936122</v>
+        <v>6936073</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2280,10 +2295,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>124880314</v>
+        <v>124880372</v>
       </c>
       <c r="B17" t="n">
-        <v>57513</v>
+        <v>78810</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2296,21 +2311,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2320,10 +2335,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>434484</v>
+        <v>434443</v>
       </c>
       <c r="R17" t="n">
-        <v>6936850</v>
+        <v>6936839</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2360,7 +2375,7 @@
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Mycket rikligt</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2387,7 +2402,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>124880317</v>
+        <v>124880304</v>
       </c>
       <c r="B18" t="n">
         <v>57513</v>
@@ -2427,10 +2442,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>434538</v>
+        <v>434155</v>
       </c>
       <c r="R18" t="n">
-        <v>6936895</v>
+        <v>6936279</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2467,7 +2482,7 @@
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2494,10 +2509,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>124880313</v>
+        <v>124880346</v>
       </c>
       <c r="B19" t="n">
-        <v>57513</v>
+        <v>91030</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2510,21 +2525,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2534,10 +2549,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>434447</v>
+        <v>434113</v>
       </c>
       <c r="R19" t="n">
-        <v>6936828</v>
+        <v>6936148</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2570,11 +2585,6 @@
       <c r="AA19" t="inlineStr">
         <is>
           <t>2025-05-08</t>
-        </is>
-      </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2601,10 +2611,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>124880371</v>
+        <v>124880299</v>
       </c>
       <c r="B20" t="n">
-        <v>78810</v>
+        <v>57513</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2617,21 +2627,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2641,10 +2651,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>434167</v>
+        <v>434112</v>
       </c>
       <c r="R20" t="n">
-        <v>6936378</v>
+        <v>6936130</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2681,7 +2691,7 @@
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>Mycket rikligt</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2708,10 +2718,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>124880337</v>
+        <v>124880310</v>
       </c>
       <c r="B21" t="n">
-        <v>91030</v>
+        <v>57513</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2724,21 +2734,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2748,10 +2758,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>433534</v>
+        <v>434385</v>
       </c>
       <c r="R21" t="n">
-        <v>6935858</v>
+        <v>6936814</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2784,6 +2794,11 @@
       <c r="AA21" t="inlineStr">
         <is>
           <t>2025-05-08</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2810,10 +2825,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>124880373</v>
+        <v>124880286</v>
       </c>
       <c r="B22" t="n">
-        <v>78810</v>
+        <v>57513</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2826,21 +2841,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2850,10 +2865,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>434482</v>
+        <v>433434</v>
       </c>
       <c r="R22" t="n">
-        <v>6936858</v>
+        <v>6935749</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2890,7 +2905,7 @@
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>Rikligt</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2917,10 +2932,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>124880237</v>
+        <v>124880316</v>
       </c>
       <c r="B23" t="n">
-        <v>91012</v>
+        <v>57513</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2933,21 +2948,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2957,10 +2972,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>433636</v>
+        <v>434532</v>
       </c>
       <c r="R23" t="n">
-        <v>6935914</v>
+        <v>6936893</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2993,6 +3008,11 @@
       <c r="AA23" t="inlineStr">
         <is>
           <t>2025-05-08</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3019,7 +3039,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>124880358</v>
+        <v>124880369</v>
       </c>
       <c r="B24" t="n">
         <v>78810</v>
@@ -3059,10 +3079,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>433076</v>
+        <v>434091</v>
       </c>
       <c r="R24" t="n">
-        <v>6935108</v>
+        <v>6936122</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3099,7 +3119,7 @@
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>Rikligt</t>
+          <t>Mycket rikligt</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3126,7 +3146,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>124880295</v>
+        <v>124880317</v>
       </c>
       <c r="B25" t="n">
         <v>57513</v>
@@ -3166,10 +3186,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>433952</v>
+        <v>434538</v>
       </c>
       <c r="R25" t="n">
-        <v>6936043</v>
+        <v>6936895</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3206,7 +3226,7 @@
       </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3233,10 +3253,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>124880283</v>
+        <v>124880331</v>
       </c>
       <c r="B26" t="n">
-        <v>57513</v>
+        <v>91030</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3249,21 +3269,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3273,10 +3293,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>433376</v>
+        <v>433193</v>
       </c>
       <c r="R26" t="n">
-        <v>6935695</v>
+        <v>6935352</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3309,11 +3329,6 @@
       <c r="AA26" t="inlineStr">
         <is>
           <t>2025-05-08</t>
-        </is>
-      </c>
-      <c r="AC26" t="inlineStr">
-        <is>
-          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3340,10 +3355,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>124880304</v>
+        <v>124880343</v>
       </c>
       <c r="B27" t="n">
-        <v>57513</v>
+        <v>91030</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3356,21 +3371,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3380,10 +3395,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>434155</v>
+        <v>433952</v>
       </c>
       <c r="R27" t="n">
-        <v>6936279</v>
+        <v>6936054</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3416,11 +3431,6 @@
       <c r="AA27" t="inlineStr">
         <is>
           <t>2025-05-08</t>
-        </is>
-      </c>
-      <c r="AC27" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3447,10 +3457,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>124880359</v>
+        <v>124880344</v>
       </c>
       <c r="B28" t="n">
-        <v>78810</v>
+        <v>91030</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3463,21 +3473,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3487,10 +3497,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>433093</v>
+        <v>434028</v>
       </c>
       <c r="R28" t="n">
-        <v>6935150</v>
+        <v>6936084</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3523,11 +3533,6 @@
       <c r="AA28" t="inlineStr">
         <is>
           <t>2025-05-08</t>
-        </is>
-      </c>
-      <c r="AC28" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3554,10 +3559,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>124880299</v>
+        <v>124880329</v>
       </c>
       <c r="B29" t="n">
-        <v>57513</v>
+        <v>91030</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3570,21 +3575,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3594,10 +3599,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>434112</v>
+        <v>433106</v>
       </c>
       <c r="R29" t="n">
-        <v>6936130</v>
+        <v>6935174</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3630,11 +3635,6 @@
       <c r="AA29" t="inlineStr">
         <is>
           <t>2025-05-08</t>
-        </is>
-      </c>
-      <c r="AC29" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3661,7 +3661,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>124880310</v>
+        <v>124880296</v>
       </c>
       <c r="B30" t="n">
         <v>57513</v>
@@ -3701,10 +3701,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>434385</v>
+        <v>434019</v>
       </c>
       <c r="R30" t="n">
-        <v>6936814</v>
+        <v>6936070</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3768,7 +3768,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>124880288</v>
+        <v>124880314</v>
       </c>
       <c r="B31" t="n">
         <v>57513</v>
@@ -3808,10 +3808,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>433505</v>
+        <v>434484</v>
       </c>
       <c r="R31" t="n">
-        <v>6935809</v>
+        <v>6936850</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3875,10 +3875,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>124880340</v>
+        <v>124880318</v>
       </c>
       <c r="B32" t="n">
-        <v>91030</v>
+        <v>57513</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3891,21 +3891,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3915,10 +3915,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>433661</v>
+        <v>434664</v>
       </c>
       <c r="R32" t="n">
-        <v>6935941</v>
+        <v>6936929</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3951,6 +3951,11 @@
       <c r="AA32" t="inlineStr">
         <is>
           <t>2025-05-08</t>
+        </is>
+      </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3977,10 +3982,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>124880333</v>
+        <v>124880324</v>
       </c>
       <c r="B33" t="n">
-        <v>91030</v>
+        <v>91008</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -3993,21 +3998,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>5432</v>
+        <v>1108</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4017,10 +4022,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>433376</v>
+        <v>433261</v>
       </c>
       <c r="R33" t="n">
-        <v>6935725</v>
+        <v>6935504</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4079,10 +4084,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>124880290</v>
+        <v>124880340</v>
       </c>
       <c r="B34" t="n">
-        <v>57513</v>
+        <v>91030</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4095,21 +4100,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4119,10 +4124,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>433820</v>
+        <v>433661</v>
       </c>
       <c r="R34" t="n">
-        <v>6936000</v>
+        <v>6935941</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4155,11 +4160,6 @@
       <c r="AA34" t="inlineStr">
         <is>
           <t>2025-05-08</t>
-        </is>
-      </c>
-      <c r="AC34" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4186,10 +4186,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>124880275</v>
+        <v>124880345</v>
       </c>
       <c r="B35" t="n">
-        <v>57513</v>
+        <v>91030</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4202,21 +4202,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4226,10 +4226,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>432954</v>
+        <v>434057</v>
       </c>
       <c r="R35" t="n">
-        <v>6934982</v>
+        <v>6936091</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4262,11 +4262,6 @@
       <c r="AA35" t="inlineStr">
         <is>
           <t>2025-05-08</t>
-        </is>
-      </c>
-      <c r="AC35" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4293,10 +4288,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>124880338</v>
+        <v>124880275</v>
       </c>
       <c r="B36" t="n">
-        <v>91030</v>
+        <v>57513</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4309,21 +4304,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4333,10 +4328,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>433585</v>
+        <v>432954</v>
       </c>
       <c r="R36" t="n">
-        <v>6935882</v>
+        <v>6934982</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4369,6 +4364,11 @@
       <c r="AA36" t="inlineStr">
         <is>
           <t>2025-05-08</t>
+        </is>
+      </c>
+      <c r="AC36" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4395,10 +4395,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>124880329</v>
+        <v>124880358</v>
       </c>
       <c r="B37" t="n">
-        <v>91030</v>
+        <v>78810</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4411,21 +4411,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4435,10 +4435,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>433106</v>
+        <v>433076</v>
       </c>
       <c r="R37" t="n">
-        <v>6935174</v>
+        <v>6935108</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4471,6 +4471,11 @@
       <c r="AA37" t="inlineStr">
         <is>
           <t>2025-05-08</t>
+        </is>
+      </c>
+      <c r="AC37" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4497,10 +4502,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>124880343</v>
+        <v>124880303</v>
       </c>
       <c r="B38" t="n">
-        <v>91030</v>
+        <v>57513</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4513,21 +4518,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4537,10 +4542,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>433952</v>
+        <v>434113</v>
       </c>
       <c r="R38" t="n">
-        <v>6936054</v>
+        <v>6936181</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4573,6 +4578,11 @@
       <c r="AA38" t="inlineStr">
         <is>
           <t>2025-05-08</t>
+        </is>
+      </c>
+      <c r="AC38" t="inlineStr">
+        <is>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4599,7 +4609,7 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>124880367</v>
+        <v>124880360</v>
       </c>
       <c r="B39" t="n">
         <v>78810</v>
@@ -4639,10 +4649,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>433984</v>
+        <v>433248</v>
       </c>
       <c r="R39" t="n">
-        <v>6936073</v>
+        <v>6935491</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4706,10 +4716,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>124880303</v>
+        <v>124880364</v>
       </c>
       <c r="B40" t="n">
-        <v>57513</v>
+        <v>78810</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4722,21 +4732,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4746,10 +4756,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>434113</v>
+        <v>433682</v>
       </c>
       <c r="R40" t="n">
-        <v>6936181</v>
+        <v>6935955</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4786,7 +4796,7 @@
       </c>
       <c r="AC40" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Mycket rikligt</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4813,7 +4823,7 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>124880315</v>
+        <v>124880290</v>
       </c>
       <c r="B41" t="n">
         <v>57513</v>
@@ -4853,10 +4863,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>434466</v>
+        <v>433820</v>
       </c>
       <c r="R41" t="n">
-        <v>6936862</v>
+        <v>6936000</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4920,10 +4930,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>124880326</v>
+        <v>124880288</v>
       </c>
       <c r="B42" t="n">
-        <v>91008</v>
+        <v>57513</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -4936,21 +4946,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>1108</v>
+        <v>100109</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4960,10 +4970,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>434175</v>
+        <v>433505</v>
       </c>
       <c r="R42" t="n">
-        <v>6936309</v>
+        <v>6935809</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4996,6 +5006,11 @@
       <c r="AA42" t="inlineStr">
         <is>
           <t>2025-05-08</t>
+        </is>
+      </c>
+      <c r="AC42" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5022,10 +5037,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>124880344</v>
+        <v>124880283</v>
       </c>
       <c r="B43" t="n">
-        <v>91030</v>
+        <v>57513</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5038,21 +5053,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5062,10 +5077,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>434028</v>
+        <v>433376</v>
       </c>
       <c r="R43" t="n">
-        <v>6936084</v>
+        <v>6935695</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5098,6 +5113,11 @@
       <c r="AA43" t="inlineStr">
         <is>
           <t>2025-05-08</t>
+        </is>
+      </c>
+      <c r="AC43" t="inlineStr">
+        <is>
+          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5124,10 +5144,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>124880361</v>
+        <v>124880305</v>
       </c>
       <c r="B44" t="n">
-        <v>78810</v>
+        <v>57513</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5140,21 +5160,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5164,10 +5184,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>433311</v>
+        <v>434128</v>
       </c>
       <c r="R44" t="n">
-        <v>6935592</v>
+        <v>6936677</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5204,7 +5224,7 @@
       </c>
       <c r="AC44" t="inlineStr">
         <is>
-          <t>Rikligt</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5231,7 +5251,7 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>124880296</v>
+        <v>124880313</v>
       </c>
       <c r="B45" t="n">
         <v>57513</v>
@@ -5271,10 +5291,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>434019</v>
+        <v>434447</v>
       </c>
       <c r="R45" t="n">
-        <v>6936070</v>
+        <v>6936828</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5311,7 +5331,7 @@
       </c>
       <c r="AC45" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5338,10 +5358,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>124880319</v>
+        <v>124880355</v>
       </c>
       <c r="B46" t="n">
-        <v>57513</v>
+        <v>91030</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5354,21 +5374,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5378,10 +5398,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>434789</v>
+        <v>434478</v>
       </c>
       <c r="R46" t="n">
-        <v>6936947</v>
+        <v>6936874</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5414,11 +5434,6 @@
       <c r="AA46" t="inlineStr">
         <is>
           <t>2025-05-08</t>
-        </is>
-      </c>
-      <c r="AC46" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5445,10 +5460,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>124880364</v>
+        <v>124880350</v>
       </c>
       <c r="B47" t="n">
-        <v>78810</v>
+        <v>91030</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5461,21 +5476,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5485,10 +5500,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>433682</v>
+        <v>434118</v>
       </c>
       <c r="R47" t="n">
-        <v>6935955</v>
+        <v>6936187</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5521,11 +5536,6 @@
       <c r="AA47" t="inlineStr">
         <is>
           <t>2025-05-08</t>
-        </is>
-      </c>
-      <c r="AC47" t="inlineStr">
-        <is>
-          <t>Mycket rikligt</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5552,10 +5562,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>124880372</v>
+        <v>124880295</v>
       </c>
       <c r="B48" t="n">
-        <v>78810</v>
+        <v>57513</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5568,21 +5578,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5592,10 +5602,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>434443</v>
+        <v>433952</v>
       </c>
       <c r="R48" t="n">
-        <v>6936839</v>
+        <v>6936043</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5632,7 +5642,7 @@
       </c>
       <c r="AC48" t="inlineStr">
         <is>
-          <t>Mycket rikligt</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5659,10 +5669,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>124880346</v>
+        <v>124880237</v>
       </c>
       <c r="B49" t="n">
-        <v>91030</v>
+        <v>91012</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -5675,21 +5685,21 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>5432</v>
+        <v>1202</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5699,10 +5709,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>434113</v>
+        <v>433636</v>
       </c>
       <c r="R49" t="n">
-        <v>6936148</v>
+        <v>6935914</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5761,10 +5771,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>124880360</v>
+        <v>124880333</v>
       </c>
       <c r="B50" t="n">
-        <v>78810</v>
+        <v>91030</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -5777,21 +5787,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5801,10 +5811,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>433248</v>
+        <v>433376</v>
       </c>
       <c r="R50" t="n">
-        <v>6935491</v>
+        <v>6935725</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5837,11 +5847,6 @@
       <c r="AA50" t="inlineStr">
         <is>
           <t>2025-05-08</t>
-        </is>
-      </c>
-      <c r="AC50" t="inlineStr">
-        <is>
-          <t>Mycket rikligt</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -5868,10 +5873,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>124880353</v>
+        <v>124880326</v>
       </c>
       <c r="B51" t="n">
-        <v>91030</v>
+        <v>91008</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -5884,21 +5889,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>5432</v>
+        <v>1108</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5908,10 +5913,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>434173</v>
+        <v>434175</v>
       </c>
       <c r="R51" t="n">
-        <v>6936342</v>
+        <v>6936309</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5970,10 +5975,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>124880318</v>
+        <v>124880332</v>
       </c>
       <c r="B52" t="n">
-        <v>57513</v>
+        <v>91030</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -5986,21 +5991,21 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -6010,10 +6015,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>434664</v>
+        <v>433197</v>
       </c>
       <c r="R52" t="n">
-        <v>6936929</v>
+        <v>6935385</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6046,11 +6051,6 @@
       <c r="AA52" t="inlineStr">
         <is>
           <t>2025-05-08</t>
-        </is>
-      </c>
-      <c r="AC52" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD52" t="b">

--- a/artfynd/A 9618-2025 artfynd.xlsx
+++ b/artfynd/A 9618-2025 artfynd.xlsx
@@ -1026,7 +1026,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124880373</v>
+        <v>124880372</v>
       </c>
       <c r="B5" t="n">
         <v>78810</v>
@@ -1066,10 +1066,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>434482</v>
+        <v>434443</v>
       </c>
       <c r="R5" t="n">
-        <v>6936858</v>
+        <v>6936839</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1106,7 +1106,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Rikligt</t>
+          <t>Mycket rikligt</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1133,10 +1133,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124880365</v>
+        <v>124880275</v>
       </c>
       <c r="B6" t="n">
-        <v>78810</v>
+        <v>57513</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1149,21 +1149,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1173,10 +1173,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>433755</v>
+        <v>432954</v>
       </c>
       <c r="R6" t="n">
-        <v>6935995</v>
+        <v>6934982</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1213,7 +1213,7 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>Rikligt</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1240,10 +1240,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124880353</v>
+        <v>124880360</v>
       </c>
       <c r="B7" t="n">
-        <v>91030</v>
+        <v>78810</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1256,21 +1256,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1280,10 +1280,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>434173</v>
+        <v>433248</v>
       </c>
       <c r="R7" t="n">
-        <v>6936342</v>
+        <v>6935491</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1316,6 +1316,11 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-05-08</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Mycket rikligt</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1342,10 +1347,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124880337</v>
+        <v>124880314</v>
       </c>
       <c r="B8" t="n">
-        <v>91030</v>
+        <v>57513</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1358,21 +1363,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1382,10 +1387,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>433534</v>
+        <v>434484</v>
       </c>
       <c r="R8" t="n">
-        <v>6935858</v>
+        <v>6936850</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1418,6 +1423,11 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-05-08</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1444,7 +1454,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124880371</v>
+        <v>124880367</v>
       </c>
       <c r="B9" t="n">
         <v>78810</v>
@@ -1484,10 +1494,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>434167</v>
+        <v>433984</v>
       </c>
       <c r="R9" t="n">
-        <v>6936378</v>
+        <v>6936073</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1551,10 +1561,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124880361</v>
+        <v>124880310</v>
       </c>
       <c r="B10" t="n">
-        <v>78810</v>
+        <v>57513</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1567,21 +1577,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1591,10 +1601,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>433311</v>
+        <v>434385</v>
       </c>
       <c r="R10" t="n">
-        <v>6935592</v>
+        <v>6936814</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1631,7 +1641,7 @@
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>Rikligt</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1658,10 +1668,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124880359</v>
+        <v>124880313</v>
       </c>
       <c r="B11" t="n">
-        <v>78810</v>
+        <v>57513</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1674,21 +1684,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1698,10 +1708,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>433093</v>
+        <v>434447</v>
       </c>
       <c r="R11" t="n">
-        <v>6935150</v>
+        <v>6936828</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1738,7 +1748,7 @@
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>Rikligt</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1765,7 +1775,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>124880278</v>
+        <v>124880288</v>
       </c>
       <c r="B12" t="n">
         <v>57513</v>
@@ -1805,10 +1815,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>433331</v>
+        <v>433505</v>
       </c>
       <c r="R12" t="n">
-        <v>6935597</v>
+        <v>6935809</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1872,10 +1882,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>124880315</v>
+        <v>124880337</v>
       </c>
       <c r="B13" t="n">
-        <v>57513</v>
+        <v>91030</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1888,21 +1898,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1912,10 +1922,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>434466</v>
+        <v>433534</v>
       </c>
       <c r="R13" t="n">
-        <v>6936862</v>
+        <v>6935858</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1948,11 +1958,6 @@
       <c r="AA13" t="inlineStr">
         <is>
           <t>2025-05-08</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1979,7 +1984,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>124880319</v>
+        <v>124880278</v>
       </c>
       <c r="B14" t="n">
         <v>57513</v>
@@ -2019,10 +2024,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>434789</v>
+        <v>433331</v>
       </c>
       <c r="R14" t="n">
-        <v>6936947</v>
+        <v>6935597</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2086,7 +2091,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>124880338</v>
+        <v>124880343</v>
       </c>
       <c r="B15" t="n">
         <v>91030</v>
@@ -2126,10 +2131,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>433585</v>
+        <v>433952</v>
       </c>
       <c r="R15" t="n">
-        <v>6935882</v>
+        <v>6936054</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2188,10 +2193,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>124880367</v>
+        <v>124880286</v>
       </c>
       <c r="B16" t="n">
-        <v>78810</v>
+        <v>57513</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2204,21 +2209,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2228,10 +2233,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>433984</v>
+        <v>433434</v>
       </c>
       <c r="R16" t="n">
-        <v>6936073</v>
+        <v>6935749</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2268,7 +2273,7 @@
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>Mycket rikligt</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2295,10 +2300,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>124880372</v>
+        <v>124880296</v>
       </c>
       <c r="B17" t="n">
-        <v>78810</v>
+        <v>57513</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2311,21 +2316,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2335,10 +2340,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>434443</v>
+        <v>434019</v>
       </c>
       <c r="R17" t="n">
-        <v>6936839</v>
+        <v>6936070</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2375,7 +2380,7 @@
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>Mycket rikligt</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2509,7 +2514,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>124880346</v>
+        <v>124880340</v>
       </c>
       <c r="B19" t="n">
         <v>91030</v>
@@ -2549,10 +2554,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>434113</v>
+        <v>433661</v>
       </c>
       <c r="R19" t="n">
-        <v>6936148</v>
+        <v>6935941</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2611,10 +2616,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>124880299</v>
+        <v>124880237</v>
       </c>
       <c r="B20" t="n">
-        <v>57513</v>
+        <v>91012</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2627,21 +2632,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2651,10 +2656,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>434112</v>
+        <v>433636</v>
       </c>
       <c r="R20" t="n">
-        <v>6936130</v>
+        <v>6935914</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2687,11 +2692,6 @@
       <c r="AA20" t="inlineStr">
         <is>
           <t>2025-05-08</t>
-        </is>
-      </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2718,7 +2718,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>124880310</v>
+        <v>124880283</v>
       </c>
       <c r="B21" t="n">
         <v>57513</v>
@@ -2758,10 +2758,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>434385</v>
+        <v>433376</v>
       </c>
       <c r="R21" t="n">
-        <v>6936814</v>
+        <v>6935695</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2798,7 +2798,7 @@
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2825,7 +2825,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>124880286</v>
+        <v>124880305</v>
       </c>
       <c r="B22" t="n">
         <v>57513</v>
@@ -2865,10 +2865,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>433434</v>
+        <v>434128</v>
       </c>
       <c r="R22" t="n">
-        <v>6935749</v>
+        <v>6936677</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2905,7 +2905,7 @@
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2932,7 +2932,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>124880316</v>
+        <v>124880318</v>
       </c>
       <c r="B23" t="n">
         <v>57513</v>
@@ -2972,10 +2972,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>434532</v>
+        <v>434664</v>
       </c>
       <c r="R23" t="n">
-        <v>6936893</v>
+        <v>6936929</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3039,10 +3039,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>124880369</v>
+        <v>124880355</v>
       </c>
       <c r="B24" t="n">
-        <v>78810</v>
+        <v>91030</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3055,21 +3055,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3079,10 +3079,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>434091</v>
+        <v>434478</v>
       </c>
       <c r="R24" t="n">
-        <v>6936122</v>
+        <v>6936874</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3115,11 +3115,6 @@
       <c r="AA24" t="inlineStr">
         <is>
           <t>2025-05-08</t>
-        </is>
-      </c>
-      <c r="AC24" t="inlineStr">
-        <is>
-          <t>Mycket rikligt</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3146,10 +3141,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>124880317</v>
+        <v>124880350</v>
       </c>
       <c r="B25" t="n">
-        <v>57513</v>
+        <v>91030</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3162,21 +3157,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3186,10 +3181,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>434538</v>
+        <v>434118</v>
       </c>
       <c r="R25" t="n">
-        <v>6936895</v>
+        <v>6936187</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3222,11 +3217,6 @@
       <c r="AA25" t="inlineStr">
         <is>
           <t>2025-05-08</t>
-        </is>
-      </c>
-      <c r="AC25" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3253,10 +3243,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>124880331</v>
+        <v>124880359</v>
       </c>
       <c r="B26" t="n">
-        <v>91030</v>
+        <v>78810</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3269,21 +3259,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3293,10 +3283,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>433193</v>
+        <v>433093</v>
       </c>
       <c r="R26" t="n">
-        <v>6935352</v>
+        <v>6935150</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3329,6 +3319,11 @@
       <c r="AA26" t="inlineStr">
         <is>
           <t>2025-05-08</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3355,10 +3350,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>124880343</v>
+        <v>124880303</v>
       </c>
       <c r="B27" t="n">
-        <v>91030</v>
+        <v>57513</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3371,21 +3366,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3395,10 +3390,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>433952</v>
+        <v>434113</v>
       </c>
       <c r="R27" t="n">
-        <v>6936054</v>
+        <v>6936181</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3431,6 +3426,11 @@
       <c r="AA27" t="inlineStr">
         <is>
           <t>2025-05-08</t>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3457,7 +3457,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>124880344</v>
+        <v>124880346</v>
       </c>
       <c r="B28" t="n">
         <v>91030</v>
@@ -3497,10 +3497,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>434028</v>
+        <v>434113</v>
       </c>
       <c r="R28" t="n">
-        <v>6936084</v>
+        <v>6936148</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3559,7 +3559,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>124880329</v>
+        <v>124880333</v>
       </c>
       <c r="B29" t="n">
         <v>91030</v>
@@ -3599,10 +3599,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>433106</v>
+        <v>433376</v>
       </c>
       <c r="R29" t="n">
-        <v>6935174</v>
+        <v>6935725</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3661,10 +3661,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>124880296</v>
+        <v>124880365</v>
       </c>
       <c r="B30" t="n">
-        <v>57513</v>
+        <v>78810</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3677,21 +3677,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3701,10 +3701,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>434019</v>
+        <v>433755</v>
       </c>
       <c r="R30" t="n">
-        <v>6936070</v>
+        <v>6935995</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3741,7 +3741,7 @@
       </c>
       <c r="AC30" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3768,7 +3768,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>124880314</v>
+        <v>124880290</v>
       </c>
       <c r="B31" t="n">
         <v>57513</v>
@@ -3808,10 +3808,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>434484</v>
+        <v>433820</v>
       </c>
       <c r="R31" t="n">
-        <v>6936850</v>
+        <v>6936000</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3875,7 +3875,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>124880318</v>
+        <v>124880315</v>
       </c>
       <c r="B32" t="n">
         <v>57513</v>
@@ -3915,10 +3915,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>434664</v>
+        <v>434466</v>
       </c>
       <c r="R32" t="n">
-        <v>6936929</v>
+        <v>6936862</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3982,10 +3982,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>124880324</v>
+        <v>124880332</v>
       </c>
       <c r="B33" t="n">
-        <v>91008</v>
+        <v>91030</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -3998,21 +3998,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>1108</v>
+        <v>5432</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4022,10 +4022,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>433261</v>
+        <v>433197</v>
       </c>
       <c r="R33" t="n">
-        <v>6935504</v>
+        <v>6935385</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4084,10 +4084,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>124880340</v>
+        <v>124880369</v>
       </c>
       <c r="B34" t="n">
-        <v>91030</v>
+        <v>78810</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4100,21 +4100,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4124,10 +4124,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>433661</v>
+        <v>434091</v>
       </c>
       <c r="R34" t="n">
-        <v>6935941</v>
+        <v>6936122</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4160,6 +4160,11 @@
       <c r="AA34" t="inlineStr">
         <is>
           <t>2025-05-08</t>
+        </is>
+      </c>
+      <c r="AC34" t="inlineStr">
+        <is>
+          <t>Mycket rikligt</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4186,10 +4191,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>124880345</v>
+        <v>124880364</v>
       </c>
       <c r="B35" t="n">
-        <v>91030</v>
+        <v>78810</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4202,21 +4207,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4226,10 +4231,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>434057</v>
+        <v>433682</v>
       </c>
       <c r="R35" t="n">
-        <v>6936091</v>
+        <v>6935955</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4262,6 +4267,11 @@
       <c r="AA35" t="inlineStr">
         <is>
           <t>2025-05-08</t>
+        </is>
+      </c>
+      <c r="AC35" t="inlineStr">
+        <is>
+          <t>Mycket rikligt</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4288,10 +4298,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>124880275</v>
+        <v>124880324</v>
       </c>
       <c r="B36" t="n">
-        <v>57513</v>
+        <v>91008</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4304,21 +4314,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>100109</v>
+        <v>1108</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4328,10 +4338,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>432954</v>
+        <v>433261</v>
       </c>
       <c r="R36" t="n">
-        <v>6934982</v>
+        <v>6935504</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4364,11 +4374,6 @@
       <c r="AA36" t="inlineStr">
         <is>
           <t>2025-05-08</t>
-        </is>
-      </c>
-      <c r="AC36" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4395,10 +4400,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>124880358</v>
+        <v>124880329</v>
       </c>
       <c r="B37" t="n">
-        <v>78810</v>
+        <v>91030</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4411,21 +4416,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4435,10 +4440,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>433076</v>
+        <v>433106</v>
       </c>
       <c r="R37" t="n">
-        <v>6935108</v>
+        <v>6935174</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4471,11 +4476,6 @@
       <c r="AA37" t="inlineStr">
         <is>
           <t>2025-05-08</t>
-        </is>
-      </c>
-      <c r="AC37" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4502,10 +4502,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>124880303</v>
+        <v>124880326</v>
       </c>
       <c r="B38" t="n">
-        <v>57513</v>
+        <v>91008</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4518,21 +4518,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>100109</v>
+        <v>1108</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4542,10 +4542,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>434113</v>
+        <v>434175</v>
       </c>
       <c r="R38" t="n">
-        <v>6936181</v>
+        <v>6936309</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4578,11 +4578,6 @@
       <c r="AA38" t="inlineStr">
         <is>
           <t>2025-05-08</t>
-        </is>
-      </c>
-      <c r="AC38" t="inlineStr">
-        <is>
-          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4609,10 +4604,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>124880360</v>
+        <v>124880353</v>
       </c>
       <c r="B39" t="n">
-        <v>78810</v>
+        <v>91030</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4625,21 +4620,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4649,10 +4644,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>433248</v>
+        <v>434173</v>
       </c>
       <c r="R39" t="n">
-        <v>6935491</v>
+        <v>6936342</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4685,11 +4680,6 @@
       <c r="AA39" t="inlineStr">
         <is>
           <t>2025-05-08</t>
-        </is>
-      </c>
-      <c r="AC39" t="inlineStr">
-        <is>
-          <t>Mycket rikligt</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4716,7 +4706,7 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>124880364</v>
+        <v>124880361</v>
       </c>
       <c r="B40" t="n">
         <v>78810</v>
@@ -4756,10 +4746,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>433682</v>
+        <v>433311</v>
       </c>
       <c r="R40" t="n">
-        <v>6935955</v>
+        <v>6935592</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4796,7 +4786,7 @@
       </c>
       <c r="AC40" t="inlineStr">
         <is>
-          <t>Mycket rikligt</t>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4823,7 +4813,7 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>124880290</v>
+        <v>124880295</v>
       </c>
       <c r="B41" t="n">
         <v>57513</v>
@@ -4863,10 +4853,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>433820</v>
+        <v>433952</v>
       </c>
       <c r="R41" t="n">
-        <v>6936000</v>
+        <v>6936043</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4930,7 +4920,7 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>124880288</v>
+        <v>124880316</v>
       </c>
       <c r="B42" t="n">
         <v>57513</v>
@@ -4970,10 +4960,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>433505</v>
+        <v>434532</v>
       </c>
       <c r="R42" t="n">
-        <v>6935809</v>
+        <v>6936893</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5037,10 +5027,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>124880283</v>
+        <v>124880358</v>
       </c>
       <c r="B43" t="n">
-        <v>57513</v>
+        <v>78810</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5053,21 +5043,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5077,10 +5067,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>433376</v>
+        <v>433076</v>
       </c>
       <c r="R43" t="n">
-        <v>6935695</v>
+        <v>6935108</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5117,7 +5107,7 @@
       </c>
       <c r="AC43" t="inlineStr">
         <is>
-          <t>Ringhack färska</t>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5144,10 +5134,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>124880305</v>
+        <v>124880371</v>
       </c>
       <c r="B44" t="n">
-        <v>57513</v>
+        <v>78810</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5160,21 +5150,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5184,10 +5174,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>434128</v>
+        <v>434167</v>
       </c>
       <c r="R44" t="n">
-        <v>6936677</v>
+        <v>6936378</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5224,7 +5214,7 @@
       </c>
       <c r="AC44" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Mycket rikligt</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5251,7 +5241,7 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>124880313</v>
+        <v>124880299</v>
       </c>
       <c r="B45" t="n">
         <v>57513</v>
@@ -5291,10 +5281,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>434447</v>
+        <v>434112</v>
       </c>
       <c r="R45" t="n">
-        <v>6936828</v>
+        <v>6936130</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5331,7 +5321,7 @@
       </c>
       <c r="AC45" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5358,10 +5348,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>124880355</v>
+        <v>124880319</v>
       </c>
       <c r="B46" t="n">
-        <v>91030</v>
+        <v>57513</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5374,21 +5364,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5398,10 +5388,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>434478</v>
+        <v>434789</v>
       </c>
       <c r="R46" t="n">
-        <v>6936874</v>
+        <v>6936947</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5434,6 +5424,11 @@
       <c r="AA46" t="inlineStr">
         <is>
           <t>2025-05-08</t>
+        </is>
+      </c>
+      <c r="AC46" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5460,7 +5455,7 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>124880350</v>
+        <v>124880331</v>
       </c>
       <c r="B47" t="n">
         <v>91030</v>
@@ -5500,10 +5495,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>434118</v>
+        <v>433193</v>
       </c>
       <c r="R47" t="n">
-        <v>6936187</v>
+        <v>6935352</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5562,10 +5557,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>124880295</v>
+        <v>124880373</v>
       </c>
       <c r="B48" t="n">
-        <v>57513</v>
+        <v>78810</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5578,21 +5573,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5602,10 +5597,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>433952</v>
+        <v>434482</v>
       </c>
       <c r="R48" t="n">
-        <v>6936043</v>
+        <v>6936858</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5642,7 +5637,7 @@
       </c>
       <c r="AC48" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5669,10 +5664,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>124880237</v>
+        <v>124880344</v>
       </c>
       <c r="B49" t="n">
-        <v>91012</v>
+        <v>91030</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -5685,21 +5680,21 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>1202</v>
+        <v>5432</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5709,10 +5704,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>433636</v>
+        <v>434028</v>
       </c>
       <c r="R49" t="n">
-        <v>6935914</v>
+        <v>6936084</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5771,7 +5766,7 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>124880333</v>
+        <v>124880345</v>
       </c>
       <c r="B50" t="n">
         <v>91030</v>
@@ -5811,10 +5806,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>433376</v>
+        <v>434057</v>
       </c>
       <c r="R50" t="n">
-        <v>6935725</v>
+        <v>6936091</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5873,10 +5868,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>124880326</v>
+        <v>124880338</v>
       </c>
       <c r="B51" t="n">
-        <v>91008</v>
+        <v>91030</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -5889,21 +5884,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>1108</v>
+        <v>5432</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5913,10 +5908,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>434175</v>
+        <v>433585</v>
       </c>
       <c r="R51" t="n">
-        <v>6936309</v>
+        <v>6935882</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5975,10 +5970,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>124880332</v>
+        <v>124880317</v>
       </c>
       <c r="B52" t="n">
-        <v>91030</v>
+        <v>57513</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -5991,21 +5986,21 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -6015,10 +6010,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>433197</v>
+        <v>434538</v>
       </c>
       <c r="R52" t="n">
-        <v>6935385</v>
+        <v>6936895</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6051,6 +6046,11 @@
       <c r="AA52" t="inlineStr">
         <is>
           <t>2025-05-08</t>
+        </is>
+      </c>
+      <c r="AC52" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD52" t="b">

--- a/artfynd/A 9618-2025 artfynd.xlsx
+++ b/artfynd/A 9618-2025 artfynd.xlsx
@@ -1026,10 +1026,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124880372</v>
+        <v>124880275</v>
       </c>
       <c r="B5" t="n">
-        <v>78810</v>
+        <v>57513</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1042,21 +1042,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1066,10 +1066,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>434443</v>
+        <v>432954</v>
       </c>
       <c r="R5" t="n">
-        <v>6936839</v>
+        <v>6934982</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1106,7 +1106,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Mycket rikligt</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1133,10 +1133,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124880275</v>
+        <v>124880372</v>
       </c>
       <c r="B6" t="n">
-        <v>57513</v>
+        <v>78810</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1149,21 +1149,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1173,10 +1173,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>432954</v>
+        <v>434443</v>
       </c>
       <c r="R6" t="n">
-        <v>6934982</v>
+        <v>6936839</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1213,7 +1213,7 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Mycket rikligt</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1454,10 +1454,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124880367</v>
+        <v>124880313</v>
       </c>
       <c r="B9" t="n">
-        <v>78810</v>
+        <v>57513</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1470,21 +1470,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1494,10 +1494,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>433984</v>
+        <v>434447</v>
       </c>
       <c r="R9" t="n">
-        <v>6936073</v>
+        <v>6936828</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1534,7 +1534,7 @@
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>Mycket rikligt</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1561,10 +1561,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124880310</v>
+        <v>124880367</v>
       </c>
       <c r="B10" t="n">
-        <v>57513</v>
+        <v>78810</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1577,21 +1577,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1601,10 +1601,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>434385</v>
+        <v>433984</v>
       </c>
       <c r="R10" t="n">
-        <v>6936814</v>
+        <v>6936073</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1641,7 +1641,7 @@
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Mycket rikligt</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1668,7 +1668,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124880313</v>
+        <v>124880310</v>
       </c>
       <c r="B11" t="n">
         <v>57513</v>
@@ -1708,10 +1708,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>434447</v>
+        <v>434385</v>
       </c>
       <c r="R11" t="n">
-        <v>6936828</v>
+        <v>6936814</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1748,7 +1748,7 @@
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -2091,10 +2091,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>124880343</v>
+        <v>124880296</v>
       </c>
       <c r="B15" t="n">
-        <v>91030</v>
+        <v>57513</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2107,21 +2107,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2131,10 +2131,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>433952</v>
+        <v>434019</v>
       </c>
       <c r="R15" t="n">
-        <v>6936054</v>
+        <v>6936070</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2167,6 +2167,11 @@
       <c r="AA15" t="inlineStr">
         <is>
           <t>2025-05-08</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2193,10 +2198,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>124880286</v>
+        <v>124880343</v>
       </c>
       <c r="B16" t="n">
-        <v>57513</v>
+        <v>91030</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2209,21 +2214,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2233,10 +2238,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>433434</v>
+        <v>433952</v>
       </c>
       <c r="R16" t="n">
-        <v>6935749</v>
+        <v>6936054</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2269,11 +2274,6 @@
       <c r="AA16" t="inlineStr">
         <is>
           <t>2025-05-08</t>
-        </is>
-      </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2300,7 +2300,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>124880296</v>
+        <v>124880286</v>
       </c>
       <c r="B17" t="n">
         <v>57513</v>
@@ -2340,10 +2340,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>434019</v>
+        <v>433434</v>
       </c>
       <c r="R17" t="n">
-        <v>6936070</v>
+        <v>6935749</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2380,7 +2380,7 @@
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2718,7 +2718,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>124880283</v>
+        <v>124880318</v>
       </c>
       <c r="B21" t="n">
         <v>57513</v>
@@ -2758,10 +2758,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>433376</v>
+        <v>434664</v>
       </c>
       <c r="R21" t="n">
-        <v>6935695</v>
+        <v>6936929</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2798,7 +2798,7 @@
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>Ringhack färska</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2825,7 +2825,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>124880305</v>
+        <v>124880283</v>
       </c>
       <c r="B22" t="n">
         <v>57513</v>
@@ -2865,10 +2865,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>434128</v>
+        <v>433376</v>
       </c>
       <c r="R22" t="n">
-        <v>6936677</v>
+        <v>6935695</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2905,7 +2905,7 @@
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2932,7 +2932,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>124880318</v>
+        <v>124880305</v>
       </c>
       <c r="B23" t="n">
         <v>57513</v>
@@ -2972,10 +2972,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>434664</v>
+        <v>434128</v>
       </c>
       <c r="R23" t="n">
-        <v>6936929</v>
+        <v>6936677</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -4298,10 +4298,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>124880324</v>
+        <v>124880361</v>
       </c>
       <c r="B36" t="n">
-        <v>91008</v>
+        <v>78810</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4314,21 +4314,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>1108</v>
+        <v>6425</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4338,10 +4338,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>433261</v>
+        <v>433311</v>
       </c>
       <c r="R36" t="n">
-        <v>6935504</v>
+        <v>6935592</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4374,6 +4374,11 @@
       <c r="AA36" t="inlineStr">
         <is>
           <t>2025-05-08</t>
+        </is>
+      </c>
+      <c r="AC36" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4400,10 +4405,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>124880329</v>
+        <v>124880295</v>
       </c>
       <c r="B37" t="n">
-        <v>91030</v>
+        <v>57513</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4416,21 +4421,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4440,10 +4445,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>433106</v>
+        <v>433952</v>
       </c>
       <c r="R37" t="n">
-        <v>6935174</v>
+        <v>6936043</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4476,6 +4481,11 @@
       <c r="AA37" t="inlineStr">
         <is>
           <t>2025-05-08</t>
+        </is>
+      </c>
+      <c r="AC37" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4502,10 +4512,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>124880326</v>
+        <v>124880316</v>
       </c>
       <c r="B38" t="n">
-        <v>91008</v>
+        <v>57513</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4518,21 +4528,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>1108</v>
+        <v>100109</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4542,10 +4552,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>434175</v>
+        <v>434532</v>
       </c>
       <c r="R38" t="n">
-        <v>6936309</v>
+        <v>6936893</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4578,6 +4588,11 @@
       <c r="AA38" t="inlineStr">
         <is>
           <t>2025-05-08</t>
+        </is>
+      </c>
+      <c r="AC38" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4604,10 +4619,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>124880353</v>
+        <v>124880324</v>
       </c>
       <c r="B39" t="n">
-        <v>91030</v>
+        <v>91008</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4620,21 +4635,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>5432</v>
+        <v>1108</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4644,10 +4659,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>434173</v>
+        <v>433261</v>
       </c>
       <c r="R39" t="n">
-        <v>6936342</v>
+        <v>6935504</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4706,10 +4721,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>124880361</v>
+        <v>124880329</v>
       </c>
       <c r="B40" t="n">
-        <v>78810</v>
+        <v>91030</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4722,21 +4737,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4746,10 +4761,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>433311</v>
+        <v>433106</v>
       </c>
       <c r="R40" t="n">
-        <v>6935592</v>
+        <v>6935174</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4782,11 +4797,6 @@
       <c r="AA40" t="inlineStr">
         <is>
           <t>2025-05-08</t>
-        </is>
-      </c>
-      <c r="AC40" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4813,10 +4823,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>124880295</v>
+        <v>124880326</v>
       </c>
       <c r="B41" t="n">
-        <v>57513</v>
+        <v>91008</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -4829,21 +4839,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>100109</v>
+        <v>1108</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4853,10 +4863,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>433952</v>
+        <v>434175</v>
       </c>
       <c r="R41" t="n">
-        <v>6936043</v>
+        <v>6936309</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4889,11 +4899,6 @@
       <c r="AA41" t="inlineStr">
         <is>
           <t>2025-05-08</t>
-        </is>
-      </c>
-      <c r="AC41" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4920,10 +4925,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>124880316</v>
+        <v>124880353</v>
       </c>
       <c r="B42" t="n">
-        <v>57513</v>
+        <v>91030</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -4936,21 +4941,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4960,10 +4965,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>434532</v>
+        <v>434173</v>
       </c>
       <c r="R42" t="n">
-        <v>6936893</v>
+        <v>6936342</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4996,11 +5001,6 @@
       <c r="AA42" t="inlineStr">
         <is>
           <t>2025-05-08</t>
-        </is>
-      </c>
-      <c r="AC42" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD42" t="b">

--- a/artfynd/A 9618-2025 artfynd.xlsx
+++ b/artfynd/A 9618-2025 artfynd.xlsx
@@ -1026,10 +1026,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124880275</v>
+        <v>124880372</v>
       </c>
       <c r="B5" t="n">
-        <v>57513</v>
+        <v>78810</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1042,21 +1042,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1066,10 +1066,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>432954</v>
+        <v>434443</v>
       </c>
       <c r="R5" t="n">
-        <v>6934982</v>
+        <v>6936839</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1106,7 +1106,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Mycket rikligt</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1133,10 +1133,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124880372</v>
+        <v>124880275</v>
       </c>
       <c r="B6" t="n">
-        <v>78810</v>
+        <v>57513</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1149,21 +1149,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1173,10 +1173,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>434443</v>
+        <v>432954</v>
       </c>
       <c r="R6" t="n">
-        <v>6936839</v>
+        <v>6934982</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1213,7 +1213,7 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>Mycket rikligt</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1454,10 +1454,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124880313</v>
+        <v>124880367</v>
       </c>
       <c r="B9" t="n">
-        <v>57513</v>
+        <v>78810</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1470,21 +1470,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1494,10 +1494,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>434447</v>
+        <v>433984</v>
       </c>
       <c r="R9" t="n">
-        <v>6936828</v>
+        <v>6936073</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1534,7 +1534,7 @@
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Mycket rikligt</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1561,10 +1561,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124880367</v>
+        <v>124880310</v>
       </c>
       <c r="B10" t="n">
-        <v>78810</v>
+        <v>57513</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1577,21 +1577,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1601,10 +1601,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>433984</v>
+        <v>434385</v>
       </c>
       <c r="R10" t="n">
-        <v>6936073</v>
+        <v>6936814</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1641,7 +1641,7 @@
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>Mycket rikligt</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1668,7 +1668,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124880310</v>
+        <v>124880313</v>
       </c>
       <c r="B11" t="n">
         <v>57513</v>
@@ -1708,10 +1708,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>434385</v>
+        <v>434447</v>
       </c>
       <c r="R11" t="n">
-        <v>6936814</v>
+        <v>6936828</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1748,7 +1748,7 @@
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1882,10 +1882,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>124880337</v>
+        <v>124880278</v>
       </c>
       <c r="B13" t="n">
-        <v>91030</v>
+        <v>57513</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1898,21 +1898,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1922,10 +1922,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>433534</v>
+        <v>433331</v>
       </c>
       <c r="R13" t="n">
-        <v>6935858</v>
+        <v>6935597</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1958,6 +1958,11 @@
       <c r="AA13" t="inlineStr">
         <is>
           <t>2025-05-08</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1984,10 +1989,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>124880278</v>
+        <v>124880337</v>
       </c>
       <c r="B14" t="n">
-        <v>57513</v>
+        <v>91030</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2000,21 +2005,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2024,10 +2029,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>433331</v>
+        <v>433534</v>
       </c>
       <c r="R14" t="n">
-        <v>6935597</v>
+        <v>6935858</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2060,11 +2065,6 @@
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-05-08</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2091,10 +2091,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>124880296</v>
+        <v>124880343</v>
       </c>
       <c r="B15" t="n">
-        <v>57513</v>
+        <v>91030</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2107,21 +2107,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2131,10 +2131,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>434019</v>
+        <v>433952</v>
       </c>
       <c r="R15" t="n">
-        <v>6936070</v>
+        <v>6936054</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2167,11 +2167,6 @@
       <c r="AA15" t="inlineStr">
         <is>
           <t>2025-05-08</t>
-        </is>
-      </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2198,10 +2193,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>124880343</v>
+        <v>124880286</v>
       </c>
       <c r="B16" t="n">
-        <v>91030</v>
+        <v>57513</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2214,21 +2209,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2238,10 +2233,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>433952</v>
+        <v>433434</v>
       </c>
       <c r="R16" t="n">
-        <v>6936054</v>
+        <v>6935749</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2274,6 +2269,11 @@
       <c r="AA16" t="inlineStr">
         <is>
           <t>2025-05-08</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2300,7 +2300,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>124880286</v>
+        <v>124880296</v>
       </c>
       <c r="B17" t="n">
         <v>57513</v>
@@ -2340,10 +2340,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>433434</v>
+        <v>434019</v>
       </c>
       <c r="R17" t="n">
-        <v>6935749</v>
+        <v>6936070</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2380,7 +2380,7 @@
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -4298,10 +4298,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>124880361</v>
+        <v>124880324</v>
       </c>
       <c r="B36" t="n">
-        <v>78810</v>
+        <v>91008</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4314,21 +4314,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6425</v>
+        <v>1108</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4338,10 +4338,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>433311</v>
+        <v>433261</v>
       </c>
       <c r="R36" t="n">
-        <v>6935592</v>
+        <v>6935504</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4374,11 +4374,6 @@
       <c r="AA36" t="inlineStr">
         <is>
           <t>2025-05-08</t>
-        </is>
-      </c>
-      <c r="AC36" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4405,10 +4400,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>124880295</v>
+        <v>124880329</v>
       </c>
       <c r="B37" t="n">
-        <v>57513</v>
+        <v>91030</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4421,21 +4416,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4445,10 +4440,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>433952</v>
+        <v>433106</v>
       </c>
       <c r="R37" t="n">
-        <v>6936043</v>
+        <v>6935174</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4481,11 +4476,6 @@
       <c r="AA37" t="inlineStr">
         <is>
           <t>2025-05-08</t>
-        </is>
-      </c>
-      <c r="AC37" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4512,10 +4502,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>124880316</v>
+        <v>124880326</v>
       </c>
       <c r="B38" t="n">
-        <v>57513</v>
+        <v>91008</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4528,21 +4518,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>100109</v>
+        <v>1108</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4552,10 +4542,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>434532</v>
+        <v>434175</v>
       </c>
       <c r="R38" t="n">
-        <v>6936893</v>
+        <v>6936309</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4588,11 +4578,6 @@
       <c r="AA38" t="inlineStr">
         <is>
           <t>2025-05-08</t>
-        </is>
-      </c>
-      <c r="AC38" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4619,10 +4604,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>124880324</v>
+        <v>124880353</v>
       </c>
       <c r="B39" t="n">
-        <v>91008</v>
+        <v>91030</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4635,21 +4620,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>1108</v>
+        <v>5432</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4659,10 +4644,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>433261</v>
+        <v>434173</v>
       </c>
       <c r="R39" t="n">
-        <v>6935504</v>
+        <v>6936342</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4721,10 +4706,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>124880329</v>
+        <v>124880361</v>
       </c>
       <c r="B40" t="n">
-        <v>91030</v>
+        <v>78810</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4737,21 +4722,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4761,10 +4746,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>433106</v>
+        <v>433311</v>
       </c>
       <c r="R40" t="n">
-        <v>6935174</v>
+        <v>6935592</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4797,6 +4782,11 @@
       <c r="AA40" t="inlineStr">
         <is>
           <t>2025-05-08</t>
+        </is>
+      </c>
+      <c r="AC40" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4823,10 +4813,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>124880326</v>
+        <v>124880295</v>
       </c>
       <c r="B41" t="n">
-        <v>91008</v>
+        <v>57513</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -4839,21 +4829,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>1108</v>
+        <v>100109</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4863,10 +4853,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>434175</v>
+        <v>433952</v>
       </c>
       <c r="R41" t="n">
-        <v>6936309</v>
+        <v>6936043</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4899,6 +4889,11 @@
       <c r="AA41" t="inlineStr">
         <is>
           <t>2025-05-08</t>
+        </is>
+      </c>
+      <c r="AC41" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4925,10 +4920,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>124880353</v>
+        <v>124880316</v>
       </c>
       <c r="B42" t="n">
-        <v>91030</v>
+        <v>57513</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -4941,21 +4936,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4965,10 +4960,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>434173</v>
+        <v>434532</v>
       </c>
       <c r="R42" t="n">
-        <v>6936342</v>
+        <v>6936893</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5001,6 +4996,11 @@
       <c r="AA42" t="inlineStr">
         <is>
           <t>2025-05-08</t>
+        </is>
+      </c>
+      <c r="AC42" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5664,10 +5664,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>124880344</v>
+        <v>124880317</v>
       </c>
       <c r="B49" t="n">
-        <v>91030</v>
+        <v>57513</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -5680,21 +5680,21 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5704,10 +5704,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>434028</v>
+        <v>434538</v>
       </c>
       <c r="R49" t="n">
-        <v>6936084</v>
+        <v>6936895</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5740,6 +5740,11 @@
       <c r="AA49" t="inlineStr">
         <is>
           <t>2025-05-08</t>
+        </is>
+      </c>
+      <c r="AC49" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5766,7 +5771,7 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>124880345</v>
+        <v>124880344</v>
       </c>
       <c r="B50" t="n">
         <v>91030</v>
@@ -5806,10 +5811,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>434057</v>
+        <v>434028</v>
       </c>
       <c r="R50" t="n">
-        <v>6936091</v>
+        <v>6936084</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5868,7 +5873,7 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>124880338</v>
+        <v>124880345</v>
       </c>
       <c r="B51" t="n">
         <v>91030</v>
@@ -5908,10 +5913,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>433585</v>
+        <v>434057</v>
       </c>
       <c r="R51" t="n">
-        <v>6935882</v>
+        <v>6936091</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5970,10 +5975,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>124880317</v>
+        <v>124880338</v>
       </c>
       <c r="B52" t="n">
-        <v>57513</v>
+        <v>91030</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -5986,21 +5991,21 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -6010,10 +6015,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>434538</v>
+        <v>433585</v>
       </c>
       <c r="R52" t="n">
-        <v>6936895</v>
+        <v>6935882</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6046,11 +6051,6 @@
       <c r="AA52" t="inlineStr">
         <is>
           <t>2025-05-08</t>
-        </is>
-      </c>
-      <c r="AC52" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD52" t="b">

--- a/artfynd/A 9618-2025 artfynd.xlsx
+++ b/artfynd/A 9618-2025 artfynd.xlsx
@@ -1026,10 +1026,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124880372</v>
+        <v>124880324</v>
       </c>
       <c r="B5" t="n">
-        <v>78810</v>
+        <v>91008</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1042,21 +1042,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>1108</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1066,10 +1066,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>434443</v>
+        <v>433261</v>
       </c>
       <c r="R5" t="n">
-        <v>6936839</v>
+        <v>6935504</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1102,11 +1102,6 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-05-08</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Mycket rikligt</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1133,10 +1128,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124880275</v>
+        <v>124880365</v>
       </c>
       <c r="B6" t="n">
-        <v>57513</v>
+        <v>78810</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1149,21 +1144,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1173,10 +1168,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>432954</v>
+        <v>433755</v>
       </c>
       <c r="R6" t="n">
-        <v>6934982</v>
+        <v>6935995</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1213,7 +1208,7 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1240,10 +1235,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124880360</v>
+        <v>124880353</v>
       </c>
       <c r="B7" t="n">
-        <v>78810</v>
+        <v>91030</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1256,21 +1251,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1280,10 +1275,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>433248</v>
+        <v>434173</v>
       </c>
       <c r="R7" t="n">
-        <v>6935491</v>
+        <v>6936342</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1316,11 +1311,6 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-05-08</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Mycket rikligt</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1347,7 +1337,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124880314</v>
+        <v>124880295</v>
       </c>
       <c r="B8" t="n">
         <v>57513</v>
@@ -1387,10 +1377,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>434484</v>
+        <v>433952</v>
       </c>
       <c r="R8" t="n">
-        <v>6936850</v>
+        <v>6936043</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1454,10 +1444,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124880367</v>
+        <v>124880278</v>
       </c>
       <c r="B9" t="n">
-        <v>78810</v>
+        <v>57513</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1470,21 +1460,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1494,10 +1484,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>433984</v>
+        <v>433331</v>
       </c>
       <c r="R9" t="n">
-        <v>6936073</v>
+        <v>6935597</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1534,7 +1524,7 @@
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>Mycket rikligt</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1561,7 +1551,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124880310</v>
+        <v>124880296</v>
       </c>
       <c r="B10" t="n">
         <v>57513</v>
@@ -1601,10 +1591,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>434385</v>
+        <v>434019</v>
       </c>
       <c r="R10" t="n">
-        <v>6936814</v>
+        <v>6936070</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1668,10 +1658,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124880313</v>
+        <v>124880340</v>
       </c>
       <c r="B11" t="n">
-        <v>57513</v>
+        <v>91030</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1684,21 +1674,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1708,10 +1698,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>434447</v>
+        <v>433661</v>
       </c>
       <c r="R11" t="n">
-        <v>6936828</v>
+        <v>6935941</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1744,11 +1734,6 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-05-08</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1775,10 +1760,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>124880288</v>
+        <v>124880360</v>
       </c>
       <c r="B12" t="n">
-        <v>57513</v>
+        <v>78810</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1791,21 +1776,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1815,10 +1800,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>433505</v>
+        <v>433248</v>
       </c>
       <c r="R12" t="n">
-        <v>6935809</v>
+        <v>6935491</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1855,7 +1840,7 @@
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Mycket rikligt</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1882,7 +1867,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>124880278</v>
+        <v>124880299</v>
       </c>
       <c r="B13" t="n">
         <v>57513</v>
@@ -1922,10 +1907,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>433331</v>
+        <v>434112</v>
       </c>
       <c r="R13" t="n">
-        <v>6935597</v>
+        <v>6936130</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1989,10 +1974,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>124880337</v>
+        <v>124880303</v>
       </c>
       <c r="B14" t="n">
-        <v>91030</v>
+        <v>57513</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2005,21 +1990,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2029,10 +2014,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>433534</v>
+        <v>434113</v>
       </c>
       <c r="R14" t="n">
-        <v>6935858</v>
+        <v>6936181</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2065,6 +2050,11 @@
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-05-08</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2091,10 +2081,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>124880343</v>
+        <v>124880317</v>
       </c>
       <c r="B15" t="n">
-        <v>91030</v>
+        <v>57513</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2107,21 +2097,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2131,10 +2121,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>433952</v>
+        <v>434538</v>
       </c>
       <c r="R15" t="n">
-        <v>6936054</v>
+        <v>6936895</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2167,6 +2157,11 @@
       <c r="AA15" t="inlineStr">
         <is>
           <t>2025-05-08</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2193,10 +2188,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>124880286</v>
+        <v>124880345</v>
       </c>
       <c r="B16" t="n">
-        <v>57513</v>
+        <v>91030</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2209,21 +2204,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2233,10 +2228,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>433434</v>
+        <v>434057</v>
       </c>
       <c r="R16" t="n">
-        <v>6935749</v>
+        <v>6936091</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2269,11 +2264,6 @@
       <c r="AA16" t="inlineStr">
         <is>
           <t>2025-05-08</t>
-        </is>
-      </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2300,10 +2290,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>124880296</v>
+        <v>124880329</v>
       </c>
       <c r="B17" t="n">
-        <v>57513</v>
+        <v>91030</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2316,21 +2306,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2340,10 +2330,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>434019</v>
+        <v>433106</v>
       </c>
       <c r="R17" t="n">
-        <v>6936070</v>
+        <v>6935174</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2376,11 +2366,6 @@
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-05-08</t>
-        </is>
-      </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2407,10 +2392,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>124880304</v>
+        <v>124880346</v>
       </c>
       <c r="B18" t="n">
-        <v>57513</v>
+        <v>91030</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2423,21 +2408,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2447,10 +2432,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>434155</v>
+        <v>434113</v>
       </c>
       <c r="R18" t="n">
-        <v>6936279</v>
+        <v>6936148</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2483,11 +2468,6 @@
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-05-08</t>
-        </is>
-      </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2514,10 +2494,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>124880340</v>
+        <v>124880371</v>
       </c>
       <c r="B19" t="n">
-        <v>91030</v>
+        <v>78810</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2530,21 +2510,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2554,10 +2534,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>433661</v>
+        <v>434167</v>
       </c>
       <c r="R19" t="n">
-        <v>6935941</v>
+        <v>6936378</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2590,6 +2570,11 @@
       <c r="AA19" t="inlineStr">
         <is>
           <t>2025-05-08</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Mycket rikligt</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2616,10 +2601,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>124880237</v>
+        <v>124880305</v>
       </c>
       <c r="B20" t="n">
-        <v>91012</v>
+        <v>57513</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2632,21 +2617,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2656,10 +2641,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>433636</v>
+        <v>434128</v>
       </c>
       <c r="R20" t="n">
-        <v>6935914</v>
+        <v>6936677</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2692,6 +2677,11 @@
       <c r="AA20" t="inlineStr">
         <is>
           <t>2025-05-08</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2718,10 +2708,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>124880318</v>
+        <v>124880350</v>
       </c>
       <c r="B21" t="n">
-        <v>57513</v>
+        <v>91030</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2734,21 +2724,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2758,10 +2748,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>434664</v>
+        <v>434118</v>
       </c>
       <c r="R21" t="n">
-        <v>6936929</v>
+        <v>6936187</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2794,11 +2784,6 @@
       <c r="AA21" t="inlineStr">
         <is>
           <t>2025-05-08</t>
-        </is>
-      </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2825,10 +2810,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>124880283</v>
+        <v>124880359</v>
       </c>
       <c r="B22" t="n">
-        <v>57513</v>
+        <v>78810</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2841,21 +2826,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2865,10 +2850,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>433376</v>
+        <v>433093</v>
       </c>
       <c r="R22" t="n">
-        <v>6935695</v>
+        <v>6935150</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2905,7 +2890,7 @@
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>Ringhack färska</t>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2932,10 +2917,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>124880305</v>
+        <v>124880358</v>
       </c>
       <c r="B23" t="n">
-        <v>57513</v>
+        <v>78810</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2948,21 +2933,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2972,10 +2957,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>434128</v>
+        <v>433076</v>
       </c>
       <c r="R23" t="n">
-        <v>6936677</v>
+        <v>6935108</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3012,7 +2997,7 @@
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3039,10 +3024,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>124880355</v>
+        <v>124880326</v>
       </c>
       <c r="B24" t="n">
-        <v>91030</v>
+        <v>91008</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3055,21 +3040,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>5432</v>
+        <v>1108</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3079,10 +3064,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>434478</v>
+        <v>434175</v>
       </c>
       <c r="R24" t="n">
-        <v>6936874</v>
+        <v>6936309</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3141,7 +3126,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>124880350</v>
+        <v>124880333</v>
       </c>
       <c r="B25" t="n">
         <v>91030</v>
@@ -3181,10 +3166,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>434118</v>
+        <v>433376</v>
       </c>
       <c r="R25" t="n">
-        <v>6936187</v>
+        <v>6935725</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3243,7 +3228,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>124880359</v>
+        <v>124880361</v>
       </c>
       <c r="B26" t="n">
         <v>78810</v>
@@ -3283,10 +3268,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>433093</v>
+        <v>433311</v>
       </c>
       <c r="R26" t="n">
-        <v>6935150</v>
+        <v>6935592</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3350,10 +3335,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>124880303</v>
+        <v>124880343</v>
       </c>
       <c r="B27" t="n">
-        <v>57513</v>
+        <v>91030</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3366,21 +3351,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3390,10 +3375,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>434113</v>
+        <v>433952</v>
       </c>
       <c r="R27" t="n">
-        <v>6936181</v>
+        <v>6936054</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3426,11 +3411,6 @@
       <c r="AA27" t="inlineStr">
         <is>
           <t>2025-05-08</t>
-        </is>
-      </c>
-      <c r="AC27" t="inlineStr">
-        <is>
-          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3457,10 +3437,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>124880346</v>
+        <v>124880372</v>
       </c>
       <c r="B28" t="n">
-        <v>91030</v>
+        <v>78810</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3473,21 +3453,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3497,10 +3477,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>434113</v>
+        <v>434443</v>
       </c>
       <c r="R28" t="n">
-        <v>6936148</v>
+        <v>6936839</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3533,6 +3513,11 @@
       <c r="AA28" t="inlineStr">
         <is>
           <t>2025-05-08</t>
+        </is>
+      </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>Mycket rikligt</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3559,10 +3544,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>124880333</v>
+        <v>124880304</v>
       </c>
       <c r="B29" t="n">
-        <v>91030</v>
+        <v>57513</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3575,21 +3560,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3599,10 +3584,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>433376</v>
+        <v>434155</v>
       </c>
       <c r="R29" t="n">
-        <v>6935725</v>
+        <v>6936279</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3635,6 +3620,11 @@
       <c r="AA29" t="inlineStr">
         <is>
           <t>2025-05-08</t>
+        </is>
+      </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3661,10 +3651,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>124880365</v>
+        <v>124880310</v>
       </c>
       <c r="B30" t="n">
-        <v>78810</v>
+        <v>57513</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3677,21 +3667,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3701,10 +3691,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>433755</v>
+        <v>434385</v>
       </c>
       <c r="R30" t="n">
-        <v>6935995</v>
+        <v>6936814</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3741,7 +3731,7 @@
       </c>
       <c r="AC30" t="inlineStr">
         <is>
-          <t>Rikligt</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3768,7 +3758,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>124880290</v>
+        <v>124880288</v>
       </c>
       <c r="B31" t="n">
         <v>57513</v>
@@ -3808,10 +3798,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>433820</v>
+        <v>433505</v>
       </c>
       <c r="R31" t="n">
-        <v>6936000</v>
+        <v>6935809</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3875,10 +3865,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>124880315</v>
+        <v>124880355</v>
       </c>
       <c r="B32" t="n">
-        <v>57513</v>
+        <v>91030</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3891,21 +3881,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3915,10 +3905,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>434466</v>
+        <v>434478</v>
       </c>
       <c r="R32" t="n">
-        <v>6936862</v>
+        <v>6936874</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3951,11 +3941,6 @@
       <c r="AA32" t="inlineStr">
         <is>
           <t>2025-05-08</t>
-        </is>
-      </c>
-      <c r="AC32" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3982,10 +3967,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>124880332</v>
+        <v>124880319</v>
       </c>
       <c r="B33" t="n">
-        <v>91030</v>
+        <v>57513</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -3998,21 +3983,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4022,10 +4007,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>433197</v>
+        <v>434789</v>
       </c>
       <c r="R33" t="n">
-        <v>6935385</v>
+        <v>6936947</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4058,6 +4043,11 @@
       <c r="AA33" t="inlineStr">
         <is>
           <t>2025-05-08</t>
+        </is>
+      </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4084,10 +4074,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>124880369</v>
+        <v>124880313</v>
       </c>
       <c r="B34" t="n">
-        <v>78810</v>
+        <v>57513</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4100,21 +4090,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4124,10 +4114,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>434091</v>
+        <v>434447</v>
       </c>
       <c r="R34" t="n">
-        <v>6936122</v>
+        <v>6936828</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4164,7 +4154,7 @@
       </c>
       <c r="AC34" t="inlineStr">
         <is>
-          <t>Mycket rikligt</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4191,10 +4181,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>124880364</v>
+        <v>124880344</v>
       </c>
       <c r="B35" t="n">
-        <v>78810</v>
+        <v>91030</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4207,21 +4197,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4231,10 +4221,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>433682</v>
+        <v>434028</v>
       </c>
       <c r="R35" t="n">
-        <v>6935955</v>
+        <v>6936084</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4267,11 +4257,6 @@
       <c r="AA35" t="inlineStr">
         <is>
           <t>2025-05-08</t>
-        </is>
-      </c>
-      <c r="AC35" t="inlineStr">
-        <is>
-          <t>Mycket rikligt</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4298,10 +4283,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>124880324</v>
+        <v>124880369</v>
       </c>
       <c r="B36" t="n">
-        <v>91008</v>
+        <v>78810</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4314,21 +4299,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>1108</v>
+        <v>6425</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4338,10 +4323,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>433261</v>
+        <v>434091</v>
       </c>
       <c r="R36" t="n">
-        <v>6935504</v>
+        <v>6936122</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4374,6 +4359,11 @@
       <c r="AA36" t="inlineStr">
         <is>
           <t>2025-05-08</t>
+        </is>
+      </c>
+      <c r="AC36" t="inlineStr">
+        <is>
+          <t>Mycket rikligt</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4400,7 +4390,7 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>124880329</v>
+        <v>124880338</v>
       </c>
       <c r="B37" t="n">
         <v>91030</v>
@@ -4440,10 +4430,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>433106</v>
+        <v>433585</v>
       </c>
       <c r="R37" t="n">
-        <v>6935174</v>
+        <v>6935882</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4502,10 +4492,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>124880326</v>
+        <v>124880337</v>
       </c>
       <c r="B38" t="n">
-        <v>91008</v>
+        <v>91030</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4518,21 +4508,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>1108</v>
+        <v>5432</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4542,10 +4532,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>434175</v>
+        <v>433534</v>
       </c>
       <c r="R38" t="n">
-        <v>6936309</v>
+        <v>6935858</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4604,10 +4594,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>124880353</v>
+        <v>124880373</v>
       </c>
       <c r="B39" t="n">
-        <v>91030</v>
+        <v>78810</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4620,21 +4610,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4644,10 +4634,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>434173</v>
+        <v>434482</v>
       </c>
       <c r="R39" t="n">
-        <v>6936342</v>
+        <v>6936858</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4680,6 +4670,11 @@
       <c r="AA39" t="inlineStr">
         <is>
           <t>2025-05-08</t>
+        </is>
+      </c>
+      <c r="AC39" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4706,10 +4701,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>124880361</v>
+        <v>124880290</v>
       </c>
       <c r="B40" t="n">
-        <v>78810</v>
+        <v>57513</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4722,21 +4717,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4746,10 +4741,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>433311</v>
+        <v>433820</v>
       </c>
       <c r="R40" t="n">
-        <v>6935592</v>
+        <v>6936000</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4786,7 +4781,7 @@
       </c>
       <c r="AC40" t="inlineStr">
         <is>
-          <t>Rikligt</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4813,7 +4808,7 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>124880295</v>
+        <v>124880275</v>
       </c>
       <c r="B41" t="n">
         <v>57513</v>
@@ -4853,10 +4848,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>433952</v>
+        <v>432954</v>
       </c>
       <c r="R41" t="n">
-        <v>6936043</v>
+        <v>6934982</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4920,7 +4915,7 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>124880316</v>
+        <v>124880314</v>
       </c>
       <c r="B42" t="n">
         <v>57513</v>
@@ -4960,10 +4955,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>434532</v>
+        <v>434484</v>
       </c>
       <c r="R42" t="n">
-        <v>6936893</v>
+        <v>6936850</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5027,10 +5022,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>124880358</v>
+        <v>124880318</v>
       </c>
       <c r="B43" t="n">
-        <v>78810</v>
+        <v>57513</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5043,21 +5038,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5067,10 +5062,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>433076</v>
+        <v>434664</v>
       </c>
       <c r="R43" t="n">
-        <v>6935108</v>
+        <v>6936929</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5107,7 +5102,7 @@
       </c>
       <c r="AC43" t="inlineStr">
         <is>
-          <t>Rikligt</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5134,10 +5129,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>124880371</v>
+        <v>124880286</v>
       </c>
       <c r="B44" t="n">
-        <v>78810</v>
+        <v>57513</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5150,21 +5145,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5174,10 +5169,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>434167</v>
+        <v>433434</v>
       </c>
       <c r="R44" t="n">
-        <v>6936378</v>
+        <v>6935749</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5214,7 +5209,7 @@
       </c>
       <c r="AC44" t="inlineStr">
         <is>
-          <t>Mycket rikligt</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5241,7 +5236,7 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>124880299</v>
+        <v>124880315</v>
       </c>
       <c r="B45" t="n">
         <v>57513</v>
@@ -5281,10 +5276,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>434112</v>
+        <v>434466</v>
       </c>
       <c r="R45" t="n">
-        <v>6936130</v>
+        <v>6936862</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5348,10 +5343,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>124880319</v>
+        <v>124880332</v>
       </c>
       <c r="B46" t="n">
-        <v>57513</v>
+        <v>91030</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5364,21 +5359,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5388,10 +5383,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>434789</v>
+        <v>433197</v>
       </c>
       <c r="R46" t="n">
-        <v>6936947</v>
+        <v>6935385</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5424,11 +5419,6 @@
       <c r="AA46" t="inlineStr">
         <is>
           <t>2025-05-08</t>
-        </is>
-      </c>
-      <c r="AC46" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5455,10 +5445,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>124880331</v>
+        <v>124880316</v>
       </c>
       <c r="B47" t="n">
-        <v>91030</v>
+        <v>57513</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5471,21 +5461,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5495,10 +5485,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>433193</v>
+        <v>434532</v>
       </c>
       <c r="R47" t="n">
-        <v>6935352</v>
+        <v>6936893</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5531,6 +5521,11 @@
       <c r="AA47" t="inlineStr">
         <is>
           <t>2025-05-08</t>
+        </is>
+      </c>
+      <c r="AC47" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5557,10 +5552,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>124880373</v>
+        <v>124880237</v>
       </c>
       <c r="B48" t="n">
-        <v>78810</v>
+        <v>91012</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5573,21 +5568,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5597,10 +5592,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>434482</v>
+        <v>433636</v>
       </c>
       <c r="R48" t="n">
-        <v>6936858</v>
+        <v>6935914</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5633,11 +5628,6 @@
       <c r="AA48" t="inlineStr">
         <is>
           <t>2025-05-08</t>
-        </is>
-      </c>
-      <c r="AC48" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5664,10 +5654,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>124880317</v>
+        <v>124880364</v>
       </c>
       <c r="B49" t="n">
-        <v>57513</v>
+        <v>78810</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -5680,21 +5670,21 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5704,10 +5694,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>434538</v>
+        <v>433682</v>
       </c>
       <c r="R49" t="n">
-        <v>6936895</v>
+        <v>6935955</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5744,7 +5734,7 @@
       </c>
       <c r="AC49" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Mycket rikligt</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5771,10 +5761,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>124880344</v>
+        <v>124880283</v>
       </c>
       <c r="B50" t="n">
-        <v>91030</v>
+        <v>57513</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -5787,21 +5777,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5811,10 +5801,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>434028</v>
+        <v>433376</v>
       </c>
       <c r="R50" t="n">
-        <v>6936084</v>
+        <v>6935695</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5847,6 +5837,11 @@
       <c r="AA50" t="inlineStr">
         <is>
           <t>2025-05-08</t>
+        </is>
+      </c>
+      <c r="AC50" t="inlineStr">
+        <is>
+          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -5873,10 +5868,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>124880345</v>
+        <v>124880367</v>
       </c>
       <c r="B51" t="n">
-        <v>91030</v>
+        <v>78810</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -5889,21 +5884,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5913,10 +5908,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>434057</v>
+        <v>433984</v>
       </c>
       <c r="R51" t="n">
-        <v>6936091</v>
+        <v>6936073</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5949,6 +5944,11 @@
       <c r="AA51" t="inlineStr">
         <is>
           <t>2025-05-08</t>
+        </is>
+      </c>
+      <c r="AC51" t="inlineStr">
+        <is>
+          <t>Mycket rikligt</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -5975,7 +5975,7 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>124880338</v>
+        <v>124880331</v>
       </c>
       <c r="B52" t="n">
         <v>91030</v>
@@ -6015,10 +6015,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>433585</v>
+        <v>433193</v>
       </c>
       <c r="R52" t="n">
-        <v>6935882</v>
+        <v>6935352</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>

--- a/artfynd/A 9618-2025 artfynd.xlsx
+++ b/artfynd/A 9618-2025 artfynd.xlsx
@@ -1026,10 +1026,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124880324</v>
+        <v>124880369</v>
       </c>
       <c r="B5" t="n">
-        <v>91008</v>
+        <v>78810</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1042,21 +1042,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1108</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1066,10 +1066,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>433261</v>
+        <v>434091</v>
       </c>
       <c r="R5" t="n">
-        <v>6935504</v>
+        <v>6936122</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1102,6 +1102,11 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-05-08</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Mycket rikligt</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1128,10 +1133,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124880365</v>
+        <v>124880318</v>
       </c>
       <c r="B6" t="n">
-        <v>78810</v>
+        <v>57513</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1144,21 +1149,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1168,10 +1173,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>433755</v>
+        <v>434664</v>
       </c>
       <c r="R6" t="n">
-        <v>6935995</v>
+        <v>6936929</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1208,7 +1213,7 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>Rikligt</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1235,10 +1240,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124880353</v>
+        <v>124880283</v>
       </c>
       <c r="B7" t="n">
-        <v>91030</v>
+        <v>57513</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1251,21 +1256,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1275,10 +1280,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>434173</v>
+        <v>433376</v>
       </c>
       <c r="R7" t="n">
-        <v>6936342</v>
+        <v>6935695</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1311,6 +1316,11 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-05-08</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1337,10 +1347,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124880295</v>
+        <v>124880237</v>
       </c>
       <c r="B8" t="n">
-        <v>57513</v>
+        <v>91012</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1353,21 +1363,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1377,10 +1387,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>433952</v>
+        <v>433636</v>
       </c>
       <c r="R8" t="n">
-        <v>6936043</v>
+        <v>6935914</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1413,11 +1423,6 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-05-08</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1444,10 +1449,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124880278</v>
+        <v>124880333</v>
       </c>
       <c r="B9" t="n">
-        <v>57513</v>
+        <v>91030</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1460,21 +1465,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1484,10 +1489,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>433331</v>
+        <v>433376</v>
       </c>
       <c r="R9" t="n">
-        <v>6935597</v>
+        <v>6935725</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1520,11 +1525,6 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-05-08</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1551,7 +1551,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124880296</v>
+        <v>124880303</v>
       </c>
       <c r="B10" t="n">
         <v>57513</v>
@@ -1591,10 +1591,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>434019</v>
+        <v>434113</v>
       </c>
       <c r="R10" t="n">
-        <v>6936070</v>
+        <v>6936181</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1631,7 +1631,7 @@
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1658,7 +1658,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124880340</v>
+        <v>124880345</v>
       </c>
       <c r="B11" t="n">
         <v>91030</v>
@@ -1698,10 +1698,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>433661</v>
+        <v>434057</v>
       </c>
       <c r="R11" t="n">
-        <v>6935941</v>
+        <v>6936091</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1760,7 +1760,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>124880360</v>
+        <v>124880364</v>
       </c>
       <c r="B12" t="n">
         <v>78810</v>
@@ -1800,10 +1800,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>433248</v>
+        <v>433682</v>
       </c>
       <c r="R12" t="n">
-        <v>6935491</v>
+        <v>6935955</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1867,10 +1867,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>124880299</v>
+        <v>124880361</v>
       </c>
       <c r="B13" t="n">
-        <v>57513</v>
+        <v>78810</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1883,21 +1883,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1907,10 +1907,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>434112</v>
+        <v>433311</v>
       </c>
       <c r="R13" t="n">
-        <v>6936130</v>
+        <v>6935592</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1947,7 +1947,7 @@
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1974,10 +1974,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>124880303</v>
+        <v>124880331</v>
       </c>
       <c r="B14" t="n">
-        <v>57513</v>
+        <v>91030</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1990,21 +1990,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2014,10 +2014,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>434113</v>
+        <v>433193</v>
       </c>
       <c r="R14" t="n">
-        <v>6936181</v>
+        <v>6935352</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2050,11 +2050,6 @@
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-05-08</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2081,10 +2076,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>124880317</v>
+        <v>124880332</v>
       </c>
       <c r="B15" t="n">
-        <v>57513</v>
+        <v>91030</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2097,21 +2092,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2121,10 +2116,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>434538</v>
+        <v>433197</v>
       </c>
       <c r="R15" t="n">
-        <v>6936895</v>
+        <v>6935385</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2157,11 +2152,6 @@
       <c r="AA15" t="inlineStr">
         <is>
           <t>2025-05-08</t>
-        </is>
-      </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2188,7 +2178,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>124880345</v>
+        <v>124880337</v>
       </c>
       <c r="B16" t="n">
         <v>91030</v>
@@ -2228,10 +2218,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>434057</v>
+        <v>433534</v>
       </c>
       <c r="R16" t="n">
-        <v>6936091</v>
+        <v>6935858</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2290,10 +2280,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>124880329</v>
+        <v>124880326</v>
       </c>
       <c r="B17" t="n">
-        <v>91030</v>
+        <v>91008</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2306,21 +2296,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>5432</v>
+        <v>1108</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2330,10 +2320,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>433106</v>
+        <v>434175</v>
       </c>
       <c r="R17" t="n">
-        <v>6935174</v>
+        <v>6936309</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2392,10 +2382,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>124880346</v>
+        <v>124880275</v>
       </c>
       <c r="B18" t="n">
-        <v>91030</v>
+        <v>57513</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2408,21 +2398,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2432,10 +2422,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>434113</v>
+        <v>432954</v>
       </c>
       <c r="R18" t="n">
-        <v>6936148</v>
+        <v>6934982</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2468,6 +2458,11 @@
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-05-08</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2494,10 +2489,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>124880371</v>
+        <v>124880346</v>
       </c>
       <c r="B19" t="n">
-        <v>78810</v>
+        <v>91030</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2510,21 +2505,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2534,10 +2529,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>434167</v>
+        <v>434113</v>
       </c>
       <c r="R19" t="n">
-        <v>6936378</v>
+        <v>6936148</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2570,11 +2565,6 @@
       <c r="AA19" t="inlineStr">
         <is>
           <t>2025-05-08</t>
-        </is>
-      </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>Mycket rikligt</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2601,10 +2591,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>124880305</v>
+        <v>124880371</v>
       </c>
       <c r="B20" t="n">
-        <v>57513</v>
+        <v>78810</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2617,21 +2607,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2641,10 +2631,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>434128</v>
+        <v>434167</v>
       </c>
       <c r="R20" t="n">
-        <v>6936677</v>
+        <v>6936378</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2681,7 +2671,7 @@
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Mycket rikligt</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2708,7 +2698,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>124880350</v>
+        <v>124880343</v>
       </c>
       <c r="B21" t="n">
         <v>91030</v>
@@ -2748,10 +2738,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>434118</v>
+        <v>433952</v>
       </c>
       <c r="R21" t="n">
-        <v>6936187</v>
+        <v>6936054</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2810,10 +2800,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>124880359</v>
+        <v>124880319</v>
       </c>
       <c r="B22" t="n">
-        <v>78810</v>
+        <v>57513</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2826,21 +2816,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2850,10 +2840,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>433093</v>
+        <v>434789</v>
       </c>
       <c r="R22" t="n">
-        <v>6935150</v>
+        <v>6936947</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2890,7 +2880,7 @@
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>Rikligt</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2917,10 +2907,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>124880358</v>
+        <v>124880355</v>
       </c>
       <c r="B23" t="n">
-        <v>78810</v>
+        <v>91030</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2933,21 +2923,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2957,10 +2947,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>433076</v>
+        <v>434478</v>
       </c>
       <c r="R23" t="n">
-        <v>6935108</v>
+        <v>6936874</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2993,11 +2983,6 @@
       <c r="AA23" t="inlineStr">
         <is>
           <t>2025-05-08</t>
-        </is>
-      </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3024,10 +3009,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>124880326</v>
+        <v>124880329</v>
       </c>
       <c r="B24" t="n">
-        <v>91008</v>
+        <v>91030</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3040,21 +3025,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>1108</v>
+        <v>5432</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3064,10 +3049,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>434175</v>
+        <v>433106</v>
       </c>
       <c r="R24" t="n">
-        <v>6936309</v>
+        <v>6935174</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3126,10 +3111,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>124880333</v>
+        <v>124880360</v>
       </c>
       <c r="B25" t="n">
-        <v>91030</v>
+        <v>78810</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3142,21 +3127,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3166,10 +3151,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>433376</v>
+        <v>433248</v>
       </c>
       <c r="R25" t="n">
-        <v>6935725</v>
+        <v>6935491</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3202,6 +3187,11 @@
       <c r="AA25" t="inlineStr">
         <is>
           <t>2025-05-08</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>Mycket rikligt</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3228,10 +3218,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>124880361</v>
+        <v>124880338</v>
       </c>
       <c r="B26" t="n">
-        <v>78810</v>
+        <v>91030</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3244,21 +3234,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3268,10 +3258,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>433311</v>
+        <v>433585</v>
       </c>
       <c r="R26" t="n">
-        <v>6935592</v>
+        <v>6935882</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3304,11 +3294,6 @@
       <c r="AA26" t="inlineStr">
         <is>
           <t>2025-05-08</t>
-        </is>
-      </c>
-      <c r="AC26" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3335,10 +3320,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>124880343</v>
+        <v>124880313</v>
       </c>
       <c r="B27" t="n">
-        <v>91030</v>
+        <v>57513</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3351,21 +3336,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3375,10 +3360,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>433952</v>
+        <v>434447</v>
       </c>
       <c r="R27" t="n">
-        <v>6936054</v>
+        <v>6936828</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3411,6 +3396,11 @@
       <c r="AA27" t="inlineStr">
         <is>
           <t>2025-05-08</t>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3437,7 +3427,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>124880372</v>
+        <v>124880365</v>
       </c>
       <c r="B28" t="n">
         <v>78810</v>
@@ -3477,10 +3467,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>434443</v>
+        <v>433755</v>
       </c>
       <c r="R28" t="n">
-        <v>6936839</v>
+        <v>6935995</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3517,7 +3507,7 @@
       </c>
       <c r="AC28" t="inlineStr">
         <is>
-          <t>Mycket rikligt</t>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3544,7 +3534,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>124880304</v>
+        <v>124880315</v>
       </c>
       <c r="B29" t="n">
         <v>57513</v>
@@ -3584,10 +3574,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>434155</v>
+        <v>434466</v>
       </c>
       <c r="R29" t="n">
-        <v>6936279</v>
+        <v>6936862</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3651,10 +3641,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>124880310</v>
+        <v>124880359</v>
       </c>
       <c r="B30" t="n">
-        <v>57513</v>
+        <v>78810</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3667,21 +3657,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3691,10 +3681,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>434385</v>
+        <v>433093</v>
       </c>
       <c r="R30" t="n">
-        <v>6936814</v>
+        <v>6935150</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3731,7 +3721,7 @@
       </c>
       <c r="AC30" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3758,10 +3748,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>124880288</v>
+        <v>124880350</v>
       </c>
       <c r="B31" t="n">
-        <v>57513</v>
+        <v>91030</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3774,21 +3764,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3798,10 +3788,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>433505</v>
+        <v>434118</v>
       </c>
       <c r="R31" t="n">
-        <v>6935809</v>
+        <v>6936187</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3834,11 +3824,6 @@
       <c r="AA31" t="inlineStr">
         <is>
           <t>2025-05-08</t>
-        </is>
-      </c>
-      <c r="AC31" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3865,10 +3850,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>124880355</v>
+        <v>124880373</v>
       </c>
       <c r="B32" t="n">
-        <v>91030</v>
+        <v>78810</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3881,21 +3866,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3905,10 +3890,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>434478</v>
+        <v>434482</v>
       </c>
       <c r="R32" t="n">
-        <v>6936874</v>
+        <v>6936858</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3941,6 +3926,11 @@
       <c r="AA32" t="inlineStr">
         <is>
           <t>2025-05-08</t>
+        </is>
+      </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3967,7 +3957,7 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>124880319</v>
+        <v>124880317</v>
       </c>
       <c r="B33" t="n">
         <v>57513</v>
@@ -4007,10 +3997,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>434789</v>
+        <v>434538</v>
       </c>
       <c r="R33" t="n">
-        <v>6936947</v>
+        <v>6936895</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4047,7 +4037,7 @@
       </c>
       <c r="AC33" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4074,7 +4064,7 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>124880313</v>
+        <v>124880288</v>
       </c>
       <c r="B34" t="n">
         <v>57513</v>
@@ -4114,10 +4104,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>434447</v>
+        <v>433505</v>
       </c>
       <c r="R34" t="n">
-        <v>6936828</v>
+        <v>6935809</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4154,7 +4144,7 @@
       </c>
       <c r="AC34" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4181,10 +4171,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>124880344</v>
+        <v>124880296</v>
       </c>
       <c r="B35" t="n">
-        <v>91030</v>
+        <v>57513</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4197,21 +4187,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4221,10 +4211,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>434028</v>
+        <v>434019</v>
       </c>
       <c r="R35" t="n">
-        <v>6936084</v>
+        <v>6936070</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4257,6 +4247,11 @@
       <c r="AA35" t="inlineStr">
         <is>
           <t>2025-05-08</t>
+        </is>
+      </c>
+      <c r="AC35" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4283,10 +4278,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>124880369</v>
+        <v>124880290</v>
       </c>
       <c r="B36" t="n">
-        <v>78810</v>
+        <v>57513</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4299,21 +4294,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4323,10 +4318,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>434091</v>
+        <v>433820</v>
       </c>
       <c r="R36" t="n">
-        <v>6936122</v>
+        <v>6936000</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4363,7 +4358,7 @@
       </c>
       <c r="AC36" t="inlineStr">
         <is>
-          <t>Mycket rikligt</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4390,7 +4385,7 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>124880338</v>
+        <v>124880344</v>
       </c>
       <c r="B37" t="n">
         <v>91030</v>
@@ -4430,10 +4425,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>433585</v>
+        <v>434028</v>
       </c>
       <c r="R37" t="n">
-        <v>6935882</v>
+        <v>6936084</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4492,10 +4487,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>124880337</v>
+        <v>124880314</v>
       </c>
       <c r="B38" t="n">
-        <v>91030</v>
+        <v>57513</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4508,21 +4503,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4532,10 +4527,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>433534</v>
+        <v>434484</v>
       </c>
       <c r="R38" t="n">
-        <v>6935858</v>
+        <v>6936850</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4568,6 +4563,11 @@
       <c r="AA38" t="inlineStr">
         <is>
           <t>2025-05-08</t>
+        </is>
+      </c>
+      <c r="AC38" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4594,10 +4594,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>124880373</v>
+        <v>124880286</v>
       </c>
       <c r="B39" t="n">
-        <v>78810</v>
+        <v>57513</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4610,21 +4610,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4634,10 +4634,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>434482</v>
+        <v>433434</v>
       </c>
       <c r="R39" t="n">
-        <v>6936858</v>
+        <v>6935749</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4674,7 +4674,7 @@
       </c>
       <c r="AC39" t="inlineStr">
         <is>
-          <t>Rikligt</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4701,7 +4701,7 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>124880290</v>
+        <v>124880316</v>
       </c>
       <c r="B40" t="n">
         <v>57513</v>
@@ -4741,10 +4741,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>433820</v>
+        <v>434532</v>
       </c>
       <c r="R40" t="n">
-        <v>6936000</v>
+        <v>6936893</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4808,10 +4808,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>124880275</v>
+        <v>124880358</v>
       </c>
       <c r="B41" t="n">
-        <v>57513</v>
+        <v>78810</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -4824,21 +4824,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4848,10 +4848,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>432954</v>
+        <v>433076</v>
       </c>
       <c r="R41" t="n">
-        <v>6934982</v>
+        <v>6935108</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4888,7 +4888,7 @@
       </c>
       <c r="AC41" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4915,10 +4915,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>124880314</v>
+        <v>124880353</v>
       </c>
       <c r="B42" t="n">
-        <v>57513</v>
+        <v>91030</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -4931,21 +4931,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4955,10 +4955,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>434484</v>
+        <v>434173</v>
       </c>
       <c r="R42" t="n">
-        <v>6936850</v>
+        <v>6936342</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4991,11 +4991,6 @@
       <c r="AA42" t="inlineStr">
         <is>
           <t>2025-05-08</t>
-        </is>
-      </c>
-      <c r="AC42" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5022,7 +5017,7 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>124880318</v>
+        <v>124880299</v>
       </c>
       <c r="B43" t="n">
         <v>57513</v>
@@ -5062,10 +5057,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>434664</v>
+        <v>434112</v>
       </c>
       <c r="R43" t="n">
-        <v>6936929</v>
+        <v>6936130</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5129,10 +5124,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>124880286</v>
+        <v>124880367</v>
       </c>
       <c r="B44" t="n">
-        <v>57513</v>
+        <v>78810</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5145,21 +5140,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5169,10 +5164,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>433434</v>
+        <v>433984</v>
       </c>
       <c r="R44" t="n">
-        <v>6935749</v>
+        <v>6936073</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5209,7 +5204,7 @@
       </c>
       <c r="AC44" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Mycket rikligt</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5236,7 +5231,7 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>124880315</v>
+        <v>124880278</v>
       </c>
       <c r="B45" t="n">
         <v>57513</v>
@@ -5276,10 +5271,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>434466</v>
+        <v>433331</v>
       </c>
       <c r="R45" t="n">
-        <v>6936862</v>
+        <v>6935597</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5343,10 +5338,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>124880332</v>
+        <v>124880310</v>
       </c>
       <c r="B46" t="n">
-        <v>91030</v>
+        <v>57513</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5359,21 +5354,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5383,10 +5378,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>433197</v>
+        <v>434385</v>
       </c>
       <c r="R46" t="n">
-        <v>6935385</v>
+        <v>6936814</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5419,6 +5414,11 @@
       <c r="AA46" t="inlineStr">
         <is>
           <t>2025-05-08</t>
+        </is>
+      </c>
+      <c r="AC46" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5445,7 +5445,7 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>124880316</v>
+        <v>124880305</v>
       </c>
       <c r="B47" t="n">
         <v>57513</v>
@@ -5485,10 +5485,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>434532</v>
+        <v>434128</v>
       </c>
       <c r="R47" t="n">
-        <v>6936893</v>
+        <v>6936677</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5552,10 +5552,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>124880237</v>
+        <v>124880340</v>
       </c>
       <c r="B48" t="n">
-        <v>91012</v>
+        <v>91030</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5568,21 +5568,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>1202</v>
+        <v>5432</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5592,10 +5592,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>433636</v>
+        <v>433661</v>
       </c>
       <c r="R48" t="n">
-        <v>6935914</v>
+        <v>6935941</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5654,10 +5654,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>124880364</v>
+        <v>124880295</v>
       </c>
       <c r="B49" t="n">
-        <v>78810</v>
+        <v>57513</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -5670,21 +5670,21 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5694,10 +5694,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>433682</v>
+        <v>433952</v>
       </c>
       <c r="R49" t="n">
-        <v>6935955</v>
+        <v>6936043</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5734,7 +5734,7 @@
       </c>
       <c r="AC49" t="inlineStr">
         <is>
-          <t>Mycket rikligt</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5761,7 +5761,7 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>124880283</v>
+        <v>124880304</v>
       </c>
       <c r="B50" t="n">
         <v>57513</v>
@@ -5801,10 +5801,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>433376</v>
+        <v>434155</v>
       </c>
       <c r="R50" t="n">
-        <v>6935695</v>
+        <v>6936279</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5841,7 +5841,7 @@
       </c>
       <c r="AC50" t="inlineStr">
         <is>
-          <t>Ringhack färska</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -5868,7 +5868,7 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>124880367</v>
+        <v>124880372</v>
       </c>
       <c r="B51" t="n">
         <v>78810</v>
@@ -5908,10 +5908,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>433984</v>
+        <v>434443</v>
       </c>
       <c r="R51" t="n">
-        <v>6936073</v>
+        <v>6936839</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5975,10 +5975,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>124880331</v>
+        <v>124880324</v>
       </c>
       <c r="B52" t="n">
-        <v>91030</v>
+        <v>91008</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -5991,21 +5991,21 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>5432</v>
+        <v>1108</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -6015,10 +6015,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>433193</v>
+        <v>433261</v>
       </c>
       <c r="R52" t="n">
-        <v>6935352</v>
+        <v>6935504</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>

--- a/artfynd/A 9618-2025 artfynd.xlsx
+++ b/artfynd/A 9618-2025 artfynd.xlsx
@@ -1026,7 +1026,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124880369</v>
+        <v>124880359</v>
       </c>
       <c r="B5" t="n">
         <v>78810</v>
@@ -1066,10 +1066,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>434091</v>
+        <v>433093</v>
       </c>
       <c r="R5" t="n">
-        <v>6936122</v>
+        <v>6935150</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1106,7 +1106,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Mycket rikligt</t>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1133,10 +1133,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124880318</v>
+        <v>124880237</v>
       </c>
       <c r="B6" t="n">
-        <v>57513</v>
+        <v>91012</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1149,21 +1149,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1173,10 +1173,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>434664</v>
+        <v>433636</v>
       </c>
       <c r="R6" t="n">
-        <v>6936929</v>
+        <v>6935914</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1209,11 +1209,6 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-05-08</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1240,10 +1235,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124880283</v>
+        <v>124880355</v>
       </c>
       <c r="B7" t="n">
-        <v>57513</v>
+        <v>91030</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1256,21 +1251,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1280,10 +1275,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>433376</v>
+        <v>434478</v>
       </c>
       <c r="R7" t="n">
-        <v>6935695</v>
+        <v>6936874</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1316,11 +1311,6 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-05-08</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1347,10 +1337,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124880237</v>
+        <v>124880364</v>
       </c>
       <c r="B8" t="n">
-        <v>91012</v>
+        <v>78810</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1363,21 +1353,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1387,10 +1377,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>433636</v>
+        <v>433682</v>
       </c>
       <c r="R8" t="n">
-        <v>6935914</v>
+        <v>6935955</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1423,6 +1413,11 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-05-08</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Mycket rikligt</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1449,10 +1444,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124880333</v>
+        <v>124880275</v>
       </c>
       <c r="B9" t="n">
-        <v>91030</v>
+        <v>57513</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1465,21 +1460,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1489,10 +1484,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>433376</v>
+        <v>432954</v>
       </c>
       <c r="R9" t="n">
-        <v>6935725</v>
+        <v>6934982</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1525,6 +1520,11 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-05-08</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1551,10 +1551,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124880303</v>
+        <v>124880365</v>
       </c>
       <c r="B10" t="n">
-        <v>57513</v>
+        <v>78810</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1567,21 +1567,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1591,10 +1591,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>434113</v>
+        <v>433755</v>
       </c>
       <c r="R10" t="n">
-        <v>6936181</v>
+        <v>6935995</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1631,7 +1631,7 @@
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1658,10 +1658,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124880345</v>
+        <v>124880314</v>
       </c>
       <c r="B11" t="n">
-        <v>91030</v>
+        <v>57513</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1674,21 +1674,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1698,10 +1698,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>434057</v>
+        <v>434484</v>
       </c>
       <c r="R11" t="n">
-        <v>6936091</v>
+        <v>6936850</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1734,6 +1734,11 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-05-08</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1760,10 +1765,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>124880364</v>
+        <v>124880286</v>
       </c>
       <c r="B12" t="n">
-        <v>78810</v>
+        <v>57513</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1776,21 +1781,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1800,10 +1805,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>433682</v>
+        <v>433434</v>
       </c>
       <c r="R12" t="n">
-        <v>6935955</v>
+        <v>6935749</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1840,7 +1845,7 @@
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>Mycket rikligt</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1867,10 +1872,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>124880361</v>
+        <v>124880313</v>
       </c>
       <c r="B13" t="n">
-        <v>78810</v>
+        <v>57513</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1883,21 +1888,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1907,10 +1912,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>433311</v>
+        <v>434447</v>
       </c>
       <c r="R13" t="n">
-        <v>6935592</v>
+        <v>6936828</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1947,7 +1952,7 @@
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>Rikligt</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1974,10 +1979,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>124880331</v>
+        <v>124880324</v>
       </c>
       <c r="B14" t="n">
-        <v>91030</v>
+        <v>91008</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1990,21 +1995,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>5432</v>
+        <v>1108</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2014,10 +2019,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>433193</v>
+        <v>433261</v>
       </c>
       <c r="R14" t="n">
-        <v>6935352</v>
+        <v>6935504</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2076,10 +2081,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>124880332</v>
+        <v>124880288</v>
       </c>
       <c r="B15" t="n">
-        <v>91030</v>
+        <v>57513</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2092,21 +2097,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2116,10 +2121,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>433197</v>
+        <v>433505</v>
       </c>
       <c r="R15" t="n">
-        <v>6935385</v>
+        <v>6935809</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2152,6 +2157,11 @@
       <c r="AA15" t="inlineStr">
         <is>
           <t>2025-05-08</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2178,10 +2188,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>124880337</v>
+        <v>124880296</v>
       </c>
       <c r="B16" t="n">
-        <v>91030</v>
+        <v>57513</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2194,21 +2204,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2218,10 +2228,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>433534</v>
+        <v>434019</v>
       </c>
       <c r="R16" t="n">
-        <v>6935858</v>
+        <v>6936070</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2254,6 +2264,11 @@
       <c r="AA16" t="inlineStr">
         <is>
           <t>2025-05-08</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2280,10 +2295,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>124880326</v>
+        <v>124880350</v>
       </c>
       <c r="B17" t="n">
-        <v>91008</v>
+        <v>91030</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2296,21 +2311,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1108</v>
+        <v>5432</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2320,10 +2335,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>434175</v>
+        <v>434118</v>
       </c>
       <c r="R17" t="n">
-        <v>6936309</v>
+        <v>6936187</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2382,7 +2397,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>124880275</v>
+        <v>124880304</v>
       </c>
       <c r="B18" t="n">
         <v>57513</v>
@@ -2422,10 +2437,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>432954</v>
+        <v>434155</v>
       </c>
       <c r="R18" t="n">
-        <v>6934982</v>
+        <v>6936279</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2489,10 +2504,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>124880346</v>
+        <v>124880318</v>
       </c>
       <c r="B19" t="n">
-        <v>91030</v>
+        <v>57513</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2505,21 +2520,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2529,10 +2544,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>434113</v>
+        <v>434664</v>
       </c>
       <c r="R19" t="n">
-        <v>6936148</v>
+        <v>6936929</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2565,6 +2580,11 @@
       <c r="AA19" t="inlineStr">
         <is>
           <t>2025-05-08</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2591,10 +2611,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>124880371</v>
+        <v>124880338</v>
       </c>
       <c r="B20" t="n">
-        <v>78810</v>
+        <v>91030</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2607,21 +2627,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2631,10 +2651,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>434167</v>
+        <v>433585</v>
       </c>
       <c r="R20" t="n">
-        <v>6936378</v>
+        <v>6935882</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2667,11 +2687,6 @@
       <c r="AA20" t="inlineStr">
         <is>
           <t>2025-05-08</t>
-        </is>
-      </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>Mycket rikligt</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2698,7 +2713,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>124880343</v>
+        <v>124880332</v>
       </c>
       <c r="B21" t="n">
         <v>91030</v>
@@ -2738,10 +2753,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>433952</v>
+        <v>433197</v>
       </c>
       <c r="R21" t="n">
-        <v>6936054</v>
+        <v>6935385</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2800,10 +2815,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>124880319</v>
+        <v>124880337</v>
       </c>
       <c r="B22" t="n">
-        <v>57513</v>
+        <v>91030</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2816,21 +2831,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2840,10 +2855,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>434789</v>
+        <v>433534</v>
       </c>
       <c r="R22" t="n">
-        <v>6936947</v>
+        <v>6935858</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2876,11 +2891,6 @@
       <c r="AA22" t="inlineStr">
         <is>
           <t>2025-05-08</t>
-        </is>
-      </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2907,10 +2917,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>124880355</v>
+        <v>124880326</v>
       </c>
       <c r="B23" t="n">
-        <v>91030</v>
+        <v>91008</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2923,21 +2933,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>5432</v>
+        <v>1108</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2947,10 +2957,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>434478</v>
+        <v>434175</v>
       </c>
       <c r="R23" t="n">
-        <v>6936874</v>
+        <v>6936309</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3009,10 +3019,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>124880329</v>
+        <v>124880317</v>
       </c>
       <c r="B24" t="n">
-        <v>91030</v>
+        <v>57513</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3025,21 +3035,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3049,10 +3059,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>433106</v>
+        <v>434538</v>
       </c>
       <c r="R24" t="n">
-        <v>6935174</v>
+        <v>6936895</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3085,6 +3095,11 @@
       <c r="AA24" t="inlineStr">
         <is>
           <t>2025-05-08</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3111,10 +3126,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>124880360</v>
+        <v>124880353</v>
       </c>
       <c r="B25" t="n">
-        <v>78810</v>
+        <v>91030</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3127,21 +3142,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3151,10 +3166,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>433248</v>
+        <v>434173</v>
       </c>
       <c r="R25" t="n">
-        <v>6935491</v>
+        <v>6936342</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3187,11 +3202,6 @@
       <c r="AA25" t="inlineStr">
         <is>
           <t>2025-05-08</t>
-        </is>
-      </c>
-      <c r="AC25" t="inlineStr">
-        <is>
-          <t>Mycket rikligt</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3218,10 +3228,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>124880338</v>
+        <v>124880358</v>
       </c>
       <c r="B26" t="n">
-        <v>91030</v>
+        <v>78810</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3234,21 +3244,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3258,10 +3268,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>433585</v>
+        <v>433076</v>
       </c>
       <c r="R26" t="n">
-        <v>6935882</v>
+        <v>6935108</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3294,6 +3304,11 @@
       <c r="AA26" t="inlineStr">
         <is>
           <t>2025-05-08</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3320,10 +3335,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>124880313</v>
+        <v>124880361</v>
       </c>
       <c r="B27" t="n">
-        <v>57513</v>
+        <v>78810</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3336,21 +3351,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3360,10 +3375,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>434447</v>
+        <v>433311</v>
       </c>
       <c r="R27" t="n">
-        <v>6936828</v>
+        <v>6935592</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3400,7 +3415,7 @@
       </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3427,10 +3442,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>124880365</v>
+        <v>124880340</v>
       </c>
       <c r="B28" t="n">
-        <v>78810</v>
+        <v>91030</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3443,21 +3458,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3467,10 +3482,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>433755</v>
+        <v>433661</v>
       </c>
       <c r="R28" t="n">
-        <v>6935995</v>
+        <v>6935941</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3503,11 +3518,6 @@
       <c r="AA28" t="inlineStr">
         <is>
           <t>2025-05-08</t>
-        </is>
-      </c>
-      <c r="AC28" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3534,10 +3544,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>124880315</v>
+        <v>124880360</v>
       </c>
       <c r="B29" t="n">
-        <v>57513</v>
+        <v>78810</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3550,21 +3560,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3574,10 +3584,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>434466</v>
+        <v>433248</v>
       </c>
       <c r="R29" t="n">
-        <v>6936862</v>
+        <v>6935491</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3614,7 +3624,7 @@
       </c>
       <c r="AC29" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Mycket rikligt</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3641,7 +3651,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>124880359</v>
+        <v>124880369</v>
       </c>
       <c r="B30" t="n">
         <v>78810</v>
@@ -3681,10 +3691,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>433093</v>
+        <v>434091</v>
       </c>
       <c r="R30" t="n">
-        <v>6935150</v>
+        <v>6936122</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3721,7 +3731,7 @@
       </c>
       <c r="AC30" t="inlineStr">
         <is>
-          <t>Rikligt</t>
+          <t>Mycket rikligt</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3748,7 +3758,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>124880350</v>
+        <v>124880345</v>
       </c>
       <c r="B31" t="n">
         <v>91030</v>
@@ -3788,10 +3798,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>434118</v>
+        <v>434057</v>
       </c>
       <c r="R31" t="n">
-        <v>6936187</v>
+        <v>6936091</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3850,10 +3860,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>124880373</v>
+        <v>124880333</v>
       </c>
       <c r="B32" t="n">
-        <v>78810</v>
+        <v>91030</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3866,21 +3876,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3890,10 +3900,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>434482</v>
+        <v>433376</v>
       </c>
       <c r="R32" t="n">
-        <v>6936858</v>
+        <v>6935725</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3926,11 +3936,6 @@
       <c r="AA32" t="inlineStr">
         <is>
           <t>2025-05-08</t>
-        </is>
-      </c>
-      <c r="AC32" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3957,7 +3962,7 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>124880317</v>
+        <v>124880278</v>
       </c>
       <c r="B33" t="n">
         <v>57513</v>
@@ -3997,10 +4002,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>434538</v>
+        <v>433331</v>
       </c>
       <c r="R33" t="n">
-        <v>6936895</v>
+        <v>6935597</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4037,7 +4042,7 @@
       </c>
       <c r="AC33" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4064,10 +4069,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>124880288</v>
+        <v>124880343</v>
       </c>
       <c r="B34" t="n">
-        <v>57513</v>
+        <v>91030</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4080,21 +4085,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4104,10 +4109,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>433505</v>
+        <v>433952</v>
       </c>
       <c r="R34" t="n">
-        <v>6935809</v>
+        <v>6936054</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4140,11 +4145,6 @@
       <c r="AA34" t="inlineStr">
         <is>
           <t>2025-05-08</t>
-        </is>
-      </c>
-      <c r="AC34" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4171,10 +4171,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>124880296</v>
+        <v>124880373</v>
       </c>
       <c r="B35" t="n">
-        <v>57513</v>
+        <v>78810</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4187,21 +4187,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4211,10 +4211,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>434019</v>
+        <v>434482</v>
       </c>
       <c r="R35" t="n">
-        <v>6936070</v>
+        <v>6936858</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4251,7 +4251,7 @@
       </c>
       <c r="AC35" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4278,7 +4278,7 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>124880290</v>
+        <v>124880295</v>
       </c>
       <c r="B36" t="n">
         <v>57513</v>
@@ -4318,10 +4318,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>433820</v>
+        <v>433952</v>
       </c>
       <c r="R36" t="n">
-        <v>6936000</v>
+        <v>6936043</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4385,10 +4385,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>124880344</v>
+        <v>124880290</v>
       </c>
       <c r="B37" t="n">
-        <v>91030</v>
+        <v>57513</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4401,21 +4401,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4425,10 +4425,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>434028</v>
+        <v>433820</v>
       </c>
       <c r="R37" t="n">
-        <v>6936084</v>
+        <v>6936000</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4461,6 +4461,11 @@
       <c r="AA37" t="inlineStr">
         <is>
           <t>2025-05-08</t>
+        </is>
+      </c>
+      <c r="AC37" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4487,7 +4492,7 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>124880314</v>
+        <v>124880299</v>
       </c>
       <c r="B38" t="n">
         <v>57513</v>
@@ -4527,10 +4532,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>434484</v>
+        <v>434112</v>
       </c>
       <c r="R38" t="n">
-        <v>6936850</v>
+        <v>6936130</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4594,10 +4599,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>124880286</v>
+        <v>124880329</v>
       </c>
       <c r="B39" t="n">
-        <v>57513</v>
+        <v>91030</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4610,21 +4615,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4634,10 +4639,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>433434</v>
+        <v>433106</v>
       </c>
       <c r="R39" t="n">
-        <v>6935749</v>
+        <v>6935174</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4670,11 +4675,6 @@
       <c r="AA39" t="inlineStr">
         <is>
           <t>2025-05-08</t>
-        </is>
-      </c>
-      <c r="AC39" t="inlineStr">
-        <is>
-          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4701,7 +4701,7 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>124880316</v>
+        <v>124880283</v>
       </c>
       <c r="B40" t="n">
         <v>57513</v>
@@ -4741,10 +4741,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>434532</v>
+        <v>433376</v>
       </c>
       <c r="R40" t="n">
-        <v>6936893</v>
+        <v>6935695</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4781,7 +4781,7 @@
       </c>
       <c r="AC40" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4808,10 +4808,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>124880358</v>
+        <v>124880316</v>
       </c>
       <c r="B41" t="n">
-        <v>78810</v>
+        <v>57513</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -4824,21 +4824,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4848,10 +4848,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>433076</v>
+        <v>434532</v>
       </c>
       <c r="R41" t="n">
-        <v>6935108</v>
+        <v>6936893</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4888,7 +4888,7 @@
       </c>
       <c r="AC41" t="inlineStr">
         <is>
-          <t>Rikligt</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4915,10 +4915,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>124880353</v>
+        <v>124880303</v>
       </c>
       <c r="B42" t="n">
-        <v>91030</v>
+        <v>57513</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -4931,21 +4931,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4955,10 +4955,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>434173</v>
+        <v>434113</v>
       </c>
       <c r="R42" t="n">
-        <v>6936342</v>
+        <v>6936181</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4991,6 +4991,11 @@
       <c r="AA42" t="inlineStr">
         <is>
           <t>2025-05-08</t>
+        </is>
+      </c>
+      <c r="AC42" t="inlineStr">
+        <is>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5017,7 +5022,7 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>124880299</v>
+        <v>124880310</v>
       </c>
       <c r="B43" t="n">
         <v>57513</v>
@@ -5057,10 +5062,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>434112</v>
+        <v>434385</v>
       </c>
       <c r="R43" t="n">
-        <v>6936130</v>
+        <v>6936814</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5124,10 +5129,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>124880367</v>
+        <v>124880305</v>
       </c>
       <c r="B44" t="n">
-        <v>78810</v>
+        <v>57513</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5140,21 +5145,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5164,10 +5169,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>433984</v>
+        <v>434128</v>
       </c>
       <c r="R44" t="n">
-        <v>6936073</v>
+        <v>6936677</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5204,7 +5209,7 @@
       </c>
       <c r="AC44" t="inlineStr">
         <is>
-          <t>Mycket rikligt</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5231,10 +5236,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>124880278</v>
+        <v>124880372</v>
       </c>
       <c r="B45" t="n">
-        <v>57513</v>
+        <v>78810</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5247,21 +5252,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5271,10 +5276,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>433331</v>
+        <v>434443</v>
       </c>
       <c r="R45" t="n">
-        <v>6935597</v>
+        <v>6936839</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5311,7 +5316,7 @@
       </c>
       <c r="AC45" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Mycket rikligt</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5338,10 +5343,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>124880310</v>
+        <v>124880367</v>
       </c>
       <c r="B46" t="n">
-        <v>57513</v>
+        <v>78810</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5354,21 +5359,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5378,10 +5383,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>434385</v>
+        <v>433984</v>
       </c>
       <c r="R46" t="n">
-        <v>6936814</v>
+        <v>6936073</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5418,7 +5423,7 @@
       </c>
       <c r="AC46" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Mycket rikligt</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5445,7 +5450,7 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>124880305</v>
+        <v>124880315</v>
       </c>
       <c r="B47" t="n">
         <v>57513</v>
@@ -5485,10 +5490,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>434128</v>
+        <v>434466</v>
       </c>
       <c r="R47" t="n">
-        <v>6936677</v>
+        <v>6936862</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5552,10 +5557,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>124880340</v>
+        <v>124880319</v>
       </c>
       <c r="B48" t="n">
-        <v>91030</v>
+        <v>57513</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5568,21 +5573,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5592,10 +5597,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>433661</v>
+        <v>434789</v>
       </c>
       <c r="R48" t="n">
-        <v>6935941</v>
+        <v>6936947</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5628,6 +5633,11 @@
       <c r="AA48" t="inlineStr">
         <is>
           <t>2025-05-08</t>
+        </is>
+      </c>
+      <c r="AC48" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5654,10 +5664,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>124880295</v>
+        <v>124880344</v>
       </c>
       <c r="B49" t="n">
-        <v>57513</v>
+        <v>91030</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -5670,21 +5680,21 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5694,10 +5704,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>433952</v>
+        <v>434028</v>
       </c>
       <c r="R49" t="n">
-        <v>6936043</v>
+        <v>6936084</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5730,11 +5740,6 @@
       <c r="AA49" t="inlineStr">
         <is>
           <t>2025-05-08</t>
-        </is>
-      </c>
-      <c r="AC49" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5761,10 +5766,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>124880304</v>
+        <v>124880331</v>
       </c>
       <c r="B50" t="n">
-        <v>57513</v>
+        <v>91030</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -5777,21 +5782,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5801,10 +5806,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>434155</v>
+        <v>433193</v>
       </c>
       <c r="R50" t="n">
-        <v>6936279</v>
+        <v>6935352</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5837,11 +5842,6 @@
       <c r="AA50" t="inlineStr">
         <is>
           <t>2025-05-08</t>
-        </is>
-      </c>
-      <c r="AC50" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -5868,10 +5868,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>124880372</v>
+        <v>124880346</v>
       </c>
       <c r="B51" t="n">
-        <v>78810</v>
+        <v>91030</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -5884,21 +5884,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5908,10 +5908,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>434443</v>
+        <v>434113</v>
       </c>
       <c r="R51" t="n">
-        <v>6936839</v>
+        <v>6936148</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5944,11 +5944,6 @@
       <c r="AA51" t="inlineStr">
         <is>
           <t>2025-05-08</t>
-        </is>
-      </c>
-      <c r="AC51" t="inlineStr">
-        <is>
-          <t>Mycket rikligt</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -5975,10 +5970,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>124880324</v>
+        <v>124880371</v>
       </c>
       <c r="B52" t="n">
-        <v>91008</v>
+        <v>78810</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -5991,21 +5986,21 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>1108</v>
+        <v>6425</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -6015,10 +6010,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>433261</v>
+        <v>434167</v>
       </c>
       <c r="R52" t="n">
-        <v>6935504</v>
+        <v>6936378</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6051,6 +6046,11 @@
       <c r="AA52" t="inlineStr">
         <is>
           <t>2025-05-08</t>
+        </is>
+      </c>
+      <c r="AC52" t="inlineStr">
+        <is>
+          <t>Mycket rikligt</t>
         </is>
       </c>
       <c r="AD52" t="b">

--- a/artfynd/A 9618-2025 artfynd.xlsx
+++ b/artfynd/A 9618-2025 artfynd.xlsx
@@ -1026,10 +1026,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124880359</v>
+        <v>124880237</v>
       </c>
       <c r="B5" t="n">
-        <v>78810</v>
+        <v>91012</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1042,21 +1042,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1066,10 +1066,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>433093</v>
+        <v>433636</v>
       </c>
       <c r="R5" t="n">
-        <v>6935150</v>
+        <v>6935914</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1102,11 +1102,6 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-05-08</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1133,10 +1128,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124880237</v>
+        <v>124880359</v>
       </c>
       <c r="B6" t="n">
-        <v>91012</v>
+        <v>78810</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1149,21 +1144,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1173,10 +1168,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>433636</v>
+        <v>433093</v>
       </c>
       <c r="R6" t="n">
-        <v>6935914</v>
+        <v>6935150</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1209,6 +1204,11 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-05-08</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -2611,10 +2611,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>124880338</v>
+        <v>124880317</v>
       </c>
       <c r="B20" t="n">
-        <v>91030</v>
+        <v>57513</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2627,21 +2627,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2651,10 +2651,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>433585</v>
+        <v>434538</v>
       </c>
       <c r="R20" t="n">
-        <v>6935882</v>
+        <v>6936895</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2687,6 +2687,11 @@
       <c r="AA20" t="inlineStr">
         <is>
           <t>2025-05-08</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2713,10 +2718,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>124880332</v>
+        <v>124880326</v>
       </c>
       <c r="B21" t="n">
-        <v>91030</v>
+        <v>91008</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2729,21 +2734,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>5432</v>
+        <v>1108</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2753,10 +2758,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>433197</v>
+        <v>434175</v>
       </c>
       <c r="R21" t="n">
-        <v>6935385</v>
+        <v>6936309</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2815,7 +2820,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>124880337</v>
+        <v>124880338</v>
       </c>
       <c r="B22" t="n">
         <v>91030</v>
@@ -2855,10 +2860,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>433534</v>
+        <v>433585</v>
       </c>
       <c r="R22" t="n">
-        <v>6935858</v>
+        <v>6935882</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2917,10 +2922,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>124880326</v>
+        <v>124880332</v>
       </c>
       <c r="B23" t="n">
-        <v>91008</v>
+        <v>91030</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2933,21 +2938,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>1108</v>
+        <v>5432</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2957,10 +2962,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>434175</v>
+        <v>433197</v>
       </c>
       <c r="R23" t="n">
-        <v>6936309</v>
+        <v>6935385</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3019,10 +3024,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>124880317</v>
+        <v>124880337</v>
       </c>
       <c r="B24" t="n">
-        <v>57513</v>
+        <v>91030</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3035,21 +3040,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3059,10 +3064,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>434538</v>
+        <v>433534</v>
       </c>
       <c r="R24" t="n">
-        <v>6936895</v>
+        <v>6935858</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3095,11 +3100,6 @@
       <c r="AA24" t="inlineStr">
         <is>
           <t>2025-05-08</t>
-        </is>
-      </c>
-      <c r="AC24" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD24" t="b">

--- a/artfynd/A 9618-2025 artfynd.xlsx
+++ b/artfynd/A 9618-2025 artfynd.xlsx
@@ -1026,10 +1026,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124880237</v>
+        <v>124880332</v>
       </c>
       <c r="B5" t="n">
-        <v>91012</v>
+        <v>91030</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1042,21 +1042,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1202</v>
+        <v>5432</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1066,10 +1066,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>433636</v>
+        <v>433197</v>
       </c>
       <c r="R5" t="n">
-        <v>6935914</v>
+        <v>6935385</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1128,7 +1128,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124880359</v>
+        <v>124880373</v>
       </c>
       <c r="B6" t="n">
         <v>78810</v>
@@ -1168,10 +1168,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>433093</v>
+        <v>434482</v>
       </c>
       <c r="R6" t="n">
-        <v>6935150</v>
+        <v>6936858</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1235,10 +1235,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124880355</v>
+        <v>124880360</v>
       </c>
       <c r="B7" t="n">
-        <v>91030</v>
+        <v>78810</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1251,21 +1251,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1275,10 +1275,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>434478</v>
+        <v>433248</v>
       </c>
       <c r="R7" t="n">
-        <v>6936874</v>
+        <v>6935491</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1311,6 +1311,11 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-05-08</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Mycket rikligt</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1337,10 +1342,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124880364</v>
+        <v>124880319</v>
       </c>
       <c r="B8" t="n">
-        <v>78810</v>
+        <v>57513</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1353,21 +1358,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1377,10 +1382,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>433682</v>
+        <v>434789</v>
       </c>
       <c r="R8" t="n">
-        <v>6935955</v>
+        <v>6936947</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1417,7 +1422,7 @@
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>Mycket rikligt</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1444,10 +1449,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124880275</v>
+        <v>124880359</v>
       </c>
       <c r="B9" t="n">
-        <v>57513</v>
+        <v>78810</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1460,21 +1465,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1484,10 +1489,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>432954</v>
+        <v>433093</v>
       </c>
       <c r="R9" t="n">
-        <v>6934982</v>
+        <v>6935150</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1524,7 +1529,7 @@
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1551,10 +1556,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124880365</v>
+        <v>124880340</v>
       </c>
       <c r="B10" t="n">
-        <v>78810</v>
+        <v>91030</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1567,21 +1572,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1591,10 +1596,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>433755</v>
+        <v>433661</v>
       </c>
       <c r="R10" t="n">
-        <v>6935995</v>
+        <v>6935941</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1627,11 +1632,6 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-05-08</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1658,10 +1658,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124880314</v>
+        <v>124880324</v>
       </c>
       <c r="B11" t="n">
-        <v>57513</v>
+        <v>91008</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1674,21 +1674,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100109</v>
+        <v>1108</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1698,10 +1698,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>434484</v>
+        <v>433261</v>
       </c>
       <c r="R11" t="n">
-        <v>6936850</v>
+        <v>6935504</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1734,11 +1734,6 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-05-08</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1765,10 +1760,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>124880286</v>
+        <v>124880344</v>
       </c>
       <c r="B12" t="n">
-        <v>57513</v>
+        <v>91030</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1781,21 +1776,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1805,10 +1800,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>433434</v>
+        <v>434028</v>
       </c>
       <c r="R12" t="n">
-        <v>6935749</v>
+        <v>6936084</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1841,11 +1836,6 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-05-08</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1872,10 +1862,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>124880313</v>
+        <v>124880338</v>
       </c>
       <c r="B13" t="n">
-        <v>57513</v>
+        <v>91030</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1888,21 +1878,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1912,10 +1902,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>434447</v>
+        <v>433585</v>
       </c>
       <c r="R13" t="n">
-        <v>6936828</v>
+        <v>6935882</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1948,11 +1938,6 @@
       <c r="AA13" t="inlineStr">
         <is>
           <t>2025-05-08</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1979,10 +1964,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>124880324</v>
+        <v>124880316</v>
       </c>
       <c r="B14" t="n">
-        <v>91008</v>
+        <v>57513</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1995,21 +1980,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1108</v>
+        <v>100109</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2019,10 +2004,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>433261</v>
+        <v>434532</v>
       </c>
       <c r="R14" t="n">
-        <v>6935504</v>
+        <v>6936893</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2055,6 +2040,11 @@
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-05-08</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2081,7 +2071,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>124880288</v>
+        <v>124880283</v>
       </c>
       <c r="B15" t="n">
         <v>57513</v>
@@ -2121,10 +2111,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>433505</v>
+        <v>433376</v>
       </c>
       <c r="R15" t="n">
-        <v>6935809</v>
+        <v>6935695</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2161,7 +2151,7 @@
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2188,10 +2178,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>124880296</v>
+        <v>124880355</v>
       </c>
       <c r="B16" t="n">
-        <v>57513</v>
+        <v>91030</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2204,21 +2194,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2228,10 +2218,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>434019</v>
+        <v>434478</v>
       </c>
       <c r="R16" t="n">
-        <v>6936070</v>
+        <v>6936874</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2264,11 +2254,6 @@
       <c r="AA16" t="inlineStr">
         <is>
           <t>2025-05-08</t>
-        </is>
-      </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2295,10 +2280,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>124880350</v>
+        <v>124880372</v>
       </c>
       <c r="B17" t="n">
-        <v>91030</v>
+        <v>78810</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2311,21 +2296,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2335,10 +2320,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>434118</v>
+        <v>434443</v>
       </c>
       <c r="R17" t="n">
-        <v>6936187</v>
+        <v>6936839</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2371,6 +2356,11 @@
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-05-08</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Mycket rikligt</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2397,7 +2387,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>124880304</v>
+        <v>124880275</v>
       </c>
       <c r="B18" t="n">
         <v>57513</v>
@@ -2437,10 +2427,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>434155</v>
+        <v>432954</v>
       </c>
       <c r="R18" t="n">
-        <v>6936279</v>
+        <v>6934982</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2504,10 +2494,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>124880318</v>
+        <v>124880369</v>
       </c>
       <c r="B19" t="n">
-        <v>57513</v>
+        <v>78810</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2520,21 +2510,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2544,10 +2534,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>434664</v>
+        <v>434091</v>
       </c>
       <c r="R19" t="n">
-        <v>6936929</v>
+        <v>6936122</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2584,7 +2574,7 @@
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Mycket rikligt</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2611,7 +2601,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>124880317</v>
+        <v>124880295</v>
       </c>
       <c r="B20" t="n">
         <v>57513</v>
@@ -2651,10 +2641,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>434538</v>
+        <v>433952</v>
       </c>
       <c r="R20" t="n">
-        <v>6936895</v>
+        <v>6936043</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2691,7 +2681,7 @@
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2718,10 +2708,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>124880326</v>
+        <v>124880353</v>
       </c>
       <c r="B21" t="n">
-        <v>91008</v>
+        <v>91030</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2734,21 +2724,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>1108</v>
+        <v>5432</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2758,10 +2748,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>434175</v>
+        <v>434173</v>
       </c>
       <c r="R21" t="n">
-        <v>6936309</v>
+        <v>6936342</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2820,7 +2810,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>124880338</v>
+        <v>124880346</v>
       </c>
       <c r="B22" t="n">
         <v>91030</v>
@@ -2860,10 +2850,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>433585</v>
+        <v>434113</v>
       </c>
       <c r="R22" t="n">
-        <v>6935882</v>
+        <v>6936148</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2922,7 +2912,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>124880332</v>
+        <v>124880333</v>
       </c>
       <c r="B23" t="n">
         <v>91030</v>
@@ -2962,10 +2952,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>433197</v>
+        <v>433376</v>
       </c>
       <c r="R23" t="n">
-        <v>6935385</v>
+        <v>6935725</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3024,7 +3014,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>124880337</v>
+        <v>124880329</v>
       </c>
       <c r="B24" t="n">
         <v>91030</v>
@@ -3064,10 +3054,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>433534</v>
+        <v>433106</v>
       </c>
       <c r="R24" t="n">
-        <v>6935858</v>
+        <v>6935174</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3126,10 +3116,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>124880353</v>
+        <v>124880304</v>
       </c>
       <c r="B25" t="n">
-        <v>91030</v>
+        <v>57513</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3142,21 +3132,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3166,10 +3156,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>434173</v>
+        <v>434155</v>
       </c>
       <c r="R25" t="n">
-        <v>6936342</v>
+        <v>6936279</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3202,6 +3192,11 @@
       <c r="AA25" t="inlineStr">
         <is>
           <t>2025-05-08</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3228,10 +3223,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>124880358</v>
+        <v>124880305</v>
       </c>
       <c r="B26" t="n">
-        <v>78810</v>
+        <v>57513</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3244,21 +3239,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3268,10 +3263,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>433076</v>
+        <v>434128</v>
       </c>
       <c r="R26" t="n">
-        <v>6935108</v>
+        <v>6936677</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3308,7 +3303,7 @@
       </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>Rikligt</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3335,10 +3330,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>124880361</v>
+        <v>124880331</v>
       </c>
       <c r="B27" t="n">
-        <v>78810</v>
+        <v>91030</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3351,21 +3346,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3375,10 +3370,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>433311</v>
+        <v>433193</v>
       </c>
       <c r="R27" t="n">
-        <v>6935592</v>
+        <v>6935352</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3411,11 +3406,6 @@
       <c r="AA27" t="inlineStr">
         <is>
           <t>2025-05-08</t>
-        </is>
-      </c>
-      <c r="AC27" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3442,10 +3432,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>124880340</v>
+        <v>124880290</v>
       </c>
       <c r="B28" t="n">
-        <v>91030</v>
+        <v>57513</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3458,21 +3448,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3482,10 +3472,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>433661</v>
+        <v>433820</v>
       </c>
       <c r="R28" t="n">
-        <v>6935941</v>
+        <v>6936000</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3518,6 +3508,11 @@
       <c r="AA28" t="inlineStr">
         <is>
           <t>2025-05-08</t>
+        </is>
+      </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3544,10 +3539,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>124880360</v>
+        <v>124880345</v>
       </c>
       <c r="B29" t="n">
-        <v>78810</v>
+        <v>91030</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3560,21 +3555,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3584,10 +3579,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>433248</v>
+        <v>434057</v>
       </c>
       <c r="R29" t="n">
-        <v>6935491</v>
+        <v>6936091</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3620,11 +3615,6 @@
       <c r="AA29" t="inlineStr">
         <is>
           <t>2025-05-08</t>
-        </is>
-      </c>
-      <c r="AC29" t="inlineStr">
-        <is>
-          <t>Mycket rikligt</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3651,10 +3641,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>124880369</v>
+        <v>124880317</v>
       </c>
       <c r="B30" t="n">
-        <v>78810</v>
+        <v>57513</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3667,21 +3657,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3691,10 +3681,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>434091</v>
+        <v>434538</v>
       </c>
       <c r="R30" t="n">
-        <v>6936122</v>
+        <v>6936895</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3731,7 +3721,7 @@
       </c>
       <c r="AC30" t="inlineStr">
         <is>
-          <t>Mycket rikligt</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3758,10 +3748,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>124880345</v>
+        <v>124880278</v>
       </c>
       <c r="B31" t="n">
-        <v>91030</v>
+        <v>57513</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3774,21 +3764,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3798,10 +3788,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>434057</v>
+        <v>433331</v>
       </c>
       <c r="R31" t="n">
-        <v>6936091</v>
+        <v>6935597</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3834,6 +3824,11 @@
       <c r="AA31" t="inlineStr">
         <is>
           <t>2025-05-08</t>
+        </is>
+      </c>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3860,10 +3855,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>124880333</v>
+        <v>124880313</v>
       </c>
       <c r="B32" t="n">
-        <v>91030</v>
+        <v>57513</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3876,21 +3871,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3900,10 +3895,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>433376</v>
+        <v>434447</v>
       </c>
       <c r="R32" t="n">
-        <v>6935725</v>
+        <v>6936828</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3936,6 +3931,11 @@
       <c r="AA32" t="inlineStr">
         <is>
           <t>2025-05-08</t>
+        </is>
+      </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3962,10 +3962,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>124880278</v>
+        <v>124880365</v>
       </c>
       <c r="B33" t="n">
-        <v>57513</v>
+        <v>78810</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -3978,21 +3978,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4002,10 +4002,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>433331</v>
+        <v>433755</v>
       </c>
       <c r="R33" t="n">
-        <v>6935597</v>
+        <v>6935995</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4042,7 +4042,7 @@
       </c>
       <c r="AC33" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4069,7 +4069,7 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>124880343</v>
+        <v>124880350</v>
       </c>
       <c r="B34" t="n">
         <v>91030</v>
@@ -4109,10 +4109,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>433952</v>
+        <v>434118</v>
       </c>
       <c r="R34" t="n">
-        <v>6936054</v>
+        <v>6936187</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4171,10 +4171,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>124880373</v>
+        <v>124880288</v>
       </c>
       <c r="B35" t="n">
-        <v>78810</v>
+        <v>57513</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4187,21 +4187,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4211,10 +4211,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>434482</v>
+        <v>433505</v>
       </c>
       <c r="R35" t="n">
-        <v>6936858</v>
+        <v>6935809</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4251,7 +4251,7 @@
       </c>
       <c r="AC35" t="inlineStr">
         <is>
-          <t>Rikligt</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4278,7 +4278,7 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>124880295</v>
+        <v>124880303</v>
       </c>
       <c r="B36" t="n">
         <v>57513</v>
@@ -4318,10 +4318,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>433952</v>
+        <v>434113</v>
       </c>
       <c r="R36" t="n">
-        <v>6936043</v>
+        <v>6936181</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4358,7 +4358,7 @@
       </c>
       <c r="AC36" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4385,7 +4385,7 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>124880290</v>
+        <v>124880299</v>
       </c>
       <c r="B37" t="n">
         <v>57513</v>
@@ -4425,10 +4425,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>433820</v>
+        <v>434112</v>
       </c>
       <c r="R37" t="n">
-        <v>6936000</v>
+        <v>6936130</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4492,7 +4492,7 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>124880299</v>
+        <v>124880318</v>
       </c>
       <c r="B38" t="n">
         <v>57513</v>
@@ -4532,10 +4532,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>434112</v>
+        <v>434664</v>
       </c>
       <c r="R38" t="n">
-        <v>6936130</v>
+        <v>6936929</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4599,10 +4599,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>124880329</v>
+        <v>124880361</v>
       </c>
       <c r="B39" t="n">
-        <v>91030</v>
+        <v>78810</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4615,21 +4615,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4639,10 +4639,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>433106</v>
+        <v>433311</v>
       </c>
       <c r="R39" t="n">
-        <v>6935174</v>
+        <v>6935592</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4675,6 +4675,11 @@
       <c r="AA39" t="inlineStr">
         <is>
           <t>2025-05-08</t>
+        </is>
+      </c>
+      <c r="AC39" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4701,10 +4706,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>124880283</v>
+        <v>124880371</v>
       </c>
       <c r="B40" t="n">
-        <v>57513</v>
+        <v>78810</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4717,21 +4722,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4741,10 +4746,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>433376</v>
+        <v>434167</v>
       </c>
       <c r="R40" t="n">
-        <v>6935695</v>
+        <v>6936378</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4781,7 +4786,7 @@
       </c>
       <c r="AC40" t="inlineStr">
         <is>
-          <t>Ringhack färska</t>
+          <t>Mycket rikligt</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4808,10 +4813,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>124880316</v>
+        <v>124880364</v>
       </c>
       <c r="B41" t="n">
-        <v>57513</v>
+        <v>78810</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -4824,21 +4829,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4848,10 +4853,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>434532</v>
+        <v>433682</v>
       </c>
       <c r="R41" t="n">
-        <v>6936893</v>
+        <v>6935955</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4888,7 +4893,7 @@
       </c>
       <c r="AC41" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Mycket rikligt</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4915,10 +4920,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>124880303</v>
+        <v>124880358</v>
       </c>
       <c r="B42" t="n">
-        <v>57513</v>
+        <v>78810</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -4931,21 +4936,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4955,10 +4960,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>434113</v>
+        <v>433076</v>
       </c>
       <c r="R42" t="n">
-        <v>6936181</v>
+        <v>6935108</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4995,7 +5000,7 @@
       </c>
       <c r="AC42" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5022,7 +5027,7 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>124880310</v>
+        <v>124880296</v>
       </c>
       <c r="B43" t="n">
         <v>57513</v>
@@ -5062,10 +5067,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>434385</v>
+        <v>434019</v>
       </c>
       <c r="R43" t="n">
-        <v>6936814</v>
+        <v>6936070</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5129,7 +5134,7 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>124880305</v>
+        <v>124880314</v>
       </c>
       <c r="B44" t="n">
         <v>57513</v>
@@ -5169,10 +5174,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>434128</v>
+        <v>434484</v>
       </c>
       <c r="R44" t="n">
-        <v>6936677</v>
+        <v>6936850</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5236,10 +5241,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>124880372</v>
+        <v>124880315</v>
       </c>
       <c r="B45" t="n">
-        <v>78810</v>
+        <v>57513</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5252,21 +5257,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5276,10 +5281,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>434443</v>
+        <v>434466</v>
       </c>
       <c r="R45" t="n">
-        <v>6936839</v>
+        <v>6936862</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5316,7 +5321,7 @@
       </c>
       <c r="AC45" t="inlineStr">
         <is>
-          <t>Mycket rikligt</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5450,10 +5455,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>124880315</v>
+        <v>124880326</v>
       </c>
       <c r="B47" t="n">
-        <v>57513</v>
+        <v>91008</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5466,21 +5471,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>100109</v>
+        <v>1108</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5490,10 +5495,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>434466</v>
+        <v>434175</v>
       </c>
       <c r="R47" t="n">
-        <v>6936862</v>
+        <v>6936309</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5526,11 +5531,6 @@
       <c r="AA47" t="inlineStr">
         <is>
           <t>2025-05-08</t>
-        </is>
-      </c>
-      <c r="AC47" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5557,7 +5557,7 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>124880319</v>
+        <v>124880310</v>
       </c>
       <c r="B48" t="n">
         <v>57513</v>
@@ -5597,10 +5597,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>434789</v>
+        <v>434385</v>
       </c>
       <c r="R48" t="n">
-        <v>6936947</v>
+        <v>6936814</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5664,7 +5664,7 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>124880344</v>
+        <v>124880337</v>
       </c>
       <c r="B49" t="n">
         <v>91030</v>
@@ -5704,10 +5704,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>434028</v>
+        <v>433534</v>
       </c>
       <c r="R49" t="n">
-        <v>6936084</v>
+        <v>6935858</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5766,7 +5766,7 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>124880331</v>
+        <v>124880343</v>
       </c>
       <c r="B50" t="n">
         <v>91030</v>
@@ -5806,10 +5806,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>433193</v>
+        <v>433952</v>
       </c>
       <c r="R50" t="n">
-        <v>6935352</v>
+        <v>6936054</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5868,10 +5868,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>124880346</v>
+        <v>124880237</v>
       </c>
       <c r="B51" t="n">
-        <v>91030</v>
+        <v>91012</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -5884,21 +5884,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>5432</v>
+        <v>1202</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5908,10 +5908,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>434113</v>
+        <v>433636</v>
       </c>
       <c r="R51" t="n">
-        <v>6936148</v>
+        <v>6935914</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5970,10 +5970,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>124880371</v>
+        <v>124880286</v>
       </c>
       <c r="B52" t="n">
-        <v>78810</v>
+        <v>57513</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -5986,21 +5986,21 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -6010,10 +6010,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>434167</v>
+        <v>433434</v>
       </c>
       <c r="R52" t="n">
-        <v>6936378</v>
+        <v>6935749</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6050,7 +6050,7 @@
       </c>
       <c r="AC52" t="inlineStr">
         <is>
-          <t>Mycket rikligt</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD52" t="b">

--- a/artfynd/A 9618-2025 artfynd.xlsx
+++ b/artfynd/A 9618-2025 artfynd.xlsx
@@ -2071,10 +2071,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>124880283</v>
+        <v>124880355</v>
       </c>
       <c r="B15" t="n">
-        <v>57513</v>
+        <v>91030</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2087,21 +2087,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2111,10 +2111,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>433376</v>
+        <v>434478</v>
       </c>
       <c r="R15" t="n">
-        <v>6935695</v>
+        <v>6936874</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2147,11 +2147,6 @@
       <c r="AA15" t="inlineStr">
         <is>
           <t>2025-05-08</t>
-        </is>
-      </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2178,10 +2173,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>124880355</v>
+        <v>124880283</v>
       </c>
       <c r="B16" t="n">
-        <v>91030</v>
+        <v>57513</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2194,21 +2189,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2218,10 +2213,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>434478</v>
+        <v>433376</v>
       </c>
       <c r="R16" t="n">
-        <v>6936874</v>
+        <v>6935695</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2254,6 +2249,11 @@
       <c r="AA16" t="inlineStr">
         <is>
           <t>2025-05-08</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -5868,10 +5868,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>124880237</v>
+        <v>124880286</v>
       </c>
       <c r="B51" t="n">
-        <v>91012</v>
+        <v>57513</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -5884,21 +5884,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5908,10 +5908,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>433636</v>
+        <v>433434</v>
       </c>
       <c r="R51" t="n">
-        <v>6935914</v>
+        <v>6935749</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5944,6 +5944,11 @@
       <c r="AA51" t="inlineStr">
         <is>
           <t>2025-05-08</t>
+        </is>
+      </c>
+      <c r="AC51" t="inlineStr">
+        <is>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -5970,10 +5975,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>124880286</v>
+        <v>124880237</v>
       </c>
       <c r="B52" t="n">
-        <v>57513</v>
+        <v>91012</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -5986,21 +5991,21 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -6010,10 +6015,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>433434</v>
+        <v>433636</v>
       </c>
       <c r="R52" t="n">
-        <v>6935749</v>
+        <v>6935914</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6046,11 +6051,6 @@
       <c r="AA52" t="inlineStr">
         <is>
           <t>2025-05-08</t>
-        </is>
-      </c>
-      <c r="AC52" t="inlineStr">
-        <is>
-          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD52" t="b">

--- a/artfynd/A 9618-2025 artfynd.xlsx
+++ b/artfynd/A 9618-2025 artfynd.xlsx
@@ -1026,7 +1026,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124880332</v>
+        <v>124880353</v>
       </c>
       <c r="B5" t="n">
         <v>91030</v>
@@ -1066,10 +1066,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>433197</v>
+        <v>434173</v>
       </c>
       <c r="R5" t="n">
-        <v>6935385</v>
+        <v>6936342</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1128,10 +1128,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124880373</v>
+        <v>124880296</v>
       </c>
       <c r="B6" t="n">
-        <v>78810</v>
+        <v>57513</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1144,21 +1144,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1168,10 +1168,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>434482</v>
+        <v>434019</v>
       </c>
       <c r="R6" t="n">
-        <v>6936858</v>
+        <v>6936070</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1208,7 +1208,7 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>Rikligt</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1235,10 +1235,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124880360</v>
+        <v>124880333</v>
       </c>
       <c r="B7" t="n">
-        <v>78810</v>
+        <v>91030</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1251,21 +1251,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1275,10 +1275,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>433248</v>
+        <v>433376</v>
       </c>
       <c r="R7" t="n">
-        <v>6935491</v>
+        <v>6935725</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1311,11 +1311,6 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-05-08</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Mycket rikligt</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1342,10 +1337,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124880319</v>
+        <v>124880360</v>
       </c>
       <c r="B8" t="n">
-        <v>57513</v>
+        <v>78810</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1358,21 +1353,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1382,10 +1377,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>434789</v>
+        <v>433248</v>
       </c>
       <c r="R8" t="n">
-        <v>6936947</v>
+        <v>6935491</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1422,7 +1417,7 @@
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Mycket rikligt</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1449,7 +1444,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124880359</v>
+        <v>124880372</v>
       </c>
       <c r="B9" t="n">
         <v>78810</v>
@@ -1489,10 +1484,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>433093</v>
+        <v>434443</v>
       </c>
       <c r="R9" t="n">
-        <v>6935150</v>
+        <v>6936839</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1529,7 +1524,7 @@
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>Rikligt</t>
+          <t>Mycket rikligt</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1556,10 +1551,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124880340</v>
+        <v>124880315</v>
       </c>
       <c r="B10" t="n">
-        <v>91030</v>
+        <v>57513</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1572,21 +1567,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1596,10 +1591,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>433661</v>
+        <v>434466</v>
       </c>
       <c r="R10" t="n">
-        <v>6935941</v>
+        <v>6936862</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1632,6 +1627,11 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-05-08</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1658,10 +1658,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124880324</v>
+        <v>124880316</v>
       </c>
       <c r="B11" t="n">
-        <v>91008</v>
+        <v>57513</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1674,21 +1674,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1108</v>
+        <v>100109</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1698,10 +1698,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>433261</v>
+        <v>434532</v>
       </c>
       <c r="R11" t="n">
-        <v>6935504</v>
+        <v>6936893</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1734,6 +1734,11 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-05-08</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1760,10 +1765,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>124880344</v>
+        <v>124880358</v>
       </c>
       <c r="B12" t="n">
-        <v>91030</v>
+        <v>78810</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1776,21 +1781,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1800,10 +1805,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>434028</v>
+        <v>433076</v>
       </c>
       <c r="R12" t="n">
-        <v>6936084</v>
+        <v>6935108</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1836,6 +1841,11 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-05-08</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1862,10 +1872,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>124880338</v>
+        <v>124880310</v>
       </c>
       <c r="B13" t="n">
-        <v>91030</v>
+        <v>57513</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1878,21 +1888,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1902,10 +1912,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>433585</v>
+        <v>434385</v>
       </c>
       <c r="R13" t="n">
-        <v>6935882</v>
+        <v>6936814</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1938,6 +1948,11 @@
       <c r="AA13" t="inlineStr">
         <is>
           <t>2025-05-08</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1964,7 +1979,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>124880316</v>
+        <v>124880305</v>
       </c>
       <c r="B14" t="n">
         <v>57513</v>
@@ -2004,10 +2019,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>434532</v>
+        <v>434128</v>
       </c>
       <c r="R14" t="n">
-        <v>6936893</v>
+        <v>6936677</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2071,10 +2086,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>124880355</v>
+        <v>124880275</v>
       </c>
       <c r="B15" t="n">
-        <v>91030</v>
+        <v>57513</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2087,21 +2102,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2111,10 +2126,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>434478</v>
+        <v>432954</v>
       </c>
       <c r="R15" t="n">
-        <v>6936874</v>
+        <v>6934982</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2147,6 +2162,11 @@
       <c r="AA15" t="inlineStr">
         <is>
           <t>2025-05-08</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2173,7 +2193,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>124880283</v>
+        <v>124880319</v>
       </c>
       <c r="B16" t="n">
         <v>57513</v>
@@ -2213,10 +2233,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>433376</v>
+        <v>434789</v>
       </c>
       <c r="R16" t="n">
-        <v>6935695</v>
+        <v>6936947</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2253,7 +2273,7 @@
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>Ringhack färska</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2280,10 +2300,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>124880372</v>
+        <v>124880355</v>
       </c>
       <c r="B17" t="n">
-        <v>78810</v>
+        <v>91030</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2296,21 +2316,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2320,10 +2340,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>434443</v>
+        <v>434478</v>
       </c>
       <c r="R17" t="n">
-        <v>6936839</v>
+        <v>6936874</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2356,11 +2376,6 @@
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-05-08</t>
-        </is>
-      </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>Mycket rikligt</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2387,10 +2402,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>124880275</v>
+        <v>124880331</v>
       </c>
       <c r="B18" t="n">
-        <v>57513</v>
+        <v>91030</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2403,21 +2418,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2427,10 +2442,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>432954</v>
+        <v>433193</v>
       </c>
       <c r="R18" t="n">
-        <v>6934982</v>
+        <v>6935352</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2463,11 +2478,6 @@
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-05-08</t>
-        </is>
-      </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2494,10 +2504,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>124880369</v>
+        <v>124880343</v>
       </c>
       <c r="B19" t="n">
-        <v>78810</v>
+        <v>91030</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2510,21 +2520,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2534,10 +2544,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>434091</v>
+        <v>433952</v>
       </c>
       <c r="R19" t="n">
-        <v>6936122</v>
+        <v>6936054</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2570,11 +2580,6 @@
       <c r="AA19" t="inlineStr">
         <is>
           <t>2025-05-08</t>
-        </is>
-      </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>Mycket rikligt</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2601,7 +2606,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>124880295</v>
+        <v>124880317</v>
       </c>
       <c r="B20" t="n">
         <v>57513</v>
@@ -2641,10 +2646,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>433952</v>
+        <v>434538</v>
       </c>
       <c r="R20" t="n">
-        <v>6936043</v>
+        <v>6936895</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2681,7 +2686,7 @@
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2708,10 +2713,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>124880353</v>
+        <v>124880237</v>
       </c>
       <c r="B21" t="n">
-        <v>91030</v>
+        <v>91012</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2724,21 +2729,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>5432</v>
+        <v>1202</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2748,10 +2753,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>434173</v>
+        <v>433636</v>
       </c>
       <c r="R21" t="n">
-        <v>6936342</v>
+        <v>6935914</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2810,10 +2815,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>124880346</v>
+        <v>124880326</v>
       </c>
       <c r="B22" t="n">
-        <v>91030</v>
+        <v>91008</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2826,21 +2831,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>5432</v>
+        <v>1108</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2850,10 +2855,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>434113</v>
+        <v>434175</v>
       </c>
       <c r="R22" t="n">
-        <v>6936148</v>
+        <v>6936309</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2912,10 +2917,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>124880333</v>
+        <v>124880373</v>
       </c>
       <c r="B23" t="n">
-        <v>91030</v>
+        <v>78810</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2928,21 +2933,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2952,10 +2957,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>433376</v>
+        <v>434482</v>
       </c>
       <c r="R23" t="n">
-        <v>6935725</v>
+        <v>6936858</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2988,6 +2993,11 @@
       <c r="AA23" t="inlineStr">
         <is>
           <t>2025-05-08</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3014,10 +3024,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>124880329</v>
+        <v>124880283</v>
       </c>
       <c r="B24" t="n">
-        <v>91030</v>
+        <v>57513</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3030,21 +3040,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3054,10 +3064,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>433106</v>
+        <v>433376</v>
       </c>
       <c r="R24" t="n">
-        <v>6935174</v>
+        <v>6935695</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3090,6 +3100,11 @@
       <c r="AA24" t="inlineStr">
         <is>
           <t>2025-05-08</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3116,7 +3131,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>124880304</v>
+        <v>124880313</v>
       </c>
       <c r="B25" t="n">
         <v>57513</v>
@@ -3156,10 +3171,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>434155</v>
+        <v>434447</v>
       </c>
       <c r="R25" t="n">
-        <v>6936279</v>
+        <v>6936828</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3196,7 +3211,7 @@
       </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3223,10 +3238,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>124880305</v>
+        <v>124880338</v>
       </c>
       <c r="B26" t="n">
-        <v>57513</v>
+        <v>91030</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3239,21 +3254,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3263,10 +3278,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>434128</v>
+        <v>433585</v>
       </c>
       <c r="R26" t="n">
-        <v>6936677</v>
+        <v>6935882</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3299,11 +3314,6 @@
       <c r="AA26" t="inlineStr">
         <is>
           <t>2025-05-08</t>
-        </is>
-      </c>
-      <c r="AC26" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3330,7 +3340,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>124880331</v>
+        <v>124880337</v>
       </c>
       <c r="B27" t="n">
         <v>91030</v>
@@ -3370,10 +3380,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>433193</v>
+        <v>433534</v>
       </c>
       <c r="R27" t="n">
-        <v>6935352</v>
+        <v>6935858</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3432,7 +3442,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>124880290</v>
+        <v>124880288</v>
       </c>
       <c r="B28" t="n">
         <v>57513</v>
@@ -3472,10 +3482,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>433820</v>
+        <v>433505</v>
       </c>
       <c r="R28" t="n">
-        <v>6936000</v>
+        <v>6935809</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3539,10 +3549,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>124880345</v>
+        <v>124880290</v>
       </c>
       <c r="B29" t="n">
-        <v>91030</v>
+        <v>57513</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3555,21 +3565,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3579,10 +3589,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>434057</v>
+        <v>433820</v>
       </c>
       <c r="R29" t="n">
-        <v>6936091</v>
+        <v>6936000</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3615,6 +3625,11 @@
       <c r="AA29" t="inlineStr">
         <is>
           <t>2025-05-08</t>
+        </is>
+      </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3641,7 +3656,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>124880317</v>
+        <v>124880303</v>
       </c>
       <c r="B30" t="n">
         <v>57513</v>
@@ -3681,10 +3696,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>434538</v>
+        <v>434113</v>
       </c>
       <c r="R30" t="n">
-        <v>6936895</v>
+        <v>6936181</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3721,7 +3736,7 @@
       </c>
       <c r="AC30" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3748,10 +3763,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>124880278</v>
+        <v>124880367</v>
       </c>
       <c r="B31" t="n">
-        <v>57513</v>
+        <v>78810</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3764,21 +3779,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3788,10 +3803,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>433331</v>
+        <v>433984</v>
       </c>
       <c r="R31" t="n">
-        <v>6935597</v>
+        <v>6936073</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3828,7 +3843,7 @@
       </c>
       <c r="AC31" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Mycket rikligt</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3855,10 +3870,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>124880313</v>
+        <v>124880365</v>
       </c>
       <c r="B32" t="n">
-        <v>57513</v>
+        <v>78810</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3871,21 +3886,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3895,10 +3910,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>434447</v>
+        <v>433755</v>
       </c>
       <c r="R32" t="n">
-        <v>6936828</v>
+        <v>6935995</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3935,7 +3950,7 @@
       </c>
       <c r="AC32" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3962,7 +3977,7 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>124880365</v>
+        <v>124880369</v>
       </c>
       <c r="B33" t="n">
         <v>78810</v>
@@ -4002,10 +4017,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>433755</v>
+        <v>434091</v>
       </c>
       <c r="R33" t="n">
-        <v>6935995</v>
+        <v>6936122</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4042,7 +4057,7 @@
       </c>
       <c r="AC33" t="inlineStr">
         <is>
-          <t>Rikligt</t>
+          <t>Mycket rikligt</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4069,10 +4084,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>124880350</v>
+        <v>124880371</v>
       </c>
       <c r="B34" t="n">
-        <v>91030</v>
+        <v>78810</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4085,21 +4100,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4109,10 +4124,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>434118</v>
+        <v>434167</v>
       </c>
       <c r="R34" t="n">
-        <v>6936187</v>
+        <v>6936378</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4145,6 +4160,11 @@
       <c r="AA34" t="inlineStr">
         <is>
           <t>2025-05-08</t>
+        </is>
+      </c>
+      <c r="AC34" t="inlineStr">
+        <is>
+          <t>Mycket rikligt</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4171,7 +4191,7 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>124880288</v>
+        <v>124880314</v>
       </c>
       <c r="B35" t="n">
         <v>57513</v>
@@ -4211,10 +4231,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>433505</v>
+        <v>434484</v>
       </c>
       <c r="R35" t="n">
-        <v>6935809</v>
+        <v>6936850</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4278,10 +4298,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>124880303</v>
+        <v>124880346</v>
       </c>
       <c r="B36" t="n">
-        <v>57513</v>
+        <v>91030</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4294,21 +4314,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4321,7 +4341,7 @@
         <v>434113</v>
       </c>
       <c r="R36" t="n">
-        <v>6936181</v>
+        <v>6936148</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4354,11 +4374,6 @@
       <c r="AA36" t="inlineStr">
         <is>
           <t>2025-05-08</t>
-        </is>
-      </c>
-      <c r="AC36" t="inlineStr">
-        <is>
-          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4385,7 +4400,7 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>124880299</v>
+        <v>124880295</v>
       </c>
       <c r="B37" t="n">
         <v>57513</v>
@@ -4425,10 +4440,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>434112</v>
+        <v>433952</v>
       </c>
       <c r="R37" t="n">
-        <v>6936130</v>
+        <v>6936043</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4492,10 +4507,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>124880318</v>
+        <v>124880361</v>
       </c>
       <c r="B38" t="n">
-        <v>57513</v>
+        <v>78810</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4508,21 +4523,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4532,10 +4547,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>434664</v>
+        <v>433311</v>
       </c>
       <c r="R38" t="n">
-        <v>6936929</v>
+        <v>6935592</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4572,7 +4587,7 @@
       </c>
       <c r="AC38" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4599,10 +4614,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>124880361</v>
+        <v>124880329</v>
       </c>
       <c r="B39" t="n">
-        <v>78810</v>
+        <v>91030</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4615,21 +4630,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4639,10 +4654,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>433311</v>
+        <v>433106</v>
       </c>
       <c r="R39" t="n">
-        <v>6935592</v>
+        <v>6935174</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4675,11 +4690,6 @@
       <c r="AA39" t="inlineStr">
         <is>
           <t>2025-05-08</t>
-        </is>
-      </c>
-      <c r="AC39" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4706,10 +4716,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>124880371</v>
+        <v>124880344</v>
       </c>
       <c r="B40" t="n">
-        <v>78810</v>
+        <v>91030</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4722,21 +4732,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4746,10 +4756,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>434167</v>
+        <v>434028</v>
       </c>
       <c r="R40" t="n">
-        <v>6936378</v>
+        <v>6936084</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4782,11 +4792,6 @@
       <c r="AA40" t="inlineStr">
         <is>
           <t>2025-05-08</t>
-        </is>
-      </c>
-      <c r="AC40" t="inlineStr">
-        <is>
-          <t>Mycket rikligt</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4813,10 +4818,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>124880364</v>
+        <v>124880304</v>
       </c>
       <c r="B41" t="n">
-        <v>78810</v>
+        <v>57513</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -4829,21 +4834,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4853,10 +4858,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>433682</v>
+        <v>434155</v>
       </c>
       <c r="R41" t="n">
-        <v>6935955</v>
+        <v>6936279</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4893,7 +4898,7 @@
       </c>
       <c r="AC41" t="inlineStr">
         <is>
-          <t>Mycket rikligt</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4920,10 +4925,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>124880358</v>
+        <v>124880318</v>
       </c>
       <c r="B42" t="n">
-        <v>78810</v>
+        <v>57513</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -4936,21 +4941,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4960,10 +4965,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>433076</v>
+        <v>434664</v>
       </c>
       <c r="R42" t="n">
-        <v>6935108</v>
+        <v>6936929</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5000,7 +5005,7 @@
       </c>
       <c r="AC42" t="inlineStr">
         <is>
-          <t>Rikligt</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5027,10 +5032,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>124880296</v>
+        <v>124880332</v>
       </c>
       <c r="B43" t="n">
-        <v>57513</v>
+        <v>91030</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5043,21 +5048,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5067,10 +5072,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>434019</v>
+        <v>433197</v>
       </c>
       <c r="R43" t="n">
-        <v>6936070</v>
+        <v>6935385</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5103,11 +5108,6 @@
       <c r="AA43" t="inlineStr">
         <is>
           <t>2025-05-08</t>
-        </is>
-      </c>
-      <c r="AC43" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5134,10 +5134,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>124880314</v>
+        <v>124880364</v>
       </c>
       <c r="B44" t="n">
-        <v>57513</v>
+        <v>78810</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5150,21 +5150,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5174,10 +5174,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>434484</v>
+        <v>433682</v>
       </c>
       <c r="R44" t="n">
-        <v>6936850</v>
+        <v>6935955</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5214,7 +5214,7 @@
       </c>
       <c r="AC44" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Mycket rikligt</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5241,7 +5241,7 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>124880315</v>
+        <v>124880278</v>
       </c>
       <c r="B45" t="n">
         <v>57513</v>
@@ -5281,10 +5281,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>434466</v>
+        <v>433331</v>
       </c>
       <c r="R45" t="n">
-        <v>6936862</v>
+        <v>6935597</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5348,10 +5348,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>124880367</v>
+        <v>124880324</v>
       </c>
       <c r="B46" t="n">
-        <v>78810</v>
+        <v>91008</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5364,21 +5364,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6425</v>
+        <v>1108</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5388,10 +5388,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>433984</v>
+        <v>433261</v>
       </c>
       <c r="R46" t="n">
-        <v>6936073</v>
+        <v>6935504</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5424,11 +5424,6 @@
       <c r="AA46" t="inlineStr">
         <is>
           <t>2025-05-08</t>
-        </is>
-      </c>
-      <c r="AC46" t="inlineStr">
-        <is>
-          <t>Mycket rikligt</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5455,10 +5450,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>124880326</v>
+        <v>124880340</v>
       </c>
       <c r="B47" t="n">
-        <v>91008</v>
+        <v>91030</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5471,21 +5466,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>1108</v>
+        <v>5432</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5495,10 +5490,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>434175</v>
+        <v>433661</v>
       </c>
       <c r="R47" t="n">
-        <v>6936309</v>
+        <v>6935941</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5557,10 +5552,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>124880310</v>
+        <v>124880345</v>
       </c>
       <c r="B48" t="n">
-        <v>57513</v>
+        <v>91030</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5573,21 +5568,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5597,10 +5592,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>434385</v>
+        <v>434057</v>
       </c>
       <c r="R48" t="n">
-        <v>6936814</v>
+        <v>6936091</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5633,11 +5628,6 @@
       <c r="AA48" t="inlineStr">
         <is>
           <t>2025-05-08</t>
-        </is>
-      </c>
-      <c r="AC48" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5664,7 +5654,7 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>124880337</v>
+        <v>124880350</v>
       </c>
       <c r="B49" t="n">
         <v>91030</v>
@@ -5704,10 +5694,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>433534</v>
+        <v>434118</v>
       </c>
       <c r="R49" t="n">
-        <v>6935858</v>
+        <v>6936187</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5766,10 +5756,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>124880343</v>
+        <v>124880299</v>
       </c>
       <c r="B50" t="n">
-        <v>91030</v>
+        <v>57513</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -5782,21 +5772,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5806,10 +5796,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>433952</v>
+        <v>434112</v>
       </c>
       <c r="R50" t="n">
-        <v>6936054</v>
+        <v>6936130</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5842,6 +5832,11 @@
       <c r="AA50" t="inlineStr">
         <is>
           <t>2025-05-08</t>
+        </is>
+      </c>
+      <c r="AC50" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -5975,10 +5970,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>124880237</v>
+        <v>124880359</v>
       </c>
       <c r="B52" t="n">
-        <v>91012</v>
+        <v>78810</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -5991,21 +5986,21 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -6015,10 +6010,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>433636</v>
+        <v>433093</v>
       </c>
       <c r="R52" t="n">
-        <v>6935914</v>
+        <v>6935150</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6051,6 +6046,11 @@
       <c r="AA52" t="inlineStr">
         <is>
           <t>2025-05-08</t>
+        </is>
+      </c>
+      <c r="AC52" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD52" t="b">

--- a/artfynd/A 9618-2025 artfynd.xlsx
+++ b/artfynd/A 9618-2025 artfynd.xlsx
@@ -1026,10 +1026,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124880353</v>
+        <v>124880369</v>
       </c>
       <c r="B5" t="n">
-        <v>91030</v>
+        <v>78947</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1042,21 +1042,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1066,10 +1066,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>434173</v>
+        <v>434091</v>
       </c>
       <c r="R5" t="n">
-        <v>6936342</v>
+        <v>6936122</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1102,6 +1102,11 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-05-08</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Mycket rikligt</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1128,10 +1133,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124880296</v>
+        <v>124880319</v>
       </c>
       <c r="B6" t="n">
-        <v>57513</v>
+        <v>57635</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1168,10 +1173,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>434019</v>
+        <v>434789</v>
       </c>
       <c r="R6" t="n">
-        <v>6936070</v>
+        <v>6936947</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1235,10 +1240,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124880333</v>
+        <v>124880314</v>
       </c>
       <c r="B7" t="n">
-        <v>91030</v>
+        <v>57635</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1251,21 +1256,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1275,10 +1280,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>433376</v>
+        <v>434484</v>
       </c>
       <c r="R7" t="n">
-        <v>6935725</v>
+        <v>6936850</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1311,6 +1316,11 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-05-08</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1337,10 +1347,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124880360</v>
+        <v>124880305</v>
       </c>
       <c r="B8" t="n">
-        <v>78810</v>
+        <v>57635</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1353,21 +1363,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1377,10 +1387,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>433248</v>
+        <v>434128</v>
       </c>
       <c r="R8" t="n">
-        <v>6935491</v>
+        <v>6936677</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1417,7 +1427,7 @@
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>Mycket rikligt</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1444,10 +1454,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124880372</v>
+        <v>124880296</v>
       </c>
       <c r="B9" t="n">
-        <v>78810</v>
+        <v>57635</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1460,21 +1470,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1484,10 +1494,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>434443</v>
+        <v>434019</v>
       </c>
       <c r="R9" t="n">
-        <v>6936839</v>
+        <v>6936070</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1524,7 +1534,7 @@
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>Mycket rikligt</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1551,10 +1561,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124880315</v>
+        <v>124880331</v>
       </c>
       <c r="B10" t="n">
-        <v>57513</v>
+        <v>91184</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1567,21 +1577,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1591,10 +1601,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>434466</v>
+        <v>433193</v>
       </c>
       <c r="R10" t="n">
-        <v>6936862</v>
+        <v>6935352</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1627,11 +1637,6 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-05-08</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1658,10 +1663,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124880316</v>
+        <v>124880346</v>
       </c>
       <c r="B11" t="n">
-        <v>57513</v>
+        <v>91184</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1674,21 +1679,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1698,10 +1703,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>434532</v>
+        <v>434113</v>
       </c>
       <c r="R11" t="n">
-        <v>6936893</v>
+        <v>6936148</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1734,11 +1739,6 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-05-08</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1765,10 +1765,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>124880358</v>
+        <v>124880343</v>
       </c>
       <c r="B12" t="n">
-        <v>78810</v>
+        <v>91184</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1781,21 +1781,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1805,10 +1805,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>433076</v>
+        <v>433952</v>
       </c>
       <c r="R12" t="n">
-        <v>6935108</v>
+        <v>6936054</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1841,11 +1841,6 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-05-08</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1872,10 +1867,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>124880310</v>
+        <v>124880326</v>
       </c>
       <c r="B13" t="n">
-        <v>57513</v>
+        <v>91162</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1888,21 +1883,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100109</v>
+        <v>1108</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1912,10 +1907,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>434385</v>
+        <v>434175</v>
       </c>
       <c r="R13" t="n">
-        <v>6936814</v>
+        <v>6936309</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1948,11 +1943,6 @@
       <c r="AA13" t="inlineStr">
         <is>
           <t>2025-05-08</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1979,10 +1969,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>124880305</v>
+        <v>124880333</v>
       </c>
       <c r="B14" t="n">
-        <v>57513</v>
+        <v>91184</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1995,21 +1985,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2019,10 +2009,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>434128</v>
+        <v>433376</v>
       </c>
       <c r="R14" t="n">
-        <v>6936677</v>
+        <v>6935725</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2055,11 +2045,6 @@
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-05-08</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2086,10 +2071,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>124880275</v>
+        <v>124880365</v>
       </c>
       <c r="B15" t="n">
-        <v>57513</v>
+        <v>78947</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2102,21 +2087,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2126,10 +2111,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>432954</v>
+        <v>433755</v>
       </c>
       <c r="R15" t="n">
-        <v>6934982</v>
+        <v>6935995</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2166,7 +2151,7 @@
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2193,10 +2178,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>124880319</v>
+        <v>124880290</v>
       </c>
       <c r="B16" t="n">
-        <v>57513</v>
+        <v>57635</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2233,10 +2218,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>434789</v>
+        <v>433820</v>
       </c>
       <c r="R16" t="n">
-        <v>6936947</v>
+        <v>6936000</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2300,10 +2285,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>124880355</v>
+        <v>124880360</v>
       </c>
       <c r="B17" t="n">
-        <v>91030</v>
+        <v>78947</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2316,21 +2301,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2340,10 +2325,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>434478</v>
+        <v>433248</v>
       </c>
       <c r="R17" t="n">
-        <v>6936874</v>
+        <v>6935491</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2376,6 +2361,11 @@
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-05-08</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Mycket rikligt</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2402,10 +2392,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>124880331</v>
+        <v>124880299</v>
       </c>
       <c r="B18" t="n">
-        <v>91030</v>
+        <v>57635</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2418,21 +2408,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2442,10 +2432,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>433193</v>
+        <v>434112</v>
       </c>
       <c r="R18" t="n">
-        <v>6935352</v>
+        <v>6936130</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2478,6 +2468,11 @@
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-05-08</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2504,10 +2499,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>124880343</v>
+        <v>124880283</v>
       </c>
       <c r="B19" t="n">
-        <v>91030</v>
+        <v>57635</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2520,21 +2515,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2544,10 +2539,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>433952</v>
+        <v>433376</v>
       </c>
       <c r="R19" t="n">
-        <v>6936054</v>
+        <v>6935695</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2580,6 +2575,11 @@
       <c r="AA19" t="inlineStr">
         <is>
           <t>2025-05-08</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2606,10 +2606,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>124880317</v>
+        <v>124880315</v>
       </c>
       <c r="B20" t="n">
-        <v>57513</v>
+        <v>57635</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2646,10 +2646,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>434538</v>
+        <v>434466</v>
       </c>
       <c r="R20" t="n">
-        <v>6936895</v>
+        <v>6936862</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2686,7 +2686,7 @@
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2713,10 +2713,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>124880237</v>
+        <v>124880338</v>
       </c>
       <c r="B21" t="n">
-        <v>91012</v>
+        <v>91184</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2729,21 +2729,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>1202</v>
+        <v>5432</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2753,10 +2753,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>433636</v>
+        <v>433585</v>
       </c>
       <c r="R21" t="n">
-        <v>6935914</v>
+        <v>6935882</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2815,10 +2815,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>124880326</v>
+        <v>124880358</v>
       </c>
       <c r="B22" t="n">
-        <v>91008</v>
+        <v>78947</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2831,21 +2831,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>1108</v>
+        <v>6425</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2855,10 +2855,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>434175</v>
+        <v>433076</v>
       </c>
       <c r="R22" t="n">
-        <v>6936309</v>
+        <v>6935108</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2891,6 +2891,11 @@
       <c r="AA22" t="inlineStr">
         <is>
           <t>2025-05-08</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2917,10 +2922,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>124880373</v>
+        <v>124880345</v>
       </c>
       <c r="B23" t="n">
-        <v>78810</v>
+        <v>91184</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2933,21 +2938,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2957,10 +2962,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>434482</v>
+        <v>434057</v>
       </c>
       <c r="R23" t="n">
-        <v>6936858</v>
+        <v>6936091</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2993,11 +2998,6 @@
       <c r="AA23" t="inlineStr">
         <is>
           <t>2025-05-08</t>
-        </is>
-      </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3024,10 +3024,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>124880283</v>
+        <v>124880295</v>
       </c>
       <c r="B24" t="n">
-        <v>57513</v>
+        <v>57635</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3064,10 +3064,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>433376</v>
+        <v>433952</v>
       </c>
       <c r="R24" t="n">
-        <v>6935695</v>
+        <v>6936043</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3104,7 +3104,7 @@
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>Ringhack färska</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3131,10 +3131,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>124880313</v>
+        <v>124880278</v>
       </c>
       <c r="B25" t="n">
-        <v>57513</v>
+        <v>57635</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3171,10 +3171,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>434447</v>
+        <v>433331</v>
       </c>
       <c r="R25" t="n">
-        <v>6936828</v>
+        <v>6935597</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3211,7 +3211,7 @@
       </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3238,10 +3238,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>124880338</v>
+        <v>124880318</v>
       </c>
       <c r="B26" t="n">
-        <v>91030</v>
+        <v>57635</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3254,21 +3254,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3278,10 +3278,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>433585</v>
+        <v>434664</v>
       </c>
       <c r="R26" t="n">
-        <v>6935882</v>
+        <v>6936929</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3314,6 +3314,11 @@
       <c r="AA26" t="inlineStr">
         <is>
           <t>2025-05-08</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3340,10 +3345,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>124880337</v>
+        <v>124880288</v>
       </c>
       <c r="B27" t="n">
-        <v>91030</v>
+        <v>57635</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3356,21 +3361,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3380,10 +3385,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>433534</v>
+        <v>433505</v>
       </c>
       <c r="R27" t="n">
-        <v>6935858</v>
+        <v>6935809</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3416,6 +3421,11 @@
       <c r="AA27" t="inlineStr">
         <is>
           <t>2025-05-08</t>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3442,10 +3452,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>124880288</v>
+        <v>124880373</v>
       </c>
       <c r="B28" t="n">
-        <v>57513</v>
+        <v>78947</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3458,21 +3468,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3482,10 +3492,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>433505</v>
+        <v>434482</v>
       </c>
       <c r="R28" t="n">
-        <v>6935809</v>
+        <v>6936858</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3522,7 +3532,7 @@
       </c>
       <c r="AC28" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3549,10 +3559,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>124880290</v>
+        <v>124880337</v>
       </c>
       <c r="B29" t="n">
-        <v>57513</v>
+        <v>91184</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3565,21 +3575,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3589,10 +3599,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>433820</v>
+        <v>433534</v>
       </c>
       <c r="R29" t="n">
-        <v>6936000</v>
+        <v>6935858</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3625,11 +3635,6 @@
       <c r="AA29" t="inlineStr">
         <is>
           <t>2025-05-08</t>
-        </is>
-      </c>
-      <c r="AC29" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3656,10 +3661,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>124880303</v>
+        <v>124880344</v>
       </c>
       <c r="B30" t="n">
-        <v>57513</v>
+        <v>91184</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3672,21 +3677,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3696,10 +3701,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>434113</v>
+        <v>434028</v>
       </c>
       <c r="R30" t="n">
-        <v>6936181</v>
+        <v>6936084</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3732,11 +3737,6 @@
       <c r="AA30" t="inlineStr">
         <is>
           <t>2025-05-08</t>
-        </is>
-      </c>
-      <c r="AC30" t="inlineStr">
-        <is>
-          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3763,10 +3763,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>124880367</v>
+        <v>124880340</v>
       </c>
       <c r="B31" t="n">
-        <v>78810</v>
+        <v>91184</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3779,21 +3779,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3803,10 +3803,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>433984</v>
+        <v>433661</v>
       </c>
       <c r="R31" t="n">
-        <v>6936073</v>
+        <v>6935941</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3839,11 +3839,6 @@
       <c r="AA31" t="inlineStr">
         <is>
           <t>2025-05-08</t>
-        </is>
-      </c>
-      <c r="AC31" t="inlineStr">
-        <is>
-          <t>Mycket rikligt</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3870,10 +3865,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>124880365</v>
+        <v>124880355</v>
       </c>
       <c r="B32" t="n">
-        <v>78810</v>
+        <v>91184</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3886,21 +3881,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3910,10 +3905,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>433755</v>
+        <v>434478</v>
       </c>
       <c r="R32" t="n">
-        <v>6935995</v>
+        <v>6936874</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3946,11 +3941,6 @@
       <c r="AA32" t="inlineStr">
         <is>
           <t>2025-05-08</t>
-        </is>
-      </c>
-      <c r="AC32" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3977,10 +3967,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>124880369</v>
+        <v>124880353</v>
       </c>
       <c r="B33" t="n">
-        <v>78810</v>
+        <v>91184</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -3993,21 +3983,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4017,10 +4007,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>434091</v>
+        <v>434173</v>
       </c>
       <c r="R33" t="n">
-        <v>6936122</v>
+        <v>6936342</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4053,11 +4043,6 @@
       <c r="AA33" t="inlineStr">
         <is>
           <t>2025-05-08</t>
-        </is>
-      </c>
-      <c r="AC33" t="inlineStr">
-        <is>
-          <t>Mycket rikligt</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4084,10 +4069,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>124880371</v>
+        <v>124880310</v>
       </c>
       <c r="B34" t="n">
-        <v>78810</v>
+        <v>57635</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4100,21 +4085,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4124,10 +4109,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>434167</v>
+        <v>434385</v>
       </c>
       <c r="R34" t="n">
-        <v>6936378</v>
+        <v>6936814</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4164,7 +4149,7 @@
       </c>
       <c r="AC34" t="inlineStr">
         <is>
-          <t>Mycket rikligt</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4191,10 +4176,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>124880314</v>
+        <v>124880286</v>
       </c>
       <c r="B35" t="n">
-        <v>57513</v>
+        <v>57635</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4231,10 +4216,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>434484</v>
+        <v>433434</v>
       </c>
       <c r="R35" t="n">
-        <v>6936850</v>
+        <v>6935749</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4271,7 +4256,7 @@
       </c>
       <c r="AC35" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4298,10 +4283,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>124880346</v>
+        <v>124880372</v>
       </c>
       <c r="B36" t="n">
-        <v>91030</v>
+        <v>78947</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4314,21 +4299,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4338,10 +4323,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>434113</v>
+        <v>434443</v>
       </c>
       <c r="R36" t="n">
-        <v>6936148</v>
+        <v>6936839</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4374,6 +4359,11 @@
       <c r="AA36" t="inlineStr">
         <is>
           <t>2025-05-08</t>
+        </is>
+      </c>
+      <c r="AC36" t="inlineStr">
+        <is>
+          <t>Mycket rikligt</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4400,10 +4390,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>124880295</v>
+        <v>124880275</v>
       </c>
       <c r="B37" t="n">
-        <v>57513</v>
+        <v>57635</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4440,10 +4430,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>433952</v>
+        <v>432954</v>
       </c>
       <c r="R37" t="n">
-        <v>6936043</v>
+        <v>6934982</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4507,10 +4497,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>124880361</v>
+        <v>124880237</v>
       </c>
       <c r="B38" t="n">
-        <v>78810</v>
+        <v>91166</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4523,21 +4513,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4547,10 +4537,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>433311</v>
+        <v>433636</v>
       </c>
       <c r="R38" t="n">
-        <v>6935592</v>
+        <v>6935914</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4583,11 +4573,6 @@
       <c r="AA38" t="inlineStr">
         <is>
           <t>2025-05-08</t>
-        </is>
-      </c>
-      <c r="AC38" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4614,10 +4599,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>124880329</v>
+        <v>124880364</v>
       </c>
       <c r="B39" t="n">
-        <v>91030</v>
+        <v>78947</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4630,21 +4615,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4654,10 +4639,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>433106</v>
+        <v>433682</v>
       </c>
       <c r="R39" t="n">
-        <v>6935174</v>
+        <v>6935955</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4690,6 +4675,11 @@
       <c r="AA39" t="inlineStr">
         <is>
           <t>2025-05-08</t>
+        </is>
+      </c>
+      <c r="AC39" t="inlineStr">
+        <is>
+          <t>Mycket rikligt</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4716,10 +4706,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>124880344</v>
+        <v>124880367</v>
       </c>
       <c r="B40" t="n">
-        <v>91030</v>
+        <v>78947</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4732,21 +4722,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4756,10 +4746,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>434028</v>
+        <v>433984</v>
       </c>
       <c r="R40" t="n">
-        <v>6936084</v>
+        <v>6936073</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4792,6 +4782,11 @@
       <c r="AA40" t="inlineStr">
         <is>
           <t>2025-05-08</t>
+        </is>
+      </c>
+      <c r="AC40" t="inlineStr">
+        <is>
+          <t>Mycket rikligt</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4818,10 +4813,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>124880304</v>
+        <v>124880329</v>
       </c>
       <c r="B41" t="n">
-        <v>57513</v>
+        <v>91184</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -4834,21 +4829,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4858,10 +4853,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>434155</v>
+        <v>433106</v>
       </c>
       <c r="R41" t="n">
-        <v>6936279</v>
+        <v>6935174</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4894,11 +4889,6 @@
       <c r="AA41" t="inlineStr">
         <is>
           <t>2025-05-08</t>
-        </is>
-      </c>
-      <c r="AC41" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4925,10 +4915,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>124880318</v>
+        <v>124880332</v>
       </c>
       <c r="B42" t="n">
-        <v>57513</v>
+        <v>91184</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -4941,21 +4931,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4965,10 +4955,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>434664</v>
+        <v>433197</v>
       </c>
       <c r="R42" t="n">
-        <v>6936929</v>
+        <v>6935385</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5001,11 +4991,6 @@
       <c r="AA42" t="inlineStr">
         <is>
           <t>2025-05-08</t>
-        </is>
-      </c>
-      <c r="AC42" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5032,10 +5017,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>124880332</v>
+        <v>124880350</v>
       </c>
       <c r="B43" t="n">
-        <v>91030</v>
+        <v>91184</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5072,10 +5057,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>433197</v>
+        <v>434118</v>
       </c>
       <c r="R43" t="n">
-        <v>6935385</v>
+        <v>6936187</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5134,10 +5119,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>124880364</v>
+        <v>124880361</v>
       </c>
       <c r="B44" t="n">
-        <v>78810</v>
+        <v>78947</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5174,10 +5159,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>433682</v>
+        <v>433311</v>
       </c>
       <c r="R44" t="n">
-        <v>6935955</v>
+        <v>6935592</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5214,7 +5199,7 @@
       </c>
       <c r="AC44" t="inlineStr">
         <is>
-          <t>Mycket rikligt</t>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5241,10 +5226,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>124880278</v>
+        <v>124880303</v>
       </c>
       <c r="B45" t="n">
-        <v>57513</v>
+        <v>57635</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5281,10 +5266,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>433331</v>
+        <v>434113</v>
       </c>
       <c r="R45" t="n">
-        <v>6935597</v>
+        <v>6936181</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5321,7 +5306,7 @@
       </c>
       <c r="AC45" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5348,10 +5333,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>124880324</v>
+        <v>124880304</v>
       </c>
       <c r="B46" t="n">
-        <v>91008</v>
+        <v>57635</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5364,21 +5349,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>1108</v>
+        <v>100109</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5388,10 +5373,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>433261</v>
+        <v>434155</v>
       </c>
       <c r="R46" t="n">
-        <v>6935504</v>
+        <v>6936279</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5424,6 +5409,11 @@
       <c r="AA46" t="inlineStr">
         <is>
           <t>2025-05-08</t>
+        </is>
+      </c>
+      <c r="AC46" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5450,10 +5440,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>124880340</v>
+        <v>124880359</v>
       </c>
       <c r="B47" t="n">
-        <v>91030</v>
+        <v>78947</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5466,21 +5456,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5490,10 +5480,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>433661</v>
+        <v>433093</v>
       </c>
       <c r="R47" t="n">
-        <v>6935941</v>
+        <v>6935150</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5526,6 +5516,11 @@
       <c r="AA47" t="inlineStr">
         <is>
           <t>2025-05-08</t>
+        </is>
+      </c>
+      <c r="AC47" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5552,10 +5547,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>124880345</v>
+        <v>124880317</v>
       </c>
       <c r="B48" t="n">
-        <v>91030</v>
+        <v>57635</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5568,21 +5563,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5592,10 +5587,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>434057</v>
+        <v>434538</v>
       </c>
       <c r="R48" t="n">
-        <v>6936091</v>
+        <v>6936895</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5628,6 +5623,11 @@
       <c r="AA48" t="inlineStr">
         <is>
           <t>2025-05-08</t>
+        </is>
+      </c>
+      <c r="AC48" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5654,10 +5654,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>124880350</v>
+        <v>124880324</v>
       </c>
       <c r="B49" t="n">
-        <v>91030</v>
+        <v>91162</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -5670,21 +5670,21 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>5432</v>
+        <v>1108</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5694,10 +5694,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>434118</v>
+        <v>433261</v>
       </c>
       <c r="R49" t="n">
-        <v>6936187</v>
+        <v>6935504</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5756,10 +5756,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>124880299</v>
+        <v>124880316</v>
       </c>
       <c r="B50" t="n">
-        <v>57513</v>
+        <v>57635</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -5796,10 +5796,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>434112</v>
+        <v>434532</v>
       </c>
       <c r="R50" t="n">
-        <v>6936130</v>
+        <v>6936893</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5863,10 +5863,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>124880286</v>
+        <v>124880371</v>
       </c>
       <c r="B51" t="n">
-        <v>57513</v>
+        <v>78947</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -5879,21 +5879,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5903,10 +5903,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>433434</v>
+        <v>434167</v>
       </c>
       <c r="R51" t="n">
-        <v>6935749</v>
+        <v>6936378</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5943,7 +5943,7 @@
       </c>
       <c r="AC51" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Mycket rikligt</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -5970,10 +5970,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>124880359</v>
+        <v>124880313</v>
       </c>
       <c r="B52" t="n">
-        <v>78810</v>
+        <v>57635</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -5986,21 +5986,21 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -6010,10 +6010,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>433093</v>
+        <v>434447</v>
       </c>
       <c r="R52" t="n">
-        <v>6935150</v>
+        <v>6936828</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6050,7 +6050,7 @@
       </c>
       <c r="AC52" t="inlineStr">
         <is>
-          <t>Rikligt</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD52" t="b">

--- a/artfynd/A 9618-2025 artfynd.xlsx
+++ b/artfynd/A 9618-2025 artfynd.xlsx
@@ -2499,10 +2499,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>124880283</v>
+        <v>124880338</v>
       </c>
       <c r="B19" t="n">
-        <v>57635</v>
+        <v>91184</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2515,21 +2515,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2539,10 +2539,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>433376</v>
+        <v>433585</v>
       </c>
       <c r="R19" t="n">
-        <v>6935695</v>
+        <v>6935882</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2575,11 +2575,6 @@
       <c r="AA19" t="inlineStr">
         <is>
           <t>2025-05-08</t>
-        </is>
-      </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2606,10 +2601,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>124880315</v>
+        <v>124880358</v>
       </c>
       <c r="B20" t="n">
-        <v>57635</v>
+        <v>78947</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2622,21 +2617,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2646,10 +2641,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>434466</v>
+        <v>433076</v>
       </c>
       <c r="R20" t="n">
-        <v>6936862</v>
+        <v>6935108</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2686,7 +2681,7 @@
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2713,10 +2708,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>124880338</v>
+        <v>124880283</v>
       </c>
       <c r="B21" t="n">
-        <v>91184</v>
+        <v>57635</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2729,21 +2724,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2753,10 +2748,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>433585</v>
+        <v>433376</v>
       </c>
       <c r="R21" t="n">
-        <v>6935882</v>
+        <v>6935695</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2789,6 +2784,11 @@
       <c r="AA21" t="inlineStr">
         <is>
           <t>2025-05-08</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2815,10 +2815,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>124880358</v>
+        <v>124880315</v>
       </c>
       <c r="B22" t="n">
-        <v>78947</v>
+        <v>57635</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2831,21 +2831,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2855,10 +2855,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>433076</v>
+        <v>434466</v>
       </c>
       <c r="R22" t="n">
-        <v>6935108</v>
+        <v>6936862</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2895,7 +2895,7 @@
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>Rikligt</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -4497,10 +4497,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>124880237</v>
+        <v>124880364</v>
       </c>
       <c r="B38" t="n">
-        <v>91166</v>
+        <v>78947</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4513,21 +4513,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4537,10 +4537,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>433636</v>
+        <v>433682</v>
       </c>
       <c r="R38" t="n">
-        <v>6935914</v>
+        <v>6935955</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4573,6 +4573,11 @@
       <c r="AA38" t="inlineStr">
         <is>
           <t>2025-05-08</t>
+        </is>
+      </c>
+      <c r="AC38" t="inlineStr">
+        <is>
+          <t>Mycket rikligt</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4599,10 +4604,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>124880364</v>
+        <v>124880237</v>
       </c>
       <c r="B39" t="n">
-        <v>78947</v>
+        <v>91166</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4615,21 +4620,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4639,10 +4644,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>433682</v>
+        <v>433636</v>
       </c>
       <c r="R39" t="n">
-        <v>6935955</v>
+        <v>6935914</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4675,11 +4680,6 @@
       <c r="AA39" t="inlineStr">
         <is>
           <t>2025-05-08</t>
-        </is>
-      </c>
-      <c r="AC39" t="inlineStr">
-        <is>
-          <t>Mycket rikligt</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -5547,10 +5547,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>124880317</v>
+        <v>124880324</v>
       </c>
       <c r="B48" t="n">
-        <v>57635</v>
+        <v>91162</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5563,21 +5563,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>100109</v>
+        <v>1108</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5587,10 +5587,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>434538</v>
+        <v>433261</v>
       </c>
       <c r="R48" t="n">
-        <v>6936895</v>
+        <v>6935504</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5623,11 +5623,6 @@
       <c r="AA48" t="inlineStr">
         <is>
           <t>2025-05-08</t>
-        </is>
-      </c>
-      <c r="AC48" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5654,10 +5649,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>124880324</v>
+        <v>124880317</v>
       </c>
       <c r="B49" t="n">
-        <v>91162</v>
+        <v>57635</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -5670,21 +5665,21 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>1108</v>
+        <v>100109</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5694,10 +5689,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>433261</v>
+        <v>434538</v>
       </c>
       <c r="R49" t="n">
-        <v>6935504</v>
+        <v>6936895</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5730,6 +5725,11 @@
       <c r="AA49" t="inlineStr">
         <is>
           <t>2025-05-08</t>
+        </is>
+      </c>
+      <c r="AC49" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD49" t="b">

--- a/artfynd/A 9618-2025 artfynd.xlsx
+++ b/artfynd/A 9618-2025 artfynd.xlsx
@@ -1026,10 +1026,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124880369</v>
+        <v>124880318</v>
       </c>
       <c r="B5" t="n">
-        <v>78947</v>
+        <v>57635</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1042,21 +1042,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1066,10 +1066,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>434091</v>
+        <v>434664</v>
       </c>
       <c r="R5" t="n">
-        <v>6936122</v>
+        <v>6936929</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1106,7 +1106,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Mycket rikligt</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1133,7 +1133,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124880319</v>
+        <v>124880288</v>
       </c>
       <c r="B6" t="n">
         <v>57635</v>
@@ -1173,10 +1173,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>434789</v>
+        <v>433505</v>
       </c>
       <c r="R6" t="n">
-        <v>6936947</v>
+        <v>6935809</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1240,7 +1240,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124880314</v>
+        <v>124880305</v>
       </c>
       <c r="B7" t="n">
         <v>57635</v>
@@ -1280,10 +1280,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>434484</v>
+        <v>434128</v>
       </c>
       <c r="R7" t="n">
-        <v>6936850</v>
+        <v>6936677</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1347,10 +1347,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124880305</v>
+        <v>124880345</v>
       </c>
       <c r="B8" t="n">
-        <v>57635</v>
+        <v>91184</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1363,21 +1363,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1387,10 +1387,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>434128</v>
+        <v>434057</v>
       </c>
       <c r="R8" t="n">
-        <v>6936677</v>
+        <v>6936091</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1423,11 +1423,6 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-05-08</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1454,10 +1449,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124880296</v>
+        <v>124880331</v>
       </c>
       <c r="B9" t="n">
-        <v>57635</v>
+        <v>91184</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1470,21 +1465,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1494,10 +1489,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>434019</v>
+        <v>433193</v>
       </c>
       <c r="R9" t="n">
-        <v>6936070</v>
+        <v>6935352</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1530,11 +1525,6 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-05-08</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1561,7 +1551,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124880331</v>
+        <v>124880338</v>
       </c>
       <c r="B10" t="n">
         <v>91184</v>
@@ -1601,10 +1591,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>433193</v>
+        <v>433585</v>
       </c>
       <c r="R10" t="n">
-        <v>6935352</v>
+        <v>6935882</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1663,10 +1653,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124880346</v>
+        <v>124880286</v>
       </c>
       <c r="B11" t="n">
-        <v>91184</v>
+        <v>57635</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1679,21 +1669,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1703,10 +1693,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>434113</v>
+        <v>433434</v>
       </c>
       <c r="R11" t="n">
-        <v>6936148</v>
+        <v>6935749</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1739,6 +1729,11 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-05-08</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1765,10 +1760,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>124880343</v>
+        <v>124880237</v>
       </c>
       <c r="B12" t="n">
-        <v>91184</v>
+        <v>91166</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1781,21 +1776,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>5432</v>
+        <v>1202</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1805,10 +1800,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>433952</v>
+        <v>433636</v>
       </c>
       <c r="R12" t="n">
-        <v>6936054</v>
+        <v>6935914</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1867,10 +1862,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>124880326</v>
+        <v>124880364</v>
       </c>
       <c r="B13" t="n">
-        <v>91162</v>
+        <v>78947</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1883,21 +1878,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1108</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1907,10 +1902,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>434175</v>
+        <v>433682</v>
       </c>
       <c r="R13" t="n">
-        <v>6936309</v>
+        <v>6935955</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1943,6 +1938,11 @@
       <c r="AA13" t="inlineStr">
         <is>
           <t>2025-05-08</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Mycket rikligt</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1969,7 +1969,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>124880333</v>
+        <v>124880337</v>
       </c>
       <c r="B14" t="n">
         <v>91184</v>
@@ -2009,10 +2009,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>433376</v>
+        <v>433534</v>
       </c>
       <c r="R14" t="n">
-        <v>6935725</v>
+        <v>6935858</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2071,10 +2071,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>124880365</v>
+        <v>124880290</v>
       </c>
       <c r="B15" t="n">
-        <v>78947</v>
+        <v>57635</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2087,21 +2087,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2111,10 +2111,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>433755</v>
+        <v>433820</v>
       </c>
       <c r="R15" t="n">
-        <v>6935995</v>
+        <v>6936000</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2151,7 +2151,7 @@
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>Rikligt</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2178,10 +2178,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>124880290</v>
+        <v>124880350</v>
       </c>
       <c r="B16" t="n">
-        <v>57635</v>
+        <v>91184</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2194,21 +2194,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2218,10 +2218,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>433820</v>
+        <v>434118</v>
       </c>
       <c r="R16" t="n">
-        <v>6936000</v>
+        <v>6936187</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2254,11 +2254,6 @@
       <c r="AA16" t="inlineStr">
         <is>
           <t>2025-05-08</t>
-        </is>
-      </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2285,10 +2280,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>124880360</v>
+        <v>124880326</v>
       </c>
       <c r="B17" t="n">
-        <v>78947</v>
+        <v>91162</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2301,21 +2296,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>1108</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2325,10 +2320,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>433248</v>
+        <v>434175</v>
       </c>
       <c r="R17" t="n">
-        <v>6935491</v>
+        <v>6936309</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2361,11 +2356,6 @@
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-05-08</t>
-        </is>
-      </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>Mycket rikligt</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2392,7 +2382,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>124880299</v>
+        <v>124880315</v>
       </c>
       <c r="B18" t="n">
         <v>57635</v>
@@ -2432,10 +2422,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>434112</v>
+        <v>434466</v>
       </c>
       <c r="R18" t="n">
-        <v>6936130</v>
+        <v>6936862</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2499,10 +2489,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>124880338</v>
+        <v>124880314</v>
       </c>
       <c r="B19" t="n">
-        <v>91184</v>
+        <v>57635</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2515,21 +2505,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2539,10 +2529,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>433585</v>
+        <v>434484</v>
       </c>
       <c r="R19" t="n">
-        <v>6935882</v>
+        <v>6936850</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2575,6 +2565,11 @@
       <c r="AA19" t="inlineStr">
         <is>
           <t>2025-05-08</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2601,10 +2596,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>124880358</v>
+        <v>124880316</v>
       </c>
       <c r="B20" t="n">
-        <v>78947</v>
+        <v>57635</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2617,21 +2612,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2641,10 +2636,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>433076</v>
+        <v>434532</v>
       </c>
       <c r="R20" t="n">
-        <v>6935108</v>
+        <v>6936893</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2681,7 +2676,7 @@
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>Rikligt</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2708,10 +2703,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>124880283</v>
+        <v>124880358</v>
       </c>
       <c r="B21" t="n">
-        <v>57635</v>
+        <v>78947</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2724,21 +2719,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2748,10 +2743,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>433376</v>
+        <v>433076</v>
       </c>
       <c r="R21" t="n">
-        <v>6935695</v>
+        <v>6935108</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2788,7 +2783,7 @@
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>Ringhack färska</t>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2815,7 +2810,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>124880315</v>
+        <v>124880310</v>
       </c>
       <c r="B22" t="n">
         <v>57635</v>
@@ -2855,10 +2850,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>434466</v>
+        <v>434385</v>
       </c>
       <c r="R22" t="n">
-        <v>6936862</v>
+        <v>6936814</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2922,10 +2917,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>124880345</v>
+        <v>124880365</v>
       </c>
       <c r="B23" t="n">
-        <v>91184</v>
+        <v>78947</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2938,21 +2933,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2962,10 +2957,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>434057</v>
+        <v>433755</v>
       </c>
       <c r="R23" t="n">
-        <v>6936091</v>
+        <v>6935995</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2998,6 +2993,11 @@
       <c r="AA23" t="inlineStr">
         <is>
           <t>2025-05-08</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3024,10 +3024,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>124880295</v>
+        <v>124880359</v>
       </c>
       <c r="B24" t="n">
-        <v>57635</v>
+        <v>78947</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3040,21 +3040,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3064,10 +3064,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>433952</v>
+        <v>433093</v>
       </c>
       <c r="R24" t="n">
-        <v>6936043</v>
+        <v>6935150</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3104,7 +3104,7 @@
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3131,10 +3131,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>124880278</v>
+        <v>124880344</v>
       </c>
       <c r="B25" t="n">
-        <v>57635</v>
+        <v>91184</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3147,21 +3147,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3171,10 +3171,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>433331</v>
+        <v>434028</v>
       </c>
       <c r="R25" t="n">
-        <v>6935597</v>
+        <v>6936084</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3207,11 +3207,6 @@
       <c r="AA25" t="inlineStr">
         <is>
           <t>2025-05-08</t>
-        </is>
-      </c>
-      <c r="AC25" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3238,10 +3233,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>124880318</v>
+        <v>124880324</v>
       </c>
       <c r="B26" t="n">
-        <v>57635</v>
+        <v>91162</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3254,21 +3249,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>100109</v>
+        <v>1108</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3278,10 +3273,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>434664</v>
+        <v>433261</v>
       </c>
       <c r="R26" t="n">
-        <v>6936929</v>
+        <v>6935504</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3314,11 +3309,6 @@
       <c r="AA26" t="inlineStr">
         <is>
           <t>2025-05-08</t>
-        </is>
-      </c>
-      <c r="AC26" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3345,10 +3335,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>124880288</v>
+        <v>124880360</v>
       </c>
       <c r="B27" t="n">
-        <v>57635</v>
+        <v>78947</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3361,21 +3351,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3385,10 +3375,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>433505</v>
+        <v>433248</v>
       </c>
       <c r="R27" t="n">
-        <v>6935809</v>
+        <v>6935491</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3425,7 +3415,7 @@
       </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Mycket rikligt</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3452,10 +3442,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>124880373</v>
+        <v>124880329</v>
       </c>
       <c r="B28" t="n">
-        <v>78947</v>
+        <v>91184</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3468,21 +3458,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3492,10 +3482,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>434482</v>
+        <v>433106</v>
       </c>
       <c r="R28" t="n">
-        <v>6936858</v>
+        <v>6935174</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3528,11 +3518,6 @@
       <c r="AA28" t="inlineStr">
         <is>
           <t>2025-05-08</t>
-        </is>
-      </c>
-      <c r="AC28" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3559,10 +3544,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>124880337</v>
+        <v>124880299</v>
       </c>
       <c r="B29" t="n">
-        <v>91184</v>
+        <v>57635</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3575,21 +3560,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3599,10 +3584,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>433534</v>
+        <v>434112</v>
       </c>
       <c r="R29" t="n">
-        <v>6935858</v>
+        <v>6936130</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3635,6 +3620,11 @@
       <c r="AA29" t="inlineStr">
         <is>
           <t>2025-05-08</t>
+        </is>
+      </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3661,10 +3651,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>124880344</v>
+        <v>124880313</v>
       </c>
       <c r="B30" t="n">
-        <v>91184</v>
+        <v>57635</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3677,21 +3667,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3701,10 +3691,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>434028</v>
+        <v>434447</v>
       </c>
       <c r="R30" t="n">
-        <v>6936084</v>
+        <v>6936828</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3737,6 +3727,11 @@
       <c r="AA30" t="inlineStr">
         <is>
           <t>2025-05-08</t>
+        </is>
+      </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3763,10 +3758,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>124880340</v>
+        <v>124880303</v>
       </c>
       <c r="B31" t="n">
-        <v>91184</v>
+        <v>57635</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3779,21 +3774,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3803,10 +3798,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>433661</v>
+        <v>434113</v>
       </c>
       <c r="R31" t="n">
-        <v>6935941</v>
+        <v>6936181</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3839,6 +3834,11 @@
       <c r="AA31" t="inlineStr">
         <is>
           <t>2025-05-08</t>
+        </is>
+      </c>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3865,10 +3865,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>124880355</v>
+        <v>124880372</v>
       </c>
       <c r="B32" t="n">
-        <v>91184</v>
+        <v>78947</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3881,21 +3881,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3905,10 +3905,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>434478</v>
+        <v>434443</v>
       </c>
       <c r="R32" t="n">
-        <v>6936874</v>
+        <v>6936839</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3941,6 +3941,11 @@
       <c r="AA32" t="inlineStr">
         <is>
           <t>2025-05-08</t>
+        </is>
+      </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>Mycket rikligt</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3967,10 +3972,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>124880353</v>
+        <v>124880373</v>
       </c>
       <c r="B33" t="n">
-        <v>91184</v>
+        <v>78947</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -3983,21 +3988,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4007,10 +4012,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>434173</v>
+        <v>434482</v>
       </c>
       <c r="R33" t="n">
-        <v>6936342</v>
+        <v>6936858</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4043,6 +4048,11 @@
       <c r="AA33" t="inlineStr">
         <is>
           <t>2025-05-08</t>
+        </is>
+      </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4069,10 +4079,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>124880310</v>
+        <v>124880346</v>
       </c>
       <c r="B34" t="n">
-        <v>57635</v>
+        <v>91184</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4085,21 +4095,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4109,10 +4119,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>434385</v>
+        <v>434113</v>
       </c>
       <c r="R34" t="n">
-        <v>6936814</v>
+        <v>6936148</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4145,11 +4155,6 @@
       <c r="AA34" t="inlineStr">
         <is>
           <t>2025-05-08</t>
-        </is>
-      </c>
-      <c r="AC34" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4176,10 +4181,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>124880286</v>
+        <v>124880333</v>
       </c>
       <c r="B35" t="n">
-        <v>57635</v>
+        <v>91184</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4192,21 +4197,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4216,10 +4221,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>433434</v>
+        <v>433376</v>
       </c>
       <c r="R35" t="n">
-        <v>6935749</v>
+        <v>6935725</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4252,11 +4257,6 @@
       <c r="AA35" t="inlineStr">
         <is>
           <t>2025-05-08</t>
-        </is>
-      </c>
-      <c r="AC35" t="inlineStr">
-        <is>
-          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4283,10 +4283,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>124880372</v>
+        <v>124880295</v>
       </c>
       <c r="B36" t="n">
-        <v>78947</v>
+        <v>57635</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4299,21 +4299,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4323,10 +4323,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>434443</v>
+        <v>433952</v>
       </c>
       <c r="R36" t="n">
-        <v>6936839</v>
+        <v>6936043</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4363,7 +4363,7 @@
       </c>
       <c r="AC36" t="inlineStr">
         <is>
-          <t>Mycket rikligt</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4390,7 +4390,7 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>124880275</v>
+        <v>124880304</v>
       </c>
       <c r="B37" t="n">
         <v>57635</v>
@@ -4430,10 +4430,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>432954</v>
+        <v>434155</v>
       </c>
       <c r="R37" t="n">
-        <v>6934982</v>
+        <v>6936279</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4497,10 +4497,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>124880364</v>
+        <v>124880317</v>
       </c>
       <c r="B38" t="n">
-        <v>78947</v>
+        <v>57635</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4513,21 +4513,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4537,10 +4537,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>433682</v>
+        <v>434538</v>
       </c>
       <c r="R38" t="n">
-        <v>6935955</v>
+        <v>6936895</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4577,7 +4577,7 @@
       </c>
       <c r="AC38" t="inlineStr">
         <is>
-          <t>Mycket rikligt</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4604,10 +4604,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>124880237</v>
+        <v>124880319</v>
       </c>
       <c r="B39" t="n">
-        <v>91166</v>
+        <v>57635</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4620,21 +4620,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4644,10 +4644,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>433636</v>
+        <v>434789</v>
       </c>
       <c r="R39" t="n">
-        <v>6935914</v>
+        <v>6936947</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4680,6 +4680,11 @@
       <c r="AA39" t="inlineStr">
         <is>
           <t>2025-05-08</t>
+        </is>
+      </c>
+      <c r="AC39" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4706,10 +4711,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>124880367</v>
+        <v>124880355</v>
       </c>
       <c r="B40" t="n">
-        <v>78947</v>
+        <v>91184</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4722,21 +4727,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4746,10 +4751,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>433984</v>
+        <v>434478</v>
       </c>
       <c r="R40" t="n">
-        <v>6936073</v>
+        <v>6936874</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4782,11 +4787,6 @@
       <c r="AA40" t="inlineStr">
         <is>
           <t>2025-05-08</t>
-        </is>
-      </c>
-      <c r="AC40" t="inlineStr">
-        <is>
-          <t>Mycket rikligt</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4813,10 +4813,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>124880329</v>
+        <v>124880369</v>
       </c>
       <c r="B41" t="n">
-        <v>91184</v>
+        <v>78947</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -4829,21 +4829,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4853,10 +4853,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>433106</v>
+        <v>434091</v>
       </c>
       <c r="R41" t="n">
-        <v>6935174</v>
+        <v>6936122</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4889,6 +4889,11 @@
       <c r="AA41" t="inlineStr">
         <is>
           <t>2025-05-08</t>
+        </is>
+      </c>
+      <c r="AC41" t="inlineStr">
+        <is>
+          <t>Mycket rikligt</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4915,7 +4920,7 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>124880332</v>
+        <v>124880340</v>
       </c>
       <c r="B42" t="n">
         <v>91184</v>
@@ -4955,10 +4960,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>433197</v>
+        <v>433661</v>
       </c>
       <c r="R42" t="n">
-        <v>6935385</v>
+        <v>6935941</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5017,10 +5022,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>124880350</v>
+        <v>124880361</v>
       </c>
       <c r="B43" t="n">
-        <v>91184</v>
+        <v>78947</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5033,21 +5038,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5057,10 +5062,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>434118</v>
+        <v>433311</v>
       </c>
       <c r="R43" t="n">
-        <v>6936187</v>
+        <v>6935592</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5093,6 +5098,11 @@
       <c r="AA43" t="inlineStr">
         <is>
           <t>2025-05-08</t>
+        </is>
+      </c>
+      <c r="AC43" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5119,10 +5129,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>124880361</v>
+        <v>124880278</v>
       </c>
       <c r="B44" t="n">
-        <v>78947</v>
+        <v>57635</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5135,21 +5145,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5159,10 +5169,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>433311</v>
+        <v>433331</v>
       </c>
       <c r="R44" t="n">
-        <v>6935592</v>
+        <v>6935597</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5199,7 +5209,7 @@
       </c>
       <c r="AC44" t="inlineStr">
         <is>
-          <t>Rikligt</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5226,10 +5236,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>124880303</v>
+        <v>124880343</v>
       </c>
       <c r="B45" t="n">
-        <v>57635</v>
+        <v>91184</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5242,21 +5252,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5266,10 +5276,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>434113</v>
+        <v>433952</v>
       </c>
       <c r="R45" t="n">
-        <v>6936181</v>
+        <v>6936054</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5302,11 +5312,6 @@
       <c r="AA45" t="inlineStr">
         <is>
           <t>2025-05-08</t>
-        </is>
-      </c>
-      <c r="AC45" t="inlineStr">
-        <is>
-          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5333,10 +5338,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>124880304</v>
+        <v>124880353</v>
       </c>
       <c r="B46" t="n">
-        <v>57635</v>
+        <v>91184</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5349,21 +5354,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5373,10 +5378,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>434155</v>
+        <v>434173</v>
       </c>
       <c r="R46" t="n">
-        <v>6936279</v>
+        <v>6936342</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5409,11 +5414,6 @@
       <c r="AA46" t="inlineStr">
         <is>
           <t>2025-05-08</t>
-        </is>
-      </c>
-      <c r="AC46" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5440,7 +5440,7 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>124880359</v>
+        <v>124880367</v>
       </c>
       <c r="B47" t="n">
         <v>78947</v>
@@ -5480,10 +5480,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>433093</v>
+        <v>433984</v>
       </c>
       <c r="R47" t="n">
-        <v>6935150</v>
+        <v>6936073</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5520,7 +5520,7 @@
       </c>
       <c r="AC47" t="inlineStr">
         <is>
-          <t>Rikligt</t>
+          <t>Mycket rikligt</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5547,10 +5547,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>124880324</v>
+        <v>124880275</v>
       </c>
       <c r="B48" t="n">
-        <v>91162</v>
+        <v>57635</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5563,21 +5563,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>1108</v>
+        <v>100109</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5587,10 +5587,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>433261</v>
+        <v>432954</v>
       </c>
       <c r="R48" t="n">
-        <v>6935504</v>
+        <v>6934982</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5623,6 +5623,11 @@
       <c r="AA48" t="inlineStr">
         <is>
           <t>2025-05-08</t>
+        </is>
+      </c>
+      <c r="AC48" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5649,10 +5654,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>124880317</v>
+        <v>124880371</v>
       </c>
       <c r="B49" t="n">
-        <v>57635</v>
+        <v>78947</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -5665,21 +5670,21 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5689,10 +5694,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>434538</v>
+        <v>434167</v>
       </c>
       <c r="R49" t="n">
-        <v>6936895</v>
+        <v>6936378</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5729,7 +5734,7 @@
       </c>
       <c r="AC49" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Mycket rikligt</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5756,10 +5761,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>124880316</v>
+        <v>124880332</v>
       </c>
       <c r="B50" t="n">
-        <v>57635</v>
+        <v>91184</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -5772,21 +5777,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5796,10 +5801,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>434532</v>
+        <v>433197</v>
       </c>
       <c r="R50" t="n">
-        <v>6936893</v>
+        <v>6935385</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5832,11 +5837,6 @@
       <c r="AA50" t="inlineStr">
         <is>
           <t>2025-05-08</t>
-        </is>
-      </c>
-      <c r="AC50" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -5863,10 +5863,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>124880371</v>
+        <v>124880283</v>
       </c>
       <c r="B51" t="n">
-        <v>78947</v>
+        <v>57635</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -5879,21 +5879,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5903,10 +5903,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>434167</v>
+        <v>433376</v>
       </c>
       <c r="R51" t="n">
-        <v>6936378</v>
+        <v>6935695</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5943,7 +5943,7 @@
       </c>
       <c r="AC51" t="inlineStr">
         <is>
-          <t>Mycket rikligt</t>
+          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -5970,7 +5970,7 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>124880313</v>
+        <v>124880296</v>
       </c>
       <c r="B52" t="n">
         <v>57635</v>
@@ -6010,10 +6010,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>434447</v>
+        <v>434019</v>
       </c>
       <c r="R52" t="n">
-        <v>6936828</v>
+        <v>6936070</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6050,7 +6050,7 @@
       </c>
       <c r="AC52" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD52" t="b">

--- a/artfynd/A 9618-2025 artfynd.xlsx
+++ b/artfynd/A 9618-2025 artfynd.xlsx
@@ -1760,10 +1760,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>124880237</v>
+        <v>124880364</v>
       </c>
       <c r="B12" t="n">
-        <v>91166</v>
+        <v>78947</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1776,21 +1776,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1800,10 +1800,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>433636</v>
+        <v>433682</v>
       </c>
       <c r="R12" t="n">
-        <v>6935914</v>
+        <v>6935955</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1836,6 +1836,11 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-05-08</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Mycket rikligt</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1862,10 +1867,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>124880364</v>
+        <v>124880237</v>
       </c>
       <c r="B13" t="n">
-        <v>78947</v>
+        <v>91166</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1878,21 +1883,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1902,10 +1907,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>433682</v>
+        <v>433636</v>
       </c>
       <c r="R13" t="n">
-        <v>6935955</v>
+        <v>6935914</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1938,11 +1943,6 @@
       <c r="AA13" t="inlineStr">
         <is>
           <t>2025-05-08</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>Mycket rikligt</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2178,10 +2178,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>124880350</v>
+        <v>124880315</v>
       </c>
       <c r="B16" t="n">
-        <v>91184</v>
+        <v>57635</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2194,21 +2194,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2218,10 +2218,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>434118</v>
+        <v>434466</v>
       </c>
       <c r="R16" t="n">
-        <v>6936187</v>
+        <v>6936862</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2254,6 +2254,11 @@
       <c r="AA16" t="inlineStr">
         <is>
           <t>2025-05-08</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2382,10 +2387,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>124880315</v>
+        <v>124880350</v>
       </c>
       <c r="B18" t="n">
-        <v>57635</v>
+        <v>91184</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2398,21 +2403,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2422,10 +2427,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>434466</v>
+        <v>434118</v>
       </c>
       <c r="R18" t="n">
-        <v>6936862</v>
+        <v>6936187</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2458,11 +2463,6 @@
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-05-08</t>
-        </is>
-      </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -3442,10 +3442,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>124880329</v>
+        <v>124880299</v>
       </c>
       <c r="B28" t="n">
-        <v>91184</v>
+        <v>57635</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3458,21 +3458,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3482,10 +3482,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>433106</v>
+        <v>434112</v>
       </c>
       <c r="R28" t="n">
-        <v>6935174</v>
+        <v>6936130</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3518,6 +3518,11 @@
       <c r="AA28" t="inlineStr">
         <is>
           <t>2025-05-08</t>
+        </is>
+      </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3544,7 +3549,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>124880299</v>
+        <v>124880313</v>
       </c>
       <c r="B29" t="n">
         <v>57635</v>
@@ -3584,10 +3589,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>434112</v>
+        <v>434447</v>
       </c>
       <c r="R29" t="n">
-        <v>6936130</v>
+        <v>6936828</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3624,7 +3629,7 @@
       </c>
       <c r="AC29" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3651,10 +3656,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>124880313</v>
+        <v>124880329</v>
       </c>
       <c r="B30" t="n">
-        <v>57635</v>
+        <v>91184</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3667,21 +3672,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3691,10 +3696,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>434447</v>
+        <v>433106</v>
       </c>
       <c r="R30" t="n">
-        <v>6936828</v>
+        <v>6935174</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3727,11 +3732,6 @@
       <c r="AA30" t="inlineStr">
         <is>
           <t>2025-05-08</t>
-        </is>
-      </c>
-      <c r="AC30" t="inlineStr">
-        <is>
-          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4920,10 +4920,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>124880340</v>
+        <v>124880278</v>
       </c>
       <c r="B42" t="n">
-        <v>91184</v>
+        <v>57635</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -4936,21 +4936,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4960,10 +4960,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>433661</v>
+        <v>433331</v>
       </c>
       <c r="R42" t="n">
-        <v>6935941</v>
+        <v>6935597</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4996,6 +4996,11 @@
       <c r="AA42" t="inlineStr">
         <is>
           <t>2025-05-08</t>
+        </is>
+      </c>
+      <c r="AC42" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5022,10 +5027,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>124880361</v>
+        <v>124880340</v>
       </c>
       <c r="B43" t="n">
-        <v>78947</v>
+        <v>91184</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5038,21 +5043,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5062,10 +5067,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>433311</v>
+        <v>433661</v>
       </c>
       <c r="R43" t="n">
-        <v>6935592</v>
+        <v>6935941</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5098,11 +5103,6 @@
       <c r="AA43" t="inlineStr">
         <is>
           <t>2025-05-08</t>
-        </is>
-      </c>
-      <c r="AC43" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5129,10 +5129,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>124880278</v>
+        <v>124880361</v>
       </c>
       <c r="B44" t="n">
-        <v>57635</v>
+        <v>78947</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5145,21 +5145,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5169,10 +5169,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>433331</v>
+        <v>433311</v>
       </c>
       <c r="R44" t="n">
-        <v>6935597</v>
+        <v>6935592</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5209,7 +5209,7 @@
       </c>
       <c r="AC44" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD44" t="b">

--- a/artfynd/A 9618-2025 artfynd.xlsx
+++ b/artfynd/A 9618-2025 artfynd.xlsx
@@ -1551,10 +1551,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124880338</v>
+        <v>124880286</v>
       </c>
       <c r="B10" t="n">
-        <v>91184</v>
+        <v>57635</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1567,21 +1567,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1591,10 +1591,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>433585</v>
+        <v>433434</v>
       </c>
       <c r="R10" t="n">
-        <v>6935882</v>
+        <v>6935749</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1627,6 +1627,11 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-05-08</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1653,10 +1658,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124880286</v>
+        <v>124880338</v>
       </c>
       <c r="B11" t="n">
-        <v>57635</v>
+        <v>91184</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1669,21 +1674,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1693,10 +1698,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>433434</v>
+        <v>433585</v>
       </c>
       <c r="R11" t="n">
-        <v>6935749</v>
+        <v>6935882</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1729,11 +1734,6 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-05-08</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -3758,10 +3758,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>124880303</v>
+        <v>124880372</v>
       </c>
       <c r="B31" t="n">
-        <v>57635</v>
+        <v>78947</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3774,21 +3774,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3798,10 +3798,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>434113</v>
+        <v>434443</v>
       </c>
       <c r="R31" t="n">
-        <v>6936181</v>
+        <v>6936839</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3838,7 +3838,7 @@
       </c>
       <c r="AC31" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Mycket rikligt</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3865,7 +3865,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>124880372</v>
+        <v>124880373</v>
       </c>
       <c r="B32" t="n">
         <v>78947</v>
@@ -3905,10 +3905,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>434443</v>
+        <v>434482</v>
       </c>
       <c r="R32" t="n">
-        <v>6936839</v>
+        <v>6936858</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3945,7 +3945,7 @@
       </c>
       <c r="AC32" t="inlineStr">
         <is>
-          <t>Mycket rikligt</t>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3972,10 +3972,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>124880373</v>
+        <v>124880303</v>
       </c>
       <c r="B33" t="n">
-        <v>78947</v>
+        <v>57635</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -3988,21 +3988,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4012,10 +4012,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>434482</v>
+        <v>434113</v>
       </c>
       <c r="R33" t="n">
-        <v>6936858</v>
+        <v>6936181</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4052,7 +4052,7 @@
       </c>
       <c r="AC33" t="inlineStr">
         <is>
-          <t>Rikligt</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD33" t="b">

--- a/artfynd/A 9618-2025 artfynd.xlsx
+++ b/artfynd/A 9618-2025 artfynd.xlsx
@@ -1026,15 +1026,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124880318</v>
+        <v>124880333</v>
       </c>
       <c r="B5" t="n">
-        <v>57635</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91184</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1042,21 +1037,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1066,10 +1061,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>434664</v>
+        <v>433376</v>
       </c>
       <c r="R5" t="n">
-        <v>6936929</v>
+        <v>6935725</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1102,11 +1097,6 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-05-08</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1133,16 +1123,11 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124880288</v>
+        <v>124880295</v>
       </c>
       <c r="B6" t="n">
         <v>57635</v>
       </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
       <c r="D6" t="inlineStr">
         <is>
           <t>NT</t>
@@ -1173,10 +1158,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>433505</v>
+        <v>433952</v>
       </c>
       <c r="R6" t="n">
-        <v>6935809</v>
+        <v>6936043</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1240,16 +1225,11 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124880305</v>
+        <v>124880290</v>
       </c>
       <c r="B7" t="n">
         <v>57635</v>
       </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
       <c r="D7" t="inlineStr">
         <is>
           <t>NT</t>
@@ -1280,10 +1260,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>434128</v>
+        <v>433820</v>
       </c>
       <c r="R7" t="n">
-        <v>6936677</v>
+        <v>6936000</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1347,15 +1327,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124880345</v>
+        <v>124880326</v>
       </c>
       <c r="B8" t="n">
-        <v>91184</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91162</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1363,21 +1338,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>5432</v>
+        <v>1108</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1387,10 +1362,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>434057</v>
+        <v>434175</v>
       </c>
       <c r="R8" t="n">
-        <v>6936091</v>
+        <v>6936309</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1449,16 +1424,11 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124880331</v>
+        <v>124880329</v>
       </c>
       <c r="B9" t="n">
         <v>91184</v>
       </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
       <c r="D9" t="inlineStr">
         <is>
           <t>NT</t>
@@ -1489,10 +1459,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>433193</v>
+        <v>433106</v>
       </c>
       <c r="R9" t="n">
-        <v>6935352</v>
+        <v>6935174</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1556,11 +1526,6 @@
       <c r="B10" t="n">
         <v>57635</v>
       </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
       <c r="D10" t="inlineStr">
         <is>
           <t>NT</t>
@@ -1658,16 +1623,11 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124880338</v>
+        <v>124880344</v>
       </c>
       <c r="B11" t="n">
         <v>91184</v>
       </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
       <c r="D11" t="inlineStr">
         <is>
           <t>NT</t>
@@ -1698,10 +1658,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>433585</v>
+        <v>434028</v>
       </c>
       <c r="R11" t="n">
-        <v>6935882</v>
+        <v>6936084</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1760,15 +1720,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>124880364</v>
+        <v>124880313</v>
       </c>
       <c r="B12" t="n">
-        <v>78947</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57635</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1776,21 +1731,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1800,10 +1755,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>433682</v>
+        <v>434447</v>
       </c>
       <c r="R12" t="n">
-        <v>6935955</v>
+        <v>6936828</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1840,7 +1795,7 @@
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>Mycket rikligt</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1867,15 +1822,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>124880237</v>
+        <v>124880371</v>
       </c>
       <c r="B13" t="n">
-        <v>91166</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78947</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1883,21 +1833,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1907,10 +1857,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>433636</v>
+        <v>434167</v>
       </c>
       <c r="R13" t="n">
-        <v>6935914</v>
+        <v>6936378</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1943,6 +1893,11 @@
       <c r="AA13" t="inlineStr">
         <is>
           <t>2025-05-08</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Mycket rikligt</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1969,16 +1924,11 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>124880337</v>
+        <v>124880353</v>
       </c>
       <c r="B14" t="n">
         <v>91184</v>
       </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
       <c r="D14" t="inlineStr">
         <is>
           <t>NT</t>
@@ -2009,10 +1959,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>433534</v>
+        <v>434173</v>
       </c>
       <c r="R14" t="n">
-        <v>6935858</v>
+        <v>6936342</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2071,15 +2021,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>124880290</v>
+        <v>124880355</v>
       </c>
       <c r="B15" t="n">
-        <v>57635</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91184</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2087,21 +2032,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2111,10 +2056,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>433820</v>
+        <v>434478</v>
       </c>
       <c r="R15" t="n">
-        <v>6936000</v>
+        <v>6936874</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2147,11 +2092,6 @@
       <c r="AA15" t="inlineStr">
         <is>
           <t>2025-05-08</t>
-        </is>
-      </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2178,15 +2118,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>124880315</v>
+        <v>124880372</v>
       </c>
       <c r="B16" t="n">
-        <v>57635</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78947</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2194,21 +2129,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2218,10 +2153,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>434466</v>
+        <v>434443</v>
       </c>
       <c r="R16" t="n">
-        <v>6936862</v>
+        <v>6936839</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2258,7 +2193,7 @@
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Mycket rikligt</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2285,15 +2220,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>124880326</v>
+        <v>124880338</v>
       </c>
       <c r="B17" t="n">
-        <v>91162</v>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91184</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2301,21 +2231,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1108</v>
+        <v>5432</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2325,10 +2255,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>434175</v>
+        <v>433585</v>
       </c>
       <c r="R17" t="n">
-        <v>6936309</v>
+        <v>6935882</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2387,15 +2317,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>124880350</v>
+        <v>124880359</v>
       </c>
       <c r="B18" t="n">
-        <v>91184</v>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78947</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2403,21 +2328,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2427,10 +2352,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>434118</v>
+        <v>433093</v>
       </c>
       <c r="R18" t="n">
-        <v>6936187</v>
+        <v>6935150</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2463,6 +2388,11 @@
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-05-08</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2489,15 +2419,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>124880314</v>
+        <v>124880350</v>
       </c>
       <c r="B19" t="n">
-        <v>57635</v>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91184</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2505,21 +2430,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2529,10 +2454,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>434484</v>
+        <v>434118</v>
       </c>
       <c r="R19" t="n">
-        <v>6936850</v>
+        <v>6936187</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2565,11 +2490,6 @@
       <c r="AA19" t="inlineStr">
         <is>
           <t>2025-05-08</t>
-        </is>
-      </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2596,16 +2516,11 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>124880316</v>
+        <v>124880283</v>
       </c>
       <c r="B20" t="n">
         <v>57635</v>
       </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
       <c r="D20" t="inlineStr">
         <is>
           <t>NT</t>
@@ -2636,10 +2551,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>434532</v>
+        <v>433376</v>
       </c>
       <c r="R20" t="n">
-        <v>6936893</v>
+        <v>6935695</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2676,7 +2591,7 @@
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2703,16 +2618,11 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>124880358</v>
+        <v>124880369</v>
       </c>
       <c r="B21" t="n">
         <v>78947</v>
       </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
       <c r="D21" t="inlineStr">
         <is>
           <t>NT</t>
@@ -2743,10 +2653,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>433076</v>
+        <v>434091</v>
       </c>
       <c r="R21" t="n">
-        <v>6935108</v>
+        <v>6936122</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2783,7 +2693,7 @@
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>Rikligt</t>
+          <t>Mycket rikligt</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2810,16 +2720,11 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>124880310</v>
+        <v>124880305</v>
       </c>
       <c r="B22" t="n">
         <v>57635</v>
       </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
       <c r="D22" t="inlineStr">
         <is>
           <t>NT</t>
@@ -2850,10 +2755,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>434385</v>
+        <v>434128</v>
       </c>
       <c r="R22" t="n">
-        <v>6936814</v>
+        <v>6936677</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2917,15 +2822,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>124880365</v>
+        <v>124880346</v>
       </c>
       <c r="B23" t="n">
-        <v>78947</v>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91184</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2933,21 +2833,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2957,10 +2857,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>433755</v>
+        <v>434113</v>
       </c>
       <c r="R23" t="n">
-        <v>6935995</v>
+        <v>6936148</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2993,11 +2893,6 @@
       <c r="AA23" t="inlineStr">
         <is>
           <t>2025-05-08</t>
-        </is>
-      </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3024,16 +2919,11 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>124880359</v>
+        <v>124880365</v>
       </c>
       <c r="B24" t="n">
         <v>78947</v>
       </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
       <c r="D24" t="inlineStr">
         <is>
           <t>NT</t>
@@ -3064,10 +2954,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>433093</v>
+        <v>433755</v>
       </c>
       <c r="R24" t="n">
-        <v>6935150</v>
+        <v>6935995</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3131,15 +3021,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>124880344</v>
+        <v>124880360</v>
       </c>
       <c r="B25" t="n">
-        <v>91184</v>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78947</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3147,21 +3032,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3171,10 +3056,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>434028</v>
+        <v>433248</v>
       </c>
       <c r="R25" t="n">
-        <v>6936084</v>
+        <v>6935491</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3207,6 +3092,11 @@
       <c r="AA25" t="inlineStr">
         <is>
           <t>2025-05-08</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>Mycket rikligt</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3233,15 +3123,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>124880324</v>
+        <v>124880331</v>
       </c>
       <c r="B26" t="n">
-        <v>91162</v>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91184</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3249,21 +3134,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>1108</v>
+        <v>5432</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3273,10 +3158,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>433261</v>
+        <v>433193</v>
       </c>
       <c r="R26" t="n">
-        <v>6935504</v>
+        <v>6935352</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3335,16 +3220,11 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>124880360</v>
+        <v>124880367</v>
       </c>
       <c r="B27" t="n">
         <v>78947</v>
       </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
       <c r="D27" t="inlineStr">
         <is>
           <t>NT</t>
@@ -3375,10 +3255,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>433248</v>
+        <v>433984</v>
       </c>
       <c r="R27" t="n">
-        <v>6935491</v>
+        <v>6936073</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3442,15 +3322,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>124880299</v>
+        <v>124880358</v>
       </c>
       <c r="B28" t="n">
-        <v>57635</v>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78947</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3458,21 +3333,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3482,10 +3357,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>434112</v>
+        <v>433076</v>
       </c>
       <c r="R28" t="n">
-        <v>6936130</v>
+        <v>6935108</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3522,7 +3397,7 @@
       </c>
       <c r="AC28" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3549,15 +3424,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>124880313</v>
+        <v>124880332</v>
       </c>
       <c r="B29" t="n">
-        <v>57635</v>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91184</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3565,21 +3435,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3589,10 +3459,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>434447</v>
+        <v>433197</v>
       </c>
       <c r="R29" t="n">
-        <v>6936828</v>
+        <v>6935385</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3625,11 +3495,6 @@
       <c r="AA29" t="inlineStr">
         <is>
           <t>2025-05-08</t>
-        </is>
-      </c>
-      <c r="AC29" t="inlineStr">
-        <is>
-          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3656,15 +3521,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>124880329</v>
+        <v>124880361</v>
       </c>
       <c r="B30" t="n">
-        <v>91184</v>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78947</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3672,21 +3532,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3696,10 +3556,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>433106</v>
+        <v>433311</v>
       </c>
       <c r="R30" t="n">
-        <v>6935174</v>
+        <v>6935592</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3732,6 +3592,11 @@
       <c r="AA30" t="inlineStr">
         <is>
           <t>2025-05-08</t>
+        </is>
+      </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3758,16 +3623,11 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>124880372</v>
+        <v>124880373</v>
       </c>
       <c r="B31" t="n">
         <v>78947</v>
       </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
       <c r="D31" t="inlineStr">
         <is>
           <t>NT</t>
@@ -3798,10 +3658,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>434443</v>
+        <v>434482</v>
       </c>
       <c r="R31" t="n">
-        <v>6936839</v>
+        <v>6936858</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3838,7 +3698,7 @@
       </c>
       <c r="AC31" t="inlineStr">
         <is>
-          <t>Mycket rikligt</t>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3865,15 +3725,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>124880373</v>
+        <v>124880340</v>
       </c>
       <c r="B32" t="n">
-        <v>78947</v>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91184</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3881,21 +3736,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3905,10 +3760,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>434482</v>
+        <v>433661</v>
       </c>
       <c r="R32" t="n">
-        <v>6936858</v>
+        <v>6935941</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3941,11 +3796,6 @@
       <c r="AA32" t="inlineStr">
         <is>
           <t>2025-05-08</t>
-        </is>
-      </c>
-      <c r="AC32" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3972,15 +3822,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>124880303</v>
+        <v>124880364</v>
       </c>
       <c r="B33" t="n">
-        <v>57635</v>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78947</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3988,21 +3833,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4012,10 +3857,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>434113</v>
+        <v>433682</v>
       </c>
       <c r="R33" t="n">
-        <v>6936181</v>
+        <v>6935955</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4052,7 +3897,7 @@
       </c>
       <c r="AC33" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Mycket rikligt</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4079,15 +3924,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>124880346</v>
+        <v>124880299</v>
       </c>
       <c r="B34" t="n">
-        <v>91184</v>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57635</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4095,21 +3935,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4119,10 +3959,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>434113</v>
+        <v>434112</v>
       </c>
       <c r="R34" t="n">
-        <v>6936148</v>
+        <v>6936130</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4155,6 +3995,11 @@
       <c r="AA34" t="inlineStr">
         <is>
           <t>2025-05-08</t>
+        </is>
+      </c>
+      <c r="AC34" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4181,15 +4026,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>124880333</v>
+        <v>124880318</v>
       </c>
       <c r="B35" t="n">
-        <v>91184</v>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57635</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4197,21 +4037,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4221,10 +4061,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>433376</v>
+        <v>434664</v>
       </c>
       <c r="R35" t="n">
-        <v>6935725</v>
+        <v>6936929</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4257,6 +4097,11 @@
       <c r="AA35" t="inlineStr">
         <is>
           <t>2025-05-08</t>
+        </is>
+      </c>
+      <c r="AC35" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4283,16 +4128,11 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>124880295</v>
+        <v>124880288</v>
       </c>
       <c r="B36" t="n">
         <v>57635</v>
       </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
       <c r="D36" t="inlineStr">
         <is>
           <t>NT</t>
@@ -4323,10 +4163,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>433952</v>
+        <v>433505</v>
       </c>
       <c r="R36" t="n">
-        <v>6936043</v>
+        <v>6935809</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4390,16 +4230,11 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>124880304</v>
+        <v>124880275</v>
       </c>
       <c r="B37" t="n">
         <v>57635</v>
       </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
       <c r="D37" t="inlineStr">
         <is>
           <t>NT</t>
@@ -4430,10 +4265,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>434155</v>
+        <v>432954</v>
       </c>
       <c r="R37" t="n">
-        <v>6936279</v>
+        <v>6934982</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4502,11 +4337,6 @@
       <c r="B38" t="n">
         <v>57635</v>
       </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
       <c r="D38" t="inlineStr">
         <is>
           <t>NT</t>
@@ -4604,16 +4434,11 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>124880319</v>
+        <v>124880310</v>
       </c>
       <c r="B39" t="n">
         <v>57635</v>
       </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
       <c r="D39" t="inlineStr">
         <is>
           <t>NT</t>
@@ -4644,10 +4469,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>434789</v>
+        <v>434385</v>
       </c>
       <c r="R39" t="n">
-        <v>6936947</v>
+        <v>6936814</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4711,15 +4536,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>124880355</v>
+        <v>124880314</v>
       </c>
       <c r="B40" t="n">
-        <v>91184</v>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57635</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4727,21 +4547,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4751,10 +4571,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>434478</v>
+        <v>434484</v>
       </c>
       <c r="R40" t="n">
-        <v>6936874</v>
+        <v>6936850</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4787,6 +4607,11 @@
       <c r="AA40" t="inlineStr">
         <is>
           <t>2025-05-08</t>
+        </is>
+      </c>
+      <c r="AC40" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4813,15 +4638,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>124880369</v>
+        <v>124880237</v>
       </c>
       <c r="B41" t="n">
-        <v>78947</v>
-      </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91166</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4829,21 +4649,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4853,10 +4673,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>434091</v>
+        <v>433636</v>
       </c>
       <c r="R41" t="n">
-        <v>6936122</v>
+        <v>6935914</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4889,11 +4709,6 @@
       <c r="AA41" t="inlineStr">
         <is>
           <t>2025-05-08</t>
-        </is>
-      </c>
-      <c r="AC41" t="inlineStr">
-        <is>
-          <t>Mycket rikligt</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4920,15 +4735,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>124880278</v>
+        <v>124880337</v>
       </c>
       <c r="B42" t="n">
-        <v>57635</v>
-      </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91184</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4936,21 +4746,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4960,10 +4770,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>433331</v>
+        <v>433534</v>
       </c>
       <c r="R42" t="n">
-        <v>6935597</v>
+        <v>6935858</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4996,11 +4806,6 @@
       <c r="AA42" t="inlineStr">
         <is>
           <t>2025-05-08</t>
-        </is>
-      </c>
-      <c r="AC42" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5027,15 +4832,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>124880340</v>
+        <v>124880278</v>
       </c>
       <c r="B43" t="n">
-        <v>91184</v>
-      </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57635</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5043,21 +4843,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5067,10 +4867,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>433661</v>
+        <v>433331</v>
       </c>
       <c r="R43" t="n">
-        <v>6935941</v>
+        <v>6935597</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5103,6 +4903,11 @@
       <c r="AA43" t="inlineStr">
         <is>
           <t>2025-05-08</t>
+        </is>
+      </c>
+      <c r="AC43" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5129,15 +4934,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>124880361</v>
+        <v>124880319</v>
       </c>
       <c r="B44" t="n">
-        <v>78947</v>
-      </c>
-      <c r="C44" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57635</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5145,21 +4945,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5169,10 +4969,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>433311</v>
+        <v>434789</v>
       </c>
       <c r="R44" t="n">
-        <v>6935592</v>
+        <v>6936947</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5209,7 +5009,7 @@
       </c>
       <c r="AC44" t="inlineStr">
         <is>
-          <t>Rikligt</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5236,15 +5036,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>124880343</v>
+        <v>124880324</v>
       </c>
       <c r="B45" t="n">
-        <v>91184</v>
-      </c>
-      <c r="C45" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91162</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5252,21 +5047,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>5432</v>
+        <v>1108</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5276,10 +5071,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>433952</v>
+        <v>433261</v>
       </c>
       <c r="R45" t="n">
-        <v>6936054</v>
+        <v>6935504</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5338,16 +5133,11 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>124880353</v>
+        <v>124880345</v>
       </c>
       <c r="B46" t="n">
         <v>91184</v>
       </c>
-      <c r="C46" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
       <c r="D46" t="inlineStr">
         <is>
           <t>NT</t>
@@ -5378,10 +5168,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>434173</v>
+        <v>434057</v>
       </c>
       <c r="R46" t="n">
-        <v>6936342</v>
+        <v>6936091</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5440,15 +5230,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>124880367</v>
+        <v>124880303</v>
       </c>
       <c r="B47" t="n">
-        <v>78947</v>
-      </c>
-      <c r="C47" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57635</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5456,21 +5241,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5480,10 +5265,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>433984</v>
+        <v>434113</v>
       </c>
       <c r="R47" t="n">
-        <v>6936073</v>
+        <v>6936181</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5520,7 +5305,7 @@
       </c>
       <c r="AC47" t="inlineStr">
         <is>
-          <t>Mycket rikligt</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5547,16 +5332,11 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>124880275</v>
+        <v>124880316</v>
       </c>
       <c r="B48" t="n">
         <v>57635</v>
       </c>
-      <c r="C48" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
       <c r="D48" t="inlineStr">
         <is>
           <t>NT</t>
@@ -5587,10 +5367,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>432954</v>
+        <v>434532</v>
       </c>
       <c r="R48" t="n">
-        <v>6934982</v>
+        <v>6936893</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5654,15 +5434,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>124880371</v>
+        <v>124880343</v>
       </c>
       <c r="B49" t="n">
-        <v>78947</v>
-      </c>
-      <c r="C49" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91184</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5670,21 +5445,21 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5694,10 +5469,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>434167</v>
+        <v>433952</v>
       </c>
       <c r="R49" t="n">
-        <v>6936378</v>
+        <v>6936054</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5730,11 +5505,6 @@
       <c r="AA49" t="inlineStr">
         <is>
           <t>2025-05-08</t>
-        </is>
-      </c>
-      <c r="AC49" t="inlineStr">
-        <is>
-          <t>Mycket rikligt</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5761,15 +5531,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>124880332</v>
+        <v>124880304</v>
       </c>
       <c r="B50" t="n">
-        <v>91184</v>
-      </c>
-      <c r="C50" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57635</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5777,21 +5542,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5801,10 +5566,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>433197</v>
+        <v>434155</v>
       </c>
       <c r="R50" t="n">
-        <v>6935385</v>
+        <v>6936279</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5837,6 +5602,11 @@
       <c r="AA50" t="inlineStr">
         <is>
           <t>2025-05-08</t>
+        </is>
+      </c>
+      <c r="AC50" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -5863,16 +5633,11 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>124880283</v>
+        <v>124880296</v>
       </c>
       <c r="B51" t="n">
         <v>57635</v>
       </c>
-      <c r="C51" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
       <c r="D51" t="inlineStr">
         <is>
           <t>NT</t>
@@ -5903,10 +5668,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>433376</v>
+        <v>434019</v>
       </c>
       <c r="R51" t="n">
-        <v>6935695</v>
+        <v>6936070</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5943,7 +5708,7 @@
       </c>
       <c r="AC51" t="inlineStr">
         <is>
-          <t>Ringhack färska</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -5970,16 +5735,11 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>124880296</v>
+        <v>124880315</v>
       </c>
       <c r="B52" t="n">
         <v>57635</v>
       </c>
-      <c r="C52" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
       <c r="D52" t="inlineStr">
         <is>
           <t>NT</t>
@@ -6010,10 +5770,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>434019</v>
+        <v>434466</v>
       </c>
       <c r="R52" t="n">
-        <v>6936070</v>
+        <v>6936862</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
